--- a/fp22_m505_left 2.xlsx
+++ b/fp22_m505_left 2.xlsx
@@ -5,17 +5,30 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaki\Documents\Master Idrettsfysiologi og bevegelseslære\Masterprosjekt\Data_fp\FP22\Left\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nihno-my.sharepoint.com/personal/patrickm_nih_no/Documents/Desktop/WebApp1080sync/WebAppv0.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B767263-04CB-43E7-9AB6-F2094B19FE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{4B767263-04CB-43E7-9AB6-F2094B19FE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87ABD993-36DF-4D72-BB88-202091232FF5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -515,10 +528,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1068"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD1068"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -601,7 +614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -684,7 +697,7 @@
         <v>-2.2128735000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U3" s="1">
         <v>4.0400000000000001E-4</v>
       </c>
@@ -707,7 +720,7 @@
         <v>-2.22485</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U4" s="1">
         <v>8.3100000000000003E-4</v>
       </c>
@@ -730,7 +743,7 @@
         <v>-2.2509359999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U5" s="1">
         <v>1.2620000000000001E-3</v>
       </c>
@@ -753,7 +766,7 @@
         <v>-2.2826556999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U6" s="1">
         <v>1.7129999999999999E-3</v>
       </c>
@@ -775,8 +788,12 @@
       <c r="AA6" s="1">
         <v>-2.3222193999999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="AD6">
+        <f>1/V3</f>
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U7" s="1">
         <v>2.1689999999999999E-3</v>
       </c>
@@ -799,7 +816,7 @@
         <v>-2.3611276000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U8" s="1">
         <v>2.6310000000000001E-3</v>
       </c>
@@ -822,7 +839,7 @@
         <v>-2.3976307000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U9" s="1">
         <v>3.114E-3</v>
       </c>
@@ -845,7 +862,7 @@
         <v>-2.4444723000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U10" s="1">
         <v>3.6129999999999999E-3</v>
       </c>
@@ -868,7 +885,7 @@
         <v>-2.4997550999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U11" s="1">
         <v>4.1489999999999999E-3</v>
       </c>
@@ -891,7 +908,7 @@
         <v>-2.5709483999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U12" s="1">
         <v>4.7229999999999998E-3</v>
       </c>
@@ -914,7 +931,7 @@
         <v>-2.6605487000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U13" s="1">
         <v>5.025E-3</v>
       </c>
@@ -937,7 +954,7 @@
         <v>-2.7119713000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U14" s="1">
         <v>5.3420000000000004E-3</v>
       </c>
@@ -960,7 +977,7 @@
         <v>-2.7696209999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U15" s="1">
         <v>5.6639999999999998E-3</v>
       </c>
@@ -983,7 +1000,7 @@
         <v>-2.8313858999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="U16" s="1">
         <v>5.9969999999999997E-3</v>
       </c>
@@ -1006,7 +1023,7 @@
         <v>-2.8949346999999999</v>
       </c>
     </row>
-    <row r="17" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U17" s="1">
         <v>6.3330000000000001E-3</v>
       </c>
@@ -1029,7 +1046,7 @@
         <v>-2.9593492000000001</v>
       </c>
     </row>
-    <row r="18" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U18" s="1">
         <v>6.6829999999999997E-3</v>
       </c>
@@ -1052,7 +1069,7 @@
         <v>-3.0263553000000001</v>
       </c>
     </row>
-    <row r="19" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U19" s="1">
         <v>7.038E-3</v>
       </c>
@@ -1075,7 +1092,7 @@
         <v>-3.0960337999999998</v>
       </c>
     </row>
-    <row r="20" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U20" s="1">
         <v>7.3940000000000004E-3</v>
       </c>
@@ -1098,7 +1115,7 @@
         <v>-3.1631640000000001</v>
       </c>
     </row>
-    <row r="21" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U21" s="1">
         <v>7.7580000000000001E-3</v>
       </c>
@@ -1121,7 +1138,7 @@
         <v>-3.2293409999999998</v>
       </c>
     </row>
-    <row r="22" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U22" s="1">
         <v>8.1270000000000005E-3</v>
       </c>
@@ -1144,7 +1161,7 @@
         <v>-3.2956463999999999</v>
       </c>
     </row>
-    <row r="23" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U23" s="1">
         <v>8.5000000000000006E-3</v>
       </c>
@@ -1167,7 +1184,7 @@
         <v>-3.3606256999999999</v>
       </c>
     </row>
-    <row r="24" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U24" s="1">
         <v>8.8710000000000004E-3</v>
       </c>
@@ -1190,7 +1207,7 @@
         <v>-3.4225081999999998</v>
       </c>
     </row>
-    <row r="25" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U25" s="1">
         <v>9.2490000000000003E-3</v>
       </c>
@@ -1213,7 +1230,7 @@
         <v>-3.4820266000000002</v>
       </c>
     </row>
-    <row r="26" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U26" s="1">
         <v>9.6319999999999999E-3</v>
       </c>
@@ -1236,7 +1253,7 @@
         <v>-3.5418219999999998</v>
       </c>
     </row>
-    <row r="27" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U27" s="1">
         <v>1.0018000000000001E-2</v>
       </c>
@@ -1259,7 +1276,7 @@
         <v>-3.60101</v>
       </c>
     </row>
-    <row r="28" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U28" s="1">
         <v>1.0414E-2</v>
       </c>
@@ -1282,7 +1299,7 @@
         <v>-3.6611793000000001</v>
       </c>
     </row>
-    <row r="29" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U29" s="1">
         <v>1.0817E-2</v>
       </c>
@@ -1305,7 +1322,7 @@
         <v>-3.7235963000000001</v>
       </c>
     </row>
-    <row r="30" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U30" s="1">
         <v>1.1232000000000001E-2</v>
       </c>
@@ -1328,7 +1345,7 @@
         <v>-3.7892225000000002</v>
       </c>
     </row>
-    <row r="31" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U31" s="1">
         <v>1.1656E-2</v>
       </c>
@@ -1351,7 +1368,7 @@
         <v>-3.8582114999999999</v>
       </c>
     </row>
-    <row r="32" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U32" s="1">
         <v>1.2087000000000001E-2</v>
       </c>
@@ -1374,7 +1391,7 @@
         <v>-3.9284842000000002</v>
       </c>
     </row>
-    <row r="33" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="33" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U33" s="1">
         <v>1.2532E-2</v>
       </c>
@@ -1397,7 +1414,7 @@
         <v>-4.0020709999999999</v>
       </c>
     </row>
-    <row r="34" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="34" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U34" s="1">
         <v>1.2997999999999999E-2</v>
       </c>
@@ -1420,7 +1437,7 @@
         <v>-4.0837745999999999</v>
       </c>
     </row>
-    <row r="35" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="35" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U35" s="1">
         <v>1.3476999999999999E-2</v>
       </c>
@@ -1443,7 +1460,7 @@
         <v>-4.1727432999999996</v>
       </c>
     </row>
-    <row r="36" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="36" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U36" s="1">
         <v>1.3978000000000001E-2</v>
       </c>
@@ -1466,7 +1483,7 @@
         <v>-4.2689877000000003</v>
       </c>
     </row>
-    <row r="37" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="37" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U37" s="1">
         <v>1.4507000000000001E-2</v>
       </c>
@@ -1489,7 +1506,7 @@
         <v>-4.3773736999999997</v>
       </c>
     </row>
-    <row r="38" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="38" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U38" s="1">
         <v>1.506E-2</v>
       </c>
@@ -1512,7 +1529,7 @@
         <v>-4.4975610000000001</v>
       </c>
     </row>
-    <row r="39" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="39" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U39" s="1">
         <v>1.5639E-2</v>
       </c>
@@ -1535,7 +1552,7 @@
         <v>-4.6276630000000001</v>
       </c>
     </row>
-    <row r="40" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="40" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U40" s="1">
         <v>1.6240000000000001E-2</v>
       </c>
@@ -1558,7 +1575,7 @@
         <v>-4.7666700000000004</v>
       </c>
     </row>
-    <row r="41" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="41" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U41" s="1">
         <v>1.6868000000000001E-2</v>
       </c>
@@ -1581,7 +1598,7 @@
         <v>-4.9143400000000002</v>
       </c>
     </row>
-    <row r="42" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="42" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U42" s="1">
         <v>1.7517000000000001E-2</v>
       </c>
@@ -1604,7 +1621,7 @@
         <v>-5.0693564000000002</v>
       </c>
     </row>
-    <row r="43" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="43" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U43" s="1">
         <v>1.8179000000000001E-2</v>
       </c>
@@ -1627,7 +1644,7 @@
         <v>-5.2263292999999997</v>
       </c>
     </row>
-    <row r="44" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="44" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U44" s="1">
         <v>1.8860999999999999E-2</v>
       </c>
@@ -1650,7 +1667,7 @@
         <v>-5.3843899999999998</v>
       </c>
     </row>
-    <row r="45" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="45" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U45" s="1">
         <v>1.9554999999999999E-2</v>
       </c>
@@ -1673,7 +1690,7 @@
         <v>-5.5434890000000001</v>
       </c>
     </row>
-    <row r="46" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="46" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U46" s="1">
         <v>2.0258000000000002E-2</v>
       </c>
@@ -1696,7 +1713,7 @@
         <v>-5.6997232000000002</v>
       </c>
     </row>
-    <row r="47" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="47" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U47" s="1">
         <v>2.0972999999999999E-2</v>
       </c>
@@ -1719,7 +1736,7 @@
         <v>-5.853529</v>
       </c>
     </row>
-    <row r="48" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="48" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U48" s="1">
         <v>2.1699E-2</v>
       </c>
@@ -1742,7 +1759,7 @@
         <v>-6.0055785000000004</v>
       </c>
     </row>
-    <row r="49" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="49" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U49" s="1">
         <v>2.2435E-2</v>
       </c>
@@ -1765,7 +1782,7 @@
         <v>-6.1551647000000003</v>
       </c>
     </row>
-    <row r="50" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="50" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U50" s="1">
         <v>2.3185999999999998E-2</v>
       </c>
@@ -1788,7 +1805,7 @@
         <v>-6.3044250000000002</v>
       </c>
     </row>
-    <row r="51" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="51" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U51" s="1">
         <v>2.3951E-2</v>
       </c>
@@ -1811,7 +1828,7 @@
         <v>-6.4542210000000004</v>
       </c>
     </row>
-    <row r="52" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="52" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U52" s="1">
         <v>2.4735E-2</v>
       </c>
@@ -1834,7 +1851,7 @@
         <v>-6.6060749999999997</v>
       </c>
     </row>
-    <row r="53" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="53" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U53" s="1">
         <v>2.5538999999999999E-2</v>
       </c>
@@ -1857,7 +1874,7 @@
         <v>-6.7615170000000004</v>
       </c>
     </row>
-    <row r="54" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="54" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U54" s="1">
         <v>2.6363000000000001E-2</v>
       </c>
@@ -1880,7 +1897,7 @@
         <v>-6.9206000000000003</v>
       </c>
     </row>
-    <row r="55" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="55" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U55" s="1">
         <v>2.7199999999999998E-2</v>
       </c>
@@ -1903,7 +1920,7 @@
         <v>-7.0808780000000002</v>
       </c>
     </row>
-    <row r="56" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="56" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U56" s="1">
         <v>2.8053999999999999E-2</v>
       </c>
@@ -1926,7 +1943,7 @@
         <v>-7.2411903999999998</v>
       </c>
     </row>
-    <row r="57" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="57" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U57" s="1">
         <v>2.8913999999999999E-2</v>
       </c>
@@ -1949,7 +1966,7 @@
         <v>-7.3995199999999999</v>
       </c>
     </row>
-    <row r="58" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="58" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U58" s="1">
         <v>2.9787000000000001E-2</v>
       </c>
@@ -1972,7 +1989,7 @@
         <v>-7.5546509999999998</v>
       </c>
     </row>
-    <row r="59" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="59" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U59" s="1">
         <v>3.0667E-2</v>
       </c>
@@ -1995,7 +2012,7 @@
         <v>-7.7068887000000004</v>
       </c>
     </row>
-    <row r="60" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="60" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U60" s="1">
         <v>3.1553999999999999E-2</v>
       </c>
@@ -2018,7 +2035,7 @@
         <v>-7.8547799999999999</v>
       </c>
     </row>
-    <row r="61" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="61" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U61" s="1">
         <v>3.2452000000000002E-2</v>
       </c>
@@ -2041,7 +2058,7 @@
         <v>-7.9997534999999997</v>
       </c>
     </row>
-    <row r="62" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="62" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U62" s="1">
         <v>3.3362000000000003E-2</v>
       </c>
@@ -2064,7 +2081,7 @@
         <v>-8.1437489999999997</v>
       </c>
     </row>
-    <row r="63" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="63" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U63" s="1">
         <v>3.4285999999999997E-2</v>
       </c>
@@ -2087,7 +2104,7 @@
         <v>-8.2885120000000008</v>
       </c>
     </row>
-    <row r="64" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="64" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U64" s="1">
         <v>3.5229999999999997E-2</v>
       </c>
@@ -2110,7 +2127,7 @@
         <v>-8.4351129999999994</v>
       </c>
     </row>
-    <row r="65" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="65" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U65" s="1">
         <v>3.6198000000000001E-2</v>
       </c>
@@ -2133,7 +2150,7 @@
         <v>-8.5870110000000004</v>
       </c>
     </row>
-    <row r="66" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="66" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U66" s="1">
         <v>3.7178000000000003E-2</v>
       </c>
@@ -2156,7 +2173,7 @@
         <v>-8.7421629999999997</v>
       </c>
     </row>
-    <row r="67" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="67" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U67" s="1">
         <v>3.8179999999999999E-2</v>
       </c>
@@ -2179,7 +2196,7 @@
         <v>-8.8987040000000004</v>
       </c>
     </row>
-    <row r="68" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="68" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U68" s="1">
         <v>3.9187E-2</v>
       </c>
@@ -2202,7 +2219,7 @@
         <v>-9.0540289999999999</v>
       </c>
     </row>
-    <row r="69" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="69" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U69" s="1">
         <v>4.0215000000000001E-2</v>
       </c>
@@ -2225,7 +2242,7 @@
         <v>-9.2089119999999998</v>
       </c>
     </row>
-    <row r="70" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="70" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U70" s="1">
         <v>4.1258999999999997E-2</v>
       </c>
@@ -2248,7 +2265,7 @@
         <v>-9.3667870000000004</v>
       </c>
     </row>
-    <row r="71" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="71" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U71" s="1">
         <v>4.2313000000000003E-2</v>
       </c>
@@ -2271,7 +2288,7 @@
         <v>-9.5236940000000008</v>
       </c>
     </row>
-    <row r="72" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="72" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U72" s="1">
         <v>4.3393000000000001E-2</v>
       </c>
@@ -2294,7 +2311,7 @@
         <v>-9.6832180000000001</v>
       </c>
     </row>
-    <row r="73" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="73" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U73" s="1">
         <v>4.4502E-2</v>
       </c>
@@ -2317,7 +2334,7 @@
         <v>-9.8506260000000001</v>
       </c>
     </row>
-    <row r="74" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="74" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U74" s="1">
         <v>4.5638999999999999E-2</v>
       </c>
@@ -2340,7 +2357,7 @@
         <v>-10.02618</v>
       </c>
     </row>
-    <row r="75" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="75" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U75" s="1">
         <v>4.6804999999999999E-2</v>
       </c>
@@ -2363,7 +2380,7 @@
         <v>-10.2092285</v>
       </c>
     </row>
-    <row r="76" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="76" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U76" s="1">
         <v>4.7996999999999998E-2</v>
       </c>
@@ -2386,7 +2403,7 @@
         <v>-10.398078</v>
       </c>
     </row>
-    <row r="77" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="77" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U77" s="1">
         <v>4.9209000000000003E-2</v>
       </c>
@@ -2409,7 +2426,7 @@
         <v>-10.58961</v>
       </c>
     </row>
-    <row r="78" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="78" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U78" s="1">
         <v>5.0437000000000003E-2</v>
       </c>
@@ -2432,7 +2449,7 @@
         <v>-10.780436999999999</v>
       </c>
     </row>
-    <row r="79" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="79" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U79" s="1">
         <v>5.1684000000000001E-2</v>
       </c>
@@ -2455,7 +2472,7 @@
         <v>-10.971788</v>
       </c>
     </row>
-    <row r="80" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="80" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U80" s="1">
         <v>5.2953E-2</v>
       </c>
@@ -2478,7 +2495,7 @@
         <v>-11.166078000000001</v>
       </c>
     </row>
-    <row r="81" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="81" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U81" s="1">
         <v>5.4252000000000002E-2</v>
       </c>
@@ -2501,7 +2518,7 @@
         <v>-11.364907000000001</v>
       </c>
     </row>
-    <row r="82" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="82" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U82" s="1">
         <v>5.5579000000000003E-2</v>
       </c>
@@ -2524,7 +2541,7 @@
         <v>-11.57009</v>
       </c>
     </row>
-    <row r="83" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="83" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U83" s="1">
         <v>5.6945000000000003E-2</v>
       </c>
@@ -2547,7 +2564,7 @@
         <v>-11.783906</v>
       </c>
     </row>
-    <row r="84" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="84" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U84" s="1">
         <v>5.8333000000000003E-2</v>
       </c>
@@ -2570,7 +2587,7 @@
         <v>-12.0027075</v>
       </c>
     </row>
-    <row r="85" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="85" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U85" s="1">
         <v>5.9748999999999997E-2</v>
       </c>
@@ -2593,7 +2610,7 @@
         <v>-12.223364999999999</v>
       </c>
     </row>
-    <row r="86" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="86" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U86" s="1">
         <v>6.1183000000000001E-2</v>
       </c>
@@ -2616,7 +2633,7 @@
         <v>-12.445209999999999</v>
       </c>
     </row>
-    <row r="87" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="87" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U87" s="1">
         <v>6.2649999999999997E-2</v>
       </c>
@@ -2639,7 +2656,7 @@
         <v>-12.669822</v>
       </c>
     </row>
-    <row r="88" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="88" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U88" s="1">
         <v>6.4149999999999999E-2</v>
       </c>
@@ -2662,7 +2679,7 @@
         <v>-12.901928</v>
       </c>
     </row>
-    <row r="89" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="89" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U89" s="1">
         <v>6.5689999999999998E-2</v>
       </c>
@@ -2685,7 +2702,7 @@
         <v>-13.142649</v>
       </c>
     </row>
-    <row r="90" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="90" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U90" s="1">
         <v>6.7267999999999994E-2</v>
       </c>
@@ -2708,7 +2725,7 @@
         <v>-13.391736</v>
       </c>
     </row>
-    <row r="91" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="91" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U91" s="1">
         <v>6.8875000000000006E-2</v>
       </c>
@@ -2731,7 +2748,7 @@
         <v>-13.644707</v>
       </c>
     </row>
-    <row r="92" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="92" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U92" s="1">
         <v>7.0515999999999995E-2</v>
       </c>
@@ -2754,7 +2771,7 @@
         <v>-13.900867</v>
       </c>
     </row>
-    <row r="93" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="93" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U93" s="1">
         <v>7.2184999999999999E-2</v>
       </c>
@@ -2777,7 +2794,7 @@
         <v>-14.161262000000001</v>
       </c>
     </row>
-    <row r="94" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="94" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U94" s="1">
         <v>7.3891999999999999E-2</v>
       </c>
@@ -2800,7 +2817,7 @@
         <v>-14.426545000000001</v>
       </c>
     </row>
-    <row r="95" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="95" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U95" s="1">
         <v>7.5638999999999998E-2</v>
       </c>
@@ -2823,7 +2840,7 @@
         <v>-14.698883</v>
       </c>
     </row>
-    <row r="96" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="96" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U96" s="1">
         <v>7.7425999999999995E-2</v>
       </c>
@@ -2846,7 +2863,7 @@
         <v>-14.9783945</v>
       </c>
     </row>
-    <row r="97" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="97" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U97" s="1">
         <v>7.9243999999999995E-2</v>
       </c>
@@ -2869,7 +2886,7 @@
         <v>-15.261108999999999</v>
       </c>
     </row>
-    <row r="98" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="98" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U98" s="1">
         <v>8.1090999999999996E-2</v>
       </c>
@@ -2892,7 +2909,7 @@
         <v>-15.544264</v>
       </c>
     </row>
-    <row r="99" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="99" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U99" s="1">
         <v>8.2968E-2</v>
       </c>
@@ -2915,7 +2932,7 @@
         <v>-15.829007000000001</v>
       </c>
     </row>
-    <row r="100" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="100" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U100" s="1">
         <v>8.4880999999999998E-2</v>
       </c>
@@ -2938,7 +2955,7 @@
         <v>-16.117075</v>
       </c>
     </row>
-    <row r="101" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="101" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U101" s="1">
         <v>8.6830000000000004E-2</v>
       </c>
@@ -2961,7 +2978,7 @@
         <v>-16.410050999999999</v>
       </c>
     </row>
-    <row r="102" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="102" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U102" s="1">
         <v>8.8804999999999995E-2</v>
       </c>
@@ -2984,7 +3001,7 @@
         <v>-16.703678</v>
       </c>
     </row>
-    <row r="103" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="103" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U103" s="1">
         <v>9.0801000000000007E-2</v>
       </c>
@@ -3007,7 +3024,7 @@
         <v>-16.993939999999998</v>
       </c>
     </row>
-    <row r="104" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="104" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U104" s="1">
         <v>9.2824000000000004E-2</v>
       </c>
@@ -3030,7 +3047,7 @@
         <v>-17.283339999999999</v>
       </c>
     </row>
-    <row r="105" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="105" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U105" s="1">
         <v>9.4883999999999996E-2</v>
       </c>
@@ -3053,7 +3070,7 @@
         <v>-17.576029999999999</v>
       </c>
     </row>
-    <row r="106" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="106" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U106" s="1">
         <v>9.6980999999999998E-2</v>
       </c>
@@ -3076,7 +3093,7 @@
         <v>-17.873267999999999</v>
       </c>
     </row>
-    <row r="107" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="107" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U107" s="1">
         <v>9.9099999999999994E-2</v>
       </c>
@@ -3099,7 +3116,7 @@
         <v>-18.169388000000001</v>
       </c>
     </row>
-    <row r="108" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="108" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U108" s="1">
         <v>0.101253</v>
       </c>
@@ -3122,7 +3139,7 @@
         <v>-18.464756000000001</v>
       </c>
     </row>
-    <row r="109" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="109" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U109" s="1">
         <v>0.10344</v>
       </c>
@@ -3145,7 +3162,7 @@
         <v>-18.763127999999998</v>
       </c>
     </row>
-    <row r="110" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="110" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U110" s="1">
         <v>0.10567</v>
       </c>
@@ -3168,7 +3185,7 @@
         <v>-19.065968000000002</v>
       </c>
     </row>
-    <row r="111" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="111" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U111" s="1">
         <v>0.10793800000000001</v>
       </c>
@@ -3191,7 +3208,7 @@
         <v>-19.373182</v>
       </c>
     </row>
-    <row r="112" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="112" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U112" s="1">
         <v>0.11024100000000001</v>
       </c>
@@ -3214,7 +3231,7 @@
         <v>-19.681764999999999</v>
       </c>
     </row>
-    <row r="113" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="113" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U113" s="1">
         <v>0.112584</v>
       </c>
@@ -3237,7 +3254,7 @@
         <v>-19.992815</v>
       </c>
     </row>
-    <row r="114" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="114" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U114" s="1">
         <v>0.114972</v>
       </c>
@@ -3260,7 +3277,7 @@
         <v>-20.309587000000001</v>
       </c>
     </row>
-    <row r="115" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="115" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U115" s="1">
         <v>0.117411</v>
       </c>
@@ -3283,7 +3300,7 @@
         <v>-20.633823</v>
       </c>
     </row>
-    <row r="116" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="116" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U116" s="1">
         <v>0.119889</v>
       </c>
@@ -3306,7 +3323,7 @@
         <v>-20.961842999999998</v>
       </c>
     </row>
-    <row r="117" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="117" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U117" s="1">
         <v>0.122418</v>
       </c>
@@ -3329,7 +3346,7 @@
         <v>-21.293856000000002</v>
       </c>
     </row>
-    <row r="118" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="118" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U118" s="1">
         <v>0.12500900000000001</v>
       </c>
@@ -3352,7 +3369,7 @@
         <v>-21.635694999999998</v>
       </c>
     </row>
-    <row r="119" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="119" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U119" s="1">
         <v>0.12764900000000001</v>
       </c>
@@ -3375,7 +3392,7 @@
         <v>-21.984256999999999</v>
       </c>
     </row>
-    <row r="120" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="120" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U120" s="1">
         <v>0.13034200000000001</v>
       </c>
@@ -3398,7 +3415,7 @@
         <v>-22.337523999999998</v>
       </c>
     </row>
-    <row r="121" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="121" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U121" s="1">
         <v>0.13309799999999999</v>
       </c>
@@ -3421,7 +3438,7 @@
         <v>-22.699463000000002</v>
       </c>
     </row>
-    <row r="122" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="122" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U122" s="1">
         <v>0.13591800000000001</v>
       </c>
@@ -3444,7 +3461,7 @@
         <v>-23.070758999999999</v>
       </c>
     </row>
-    <row r="123" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="123" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U123" s="1">
         <v>0.138798</v>
       </c>
@@ -3467,7 +3484,7 @@
         <v>-23.449697</v>
       </c>
     </row>
-    <row r="124" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="124" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U124" s="1">
         <v>0.14174200000000001</v>
       </c>
@@ -3490,7 +3507,7 @@
         <v>-23.835094000000002</v>
       </c>
     </row>
-    <row r="125" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="125" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U125" s="1">
         <v>0.144759</v>
       </c>
@@ -3513,7 +3530,7 @@
         <v>-24.229769000000001</v>
       </c>
     </row>
-    <row r="126" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="126" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U126" s="1">
         <v>0.14785000000000001</v>
       </c>
@@ -3536,7 +3553,7 @@
         <v>-24.634253000000001</v>
       </c>
     </row>
-    <row r="127" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="127" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U127" s="1">
         <v>0.15101500000000001</v>
       </c>
@@ -3559,7 +3576,7 @@
         <v>-25.047219999999999</v>
       </c>
     </row>
-    <row r="128" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="128" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U128" s="1">
         <v>0.15426100000000001</v>
       </c>
@@ -3582,7 +3599,7 @@
         <v>-25.469536000000002</v>
       </c>
     </row>
-    <row r="129" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="129" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U129" s="1">
         <v>0.15759300000000001</v>
       </c>
@@ -3605,7 +3622,7 @@
         <v>-25.902925</v>
       </c>
     </row>
-    <row r="130" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="130" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U130" s="1">
         <v>0.16100700000000001</v>
       </c>
@@ -3628,7 +3645,7 @@
         <v>-26.344898000000001</v>
       </c>
     </row>
-    <row r="131" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="131" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U131" s="1">
         <v>0.16451299999999999</v>
       </c>
@@ -3651,7 +3668,7 @@
         <v>-26.796285999999998</v>
       </c>
     </row>
-    <row r="132" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="132" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U132" s="1">
         <v>0.16811300000000001</v>
       </c>
@@ -3674,7 +3691,7 @@
         <v>-27.257729000000001</v>
       </c>
     </row>
-    <row r="133" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="133" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U133" s="1">
         <v>0.17180799999999999</v>
       </c>
@@ -3697,7 +3714,7 @@
         <v>-27.727577</v>
       </c>
     </row>
-    <row r="134" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="134" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U134" s="1">
         <v>0.17560200000000001</v>
       </c>
@@ -3720,7 +3737,7 @@
         <v>-28.207668000000002</v>
       </c>
     </row>
-    <row r="135" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="135" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U135" s="1">
         <v>0.17949200000000001</v>
       </c>
@@ -3743,7 +3760,7 @@
         <v>-28.696169999999999</v>
       </c>
     </row>
-    <row r="136" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="136" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U136" s="1">
         <v>0.18348600000000001</v>
       </c>
@@ -3766,7 +3783,7 @@
         <v>-29.193000000000001</v>
       </c>
     </row>
-    <row r="137" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="137" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U137" s="1">
         <v>0.187581</v>
       </c>
@@ -3789,7 +3806,7 @@
         <v>-29.697092000000001</v>
       </c>
     </row>
-    <row r="138" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="138" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U138" s="1">
         <v>0.191771</v>
       </c>
@@ -3812,7 +3829,7 @@
         <v>-30.20682</v>
       </c>
     </row>
-    <row r="139" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="139" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U139" s="1">
         <v>0.19606199999999999</v>
       </c>
@@ -3835,7 +3852,7 @@
         <v>-30.723700000000001</v>
       </c>
     </row>
-    <row r="140" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="140" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U140" s="1">
         <v>0.20044600000000001</v>
       </c>
@@ -3858,7 +3875,7 @@
         <v>-31.247188999999999</v>
       </c>
     </row>
-    <row r="141" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="141" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U141" s="1">
         <v>0.204932</v>
       </c>
@@ -3881,7 +3898,7 @@
         <v>-31.778545000000001</v>
       </c>
     </row>
-    <row r="142" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="142" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U142" s="1">
         <v>0.209505</v>
       </c>
@@ -3904,7 +3921,7 @@
         <v>-32.31561</v>
       </c>
     </row>
-    <row r="143" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="143" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U143" s="1">
         <v>0.214172</v>
       </c>
@@ -3927,7 +3944,7 @@
         <v>-32.857726999999997</v>
       </c>
     </row>
-    <row r="144" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="144" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U144" s="1">
         <v>0.21892300000000001</v>
       </c>
@@ -3950,7 +3967,7 @@
         <v>-33.405482999999997</v>
       </c>
     </row>
-    <row r="145" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="145" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U145" s="1">
         <v>0.22376199999999999</v>
       </c>
@@ -3973,7 +3990,7 @@
         <v>-33.958939999999998</v>
       </c>
     </row>
-    <row r="146" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="146" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U146" s="1">
         <v>0.228681</v>
       </c>
@@ -3996,7 +4013,7 @@
         <v>-34.519444</v>
       </c>
     </row>
-    <row r="147" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="147" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U147" s="1">
         <v>0.233683</v>
       </c>
@@ -4019,7 +4036,7 @@
         <v>-35.086692999999997</v>
       </c>
     </row>
-    <row r="148" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="148" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U148" s="1">
         <v>0.23876500000000001</v>
       </c>
@@ -4042,7 +4059,7 @@
         <v>-35.66048</v>
       </c>
     </row>
-    <row r="149" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="149" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U149" s="1">
         <v>0.243922</v>
       </c>
@@ -4065,7 +4082,7 @@
         <v>-36.23939</v>
       </c>
     </row>
-    <row r="150" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="150" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U150" s="1">
         <v>0.24915599999999999</v>
       </c>
@@ -4088,7 +4105,7 @@
         <v>-36.824170000000002</v>
       </c>
     </row>
-    <row r="151" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="151" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U151" s="1">
         <v>0.254467</v>
       </c>
@@ -4111,7 +4128,7 @@
         <v>-37.415089999999999</v>
       </c>
     </row>
-    <row r="152" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="152" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U152" s="1">
         <v>0.25985599999999998</v>
       </c>
@@ -4134,7 +4151,7 @@
         <v>-38.012030000000003</v>
       </c>
     </row>
-    <row r="153" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="153" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U153" s="1">
         <v>0.265318</v>
       </c>
@@ -4157,7 +4174,7 @@
         <v>-38.614047999999997</v>
       </c>
     </row>
-    <row r="154" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="154" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U154" s="1">
         <v>0.27085300000000001</v>
       </c>
@@ -4180,7 +4197,7 @@
         <v>-39.220066000000003</v>
       </c>
     </row>
-    <row r="155" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="155" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U155" s="1">
         <v>0.27646100000000001</v>
       </c>
@@ -4203,7 +4220,7 @@
         <v>-39.829470000000001</v>
       </c>
     </row>
-    <row r="156" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="156" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U156" s="1">
         <v>0.28214299999999998</v>
       </c>
@@ -4226,7 +4243,7 @@
         <v>-40.443237000000003</v>
       </c>
     </row>
-    <row r="157" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="157" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U157" s="1">
         <v>0.28789100000000001</v>
       </c>
@@ -4249,7 +4266,7 @@
         <v>-41.061169999999997</v>
       </c>
     </row>
-    <row r="158" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="158" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U158" s="1">
         <v>0.293715</v>
       </c>
@@ -4272,7 +4289,7 @@
         <v>-41.682625000000002</v>
       </c>
     </row>
-    <row r="159" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="159" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U159" s="1">
         <v>0.29961100000000002</v>
       </c>
@@ -4295,7 +4312,7 @@
         <v>-42.306469999999997</v>
       </c>
     </row>
-    <row r="160" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="160" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U160" s="1">
         <v>0.30557899999999999</v>
       </c>
@@ -4318,7 +4335,7 @@
         <v>-42.931373999999998</v>
       </c>
     </row>
-    <row r="161" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="161" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U161" s="1">
         <v>0.31162000000000001</v>
       </c>
@@ -4341,7 +4358,7 @@
         <v>-43.558059999999998</v>
       </c>
     </row>
-    <row r="162" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="162" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U162" s="1">
         <v>0.31773899999999999</v>
       </c>
@@ -4364,7 +4381,7 @@
         <v>-44.185577000000002</v>
       </c>
     </row>
-    <row r="163" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="163" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U163" s="1">
         <v>0.323932</v>
       </c>
@@ -4387,7 +4404,7 @@
         <v>-44.812206000000003</v>
       </c>
     </row>
-    <row r="164" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="164" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U164" s="1">
         <v>0.33019999999999999</v>
       </c>
@@ -4410,7 +4427,7 @@
         <v>-45.437953999999998</v>
       </c>
     </row>
-    <row r="165" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="165" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U165" s="1">
         <v>0.33653300000000003</v>
       </c>
@@ -4433,7 +4450,7 @@
         <v>-46.063299999999998</v>
       </c>
     </row>
-    <row r="166" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="166" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U166" s="1">
         <v>0.342941</v>
       </c>
@@ -4456,7 +4473,7 @@
         <v>-46.690094000000002</v>
       </c>
     </row>
-    <row r="167" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="167" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U167" s="1">
         <v>0.349416</v>
       </c>
@@ -4479,7 +4496,7 @@
         <v>-47.318398000000002</v>
       </c>
     </row>
-    <row r="168" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="168" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U168" s="1">
         <v>0.35595599999999999</v>
       </c>
@@ -4502,7 +4519,7 @@
         <v>-47.947654999999997</v>
       </c>
     </row>
-    <row r="169" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="169" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U169" s="1">
         <v>0.36255500000000002</v>
       </c>
@@ -4525,7 +4542,7 @@
         <v>-48.580489999999998</v>
       </c>
     </row>
-    <row r="170" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="170" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U170" s="1">
         <v>0.36921500000000002</v>
       </c>
@@ -4548,7 +4565,7 @@
         <v>-49.218772999999999</v>
       </c>
     </row>
-    <row r="171" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="171" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U171" s="1">
         <v>0.37592199999999998</v>
       </c>
@@ -4571,7 +4588,7 @@
         <v>-49.862780000000001</v>
       </c>
     </row>
-    <row r="172" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="172" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U172" s="1">
         <v>0.38267800000000002</v>
       </c>
@@ -4594,7 +4611,7 @@
         <v>-50.513393000000001</v>
       </c>
     </row>
-    <row r="173" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="173" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U173" s="1">
         <v>0.38947199999999998</v>
       </c>
@@ -4617,7 +4634,7 @@
         <v>-51.171289999999999</v>
       </c>
     </row>
-    <row r="174" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="174" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U174" s="1">
         <v>0.39629999999999999</v>
       </c>
@@ -4640,7 +4657,7 @@
         <v>-51.837986000000001</v>
       </c>
     </row>
-    <row r="175" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="175" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U175" s="1">
         <v>0.40315299999999998</v>
       </c>
@@ -4663,7 +4680,7 @@
         <v>-52.51652</v>
       </c>
     </row>
-    <row r="176" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="176" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U176" s="1">
         <v>0.41001799999999999</v>
       </c>
@@ -4686,7 +4703,7 @@
         <v>-53.206879999999998</v>
       </c>
     </row>
-    <row r="177" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="177" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U177" s="1">
         <v>0.41689199999999998</v>
       </c>
@@ -4709,7 +4726,7 @@
         <v>-53.913029999999999</v>
       </c>
     </row>
-    <row r="178" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="178" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U178" s="1">
         <v>0.42375200000000002</v>
       </c>
@@ -4732,7 +4749,7 @@
         <v>-54.635463999999999</v>
       </c>
     </row>
-    <row r="179" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="179" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U179" s="1">
         <v>0.430591</v>
       </c>
@@ -4755,7 +4772,7 @@
         <v>-55.377243</v>
       </c>
     </row>
-    <row r="180" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="180" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U180" s="1">
         <v>0.43739</v>
       </c>
@@ -4778,7 +4795,7 @@
         <v>-56.141433999999997</v>
       </c>
     </row>
-    <row r="181" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="181" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U181" s="1">
         <v>0.44413599999999998</v>
       </c>
@@ -4801,7 +4818,7 @@
         <v>-56.92765</v>
       </c>
     </row>
-    <row r="182" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="182" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U182" s="1">
         <v>0.45081700000000002</v>
       </c>
@@ -4824,7 +4841,7 @@
         <v>-57.735686999999999</v>
       </c>
     </row>
-    <row r="183" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="183" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U183" s="1">
         <v>0.457424</v>
       </c>
@@ -4847,7 +4864,7 @@
         <v>-58.561030000000002</v>
       </c>
     </row>
-    <row r="184" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="184" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U184" s="1">
         <v>0.46393899999999999</v>
       </c>
@@ -4870,7 +4887,7 @@
         <v>-59.399185000000003</v>
       </c>
     </row>
-    <row r="185" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="185" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U185" s="1">
         <v>0.47036099999999997</v>
       </c>
@@ -4893,7 +4910,7 @@
         <v>-60.243206000000001</v>
       </c>
     </row>
-    <row r="186" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="186" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U186" s="1">
         <v>0.47668500000000003</v>
       </c>
@@ -4916,7 +4933,7 @@
         <v>-61.084389999999999</v>
       </c>
     </row>
-    <row r="187" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="187" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U187" s="1">
         <v>0.48291400000000001</v>
       </c>
@@ -4939,7 +4956,7 @@
         <v>-61.910632999999997</v>
       </c>
     </row>
-    <row r="188" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="188" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U188" s="1">
         <v>0.48904500000000001</v>
       </c>
@@ -4962,7 +4979,7 @@
         <v>-62.709519999999998</v>
       </c>
     </row>
-    <row r="189" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="189" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U189" s="1">
         <v>0.49509599999999998</v>
       </c>
@@ -4985,7 +5002,7 @@
         <v>-63.468800000000002</v>
       </c>
     </row>
-    <row r="190" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="190" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U190" s="1">
         <v>0.50107699999999999</v>
       </c>
@@ -5008,7 +5025,7 @@
         <v>-64.173339999999996</v>
       </c>
     </row>
-    <row r="191" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="191" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U191" s="1">
         <v>0.50700500000000004</v>
       </c>
@@ -5031,7 +5048,7 @@
         <v>-64.809905999999998</v>
       </c>
     </row>
-    <row r="192" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="192" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U192" s="1">
         <v>0.51290000000000002</v>
       </c>
@@ -5054,7 +5071,7 @@
         <v>-65.369320000000002</v>
       </c>
     </row>
-    <row r="193" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="193" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U193" s="1">
         <v>0.51877899999999999</v>
       </c>
@@ -5077,7 +5094,7 @@
         <v>-65.843895000000003</v>
       </c>
     </row>
-    <row r="194" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="194" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U194" s="1">
         <v>0.52466400000000002</v>
       </c>
@@ -5100,7 +5117,7 @@
         <v>-66.232950000000002</v>
       </c>
     </row>
-    <row r="195" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="195" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U195" s="1">
         <v>0.53057399999999999</v>
       </c>
@@ -5123,7 +5140,7 @@
         <v>-66.537180000000006</v>
       </c>
     </row>
-    <row r="196" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="196" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U196" s="1">
         <v>0.536528</v>
       </c>
@@ -5146,7 +5163,7 @@
         <v>-66.758849999999995</v>
       </c>
     </row>
-    <row r="197" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="197" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U197" s="1">
         <v>0.542543</v>
       </c>
@@ -5169,7 +5186,7 @@
         <v>-66.903229999999994</v>
       </c>
     </row>
-    <row r="198" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="198" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U198" s="1">
         <v>0.54863300000000004</v>
       </c>
@@ -5192,7 +5209,7 @@
         <v>-66.975623999999996</v>
       </c>
     </row>
-    <row r="199" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="199" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U199" s="1">
         <v>0.554809</v>
       </c>
@@ -5215,7 +5232,7 @@
         <v>-66.985725000000002</v>
       </c>
     </row>
-    <row r="200" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="200" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U200" s="1">
         <v>0.56107799999999997</v>
       </c>
@@ -5238,7 +5255,7 @@
         <v>-66.94265</v>
       </c>
     </row>
-    <row r="201" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="201" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U201" s="1">
         <v>0.56744700000000003</v>
       </c>
@@ -5261,7 +5278,7 @@
         <v>-66.856549999999999</v>
       </c>
     </row>
-    <row r="202" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="202" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U202" s="1">
         <v>0.57392900000000002</v>
       </c>
@@ -5284,7 +5301,7 @@
         <v>-66.739270000000005</v>
       </c>
     </row>
-    <row r="203" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="203" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U203" s="1">
         <v>0.58051299999999995</v>
       </c>
@@ -5307,7 +5324,7 @@
         <v>-66.595290000000006</v>
       </c>
     </row>
-    <row r="204" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="204" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U204" s="1">
         <v>0.58721500000000004</v>
       </c>
@@ -5330,7 +5347,7 @@
         <v>-66.433880000000002</v>
       </c>
     </row>
-    <row r="205" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="205" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U205" s="1">
         <v>0.59403499999999998</v>
       </c>
@@ -5353,7 +5370,7 @@
         <v>-66.261629999999997</v>
       </c>
     </row>
-    <row r="206" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="206" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U206" s="1">
         <v>0.60097699999999998</v>
       </c>
@@ -5376,7 +5393,7 @@
         <v>-66.081599999999995</v>
       </c>
     </row>
-    <row r="207" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="207" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U207" s="1">
         <v>0.60803799999999997</v>
       </c>
@@ -5399,7 +5416,7 @@
         <v>-65.89725</v>
       </c>
     </row>
-    <row r="208" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="208" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U208" s="1">
         <v>0.615232</v>
       </c>
@@ -5422,7 +5439,7 @@
         <v>-65.712329999999994</v>
       </c>
     </row>
-    <row r="209" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="209" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U209" s="1">
         <v>0.62254200000000004</v>
       </c>
@@ -5445,7 +5462,7 @@
         <v>-65.529529999999994</v>
       </c>
     </row>
-    <row r="210" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="210" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U210" s="1">
         <v>0.62998500000000002</v>
       </c>
@@ -5468,7 +5485,7 @@
         <v>-65.35257</v>
       </c>
     </row>
-    <row r="211" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="211" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U211" s="1">
         <v>0.63755799999999996</v>
       </c>
@@ -5491,7 +5508,7 @@
         <v>-65.183555999999996</v>
       </c>
     </row>
-    <row r="212" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="212" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U212" s="1">
         <v>0.64526499999999998</v>
       </c>
@@ -5514,7 +5531,7 @@
         <v>-65.020225999999994</v>
       </c>
     </row>
-    <row r="213" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="213" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U213" s="1">
         <v>0.65310299999999999</v>
       </c>
@@ -5537,7 +5554,7 @@
         <v>-64.864493999999993</v>
       </c>
     </row>
-    <row r="214" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="214" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U214" s="1">
         <v>0.66108199999999995</v>
       </c>
@@ -5560,7 +5577,7 @@
         <v>-64.717730000000003</v>
       </c>
     </row>
-    <row r="215" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="215" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U215" s="1">
         <v>0.66919799999999996</v>
       </c>
@@ -5583,7 +5600,7 @@
         <v>-64.579210000000003</v>
       </c>
     </row>
-    <row r="216" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="216" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U216" s="1">
         <v>0.67745500000000003</v>
       </c>
@@ -5606,7 +5623,7 @@
         <v>-64.447670000000002</v>
       </c>
     </row>
-    <row r="217" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="217" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U217" s="1">
         <v>0.68585700000000005</v>
       </c>
@@ -5629,7 +5646,7 @@
         <v>-64.324479999999994</v>
       </c>
     </row>
-    <row r="218" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="218" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U218" s="1">
         <v>0.694407</v>
       </c>
@@ -5652,7 +5669,7 @@
         <v>-64.210480000000004</v>
       </c>
     </row>
-    <row r="219" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="219" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U219" s="1">
         <v>0.70310799999999996</v>
       </c>
@@ -5675,7 +5692,7 @@
         <v>-64.103679999999997</v>
       </c>
     </row>
-    <row r="220" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="220" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U220" s="1">
         <v>0.71196499999999996</v>
       </c>
@@ -5698,7 +5715,7 @@
         <v>-64.000649999999993</v>
       </c>
     </row>
-    <row r="221" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="221" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U221" s="1">
         <v>0.72097699999999998</v>
       </c>
@@ -5721,7 +5738,7 @@
         <v>-63.899500000000003</v>
       </c>
     </row>
-    <row r="222" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="222" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U222" s="1">
         <v>0.73014900000000005</v>
       </c>
@@ -5744,7 +5761,7 @@
         <v>-63.802498</v>
       </c>
     </row>
-    <row r="223" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="223" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U223" s="1">
         <v>0.73948499999999995</v>
       </c>
@@ -5767,7 +5784,7 @@
         <v>-63.708495999999997</v>
       </c>
     </row>
-    <row r="224" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="224" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U224" s="1">
         <v>0.74898299999999995</v>
       </c>
@@ -5790,7 +5807,7 @@
         <v>-63.615389999999998</v>
       </c>
     </row>
-    <row r="225" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="225" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U225" s="1">
         <v>0.75865700000000003</v>
       </c>
@@ -5813,7 +5830,7 @@
         <v>-63.522185999999998</v>
       </c>
     </row>
-    <row r="226" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="226" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U226" s="1">
         <v>0.76850399999999996</v>
       </c>
@@ -5836,7 +5853,7 @@
         <v>-63.42445</v>
       </c>
     </row>
-    <row r="227" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="227" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U227" s="1">
         <v>0.778532</v>
       </c>
@@ -5859,7 +5876,7 @@
         <v>-63.322009999999999</v>
       </c>
     </row>
-    <row r="228" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="228" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U228" s="1">
         <v>0.78874100000000003</v>
       </c>
@@ -5882,7 +5899,7 @@
         <v>-63.210389999999997</v>
       </c>
     </row>
-    <row r="229" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="229" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U229" s="1">
         <v>0.79913299999999998</v>
       </c>
@@ -5905,7 +5922,7 @@
         <v>-63.088977999999997</v>
       </c>
     </row>
-    <row r="230" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="230" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U230" s="1">
         <v>0.80970600000000004</v>
       </c>
@@ -5928,7 +5945,7 @@
         <v>-62.962240000000001</v>
       </c>
     </row>
-    <row r="231" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="231" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U231" s="1">
         <v>0.820465</v>
       </c>
@@ -5951,7 +5968,7 @@
         <v>-62.834923000000003</v>
       </c>
     </row>
-    <row r="232" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="232" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U232" s="1">
         <v>0.83140700000000001</v>
       </c>
@@ -5974,7 +5991,7 @@
         <v>-62.708378000000003</v>
       </c>
     </row>
-    <row r="233" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="233" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U233" s="1">
         <v>0.84254700000000005</v>
       </c>
@@ -5997,7 +6014,7 @@
         <v>-62.577866</v>
       </c>
     </row>
-    <row r="234" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="234" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U234" s="1">
         <v>0.85387599999999997</v>
       </c>
@@ -6020,7 +6037,7 @@
         <v>-62.439137000000002</v>
       </c>
     </row>
-    <row r="235" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="235" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U235" s="1">
         <v>0.86539500000000003</v>
       </c>
@@ -6043,7 +6060,7 @@
         <v>-62.294249999999998</v>
       </c>
     </row>
-    <row r="236" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="236" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U236" s="1">
         <v>0.877085</v>
       </c>
@@ -6066,7 +6083,7 @@
         <v>-62.155769999999997</v>
       </c>
     </row>
-    <row r="237" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="237" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U237" s="1">
         <v>0.88895000000000002</v>
       </c>
@@ -6089,7 +6106,7 @@
         <v>-62.041170000000001</v>
       </c>
     </row>
-    <row r="238" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="238" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U238" s="1">
         <v>0.90097400000000005</v>
       </c>
@@ -6112,7 +6129,7 @@
         <v>-61.966507</v>
       </c>
     </row>
-    <row r="239" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="239" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U239" s="1">
         <v>0.91315400000000002</v>
       </c>
@@ -6135,7 +6152,7 @@
         <v>-61.944369999999999</v>
       </c>
     </row>
-    <row r="240" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="240" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U240" s="1">
         <v>0.91315400000000002</v>
       </c>
@@ -6158,7 +6175,7 @@
         <v>-61.944369999999999</v>
       </c>
     </row>
-    <row r="241" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="241" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U241" s="1">
         <v>0.92547699999999999</v>
       </c>
@@ -6181,7 +6198,7 @@
         <v>-61.98236</v>
       </c>
     </row>
-    <row r="242" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="242" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U242" s="1">
         <v>0.937944</v>
       </c>
@@ -6204,7 +6221,7 @@
         <v>-62.087730000000001</v>
       </c>
     </row>
-    <row r="243" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="243" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U243" s="1">
         <v>0.95055400000000001</v>
       </c>
@@ -6227,7 +6244,7 @@
         <v>-62.260554999999997</v>
       </c>
     </row>
-    <row r="244" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="244" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U244" s="1">
         <v>0.96330000000000005</v>
       </c>
@@ -6250,7 +6267,7 @@
         <v>-62.496310000000001</v>
       </c>
     </row>
-    <row r="245" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="245" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U245" s="1">
         <v>0.97619199999999995</v>
       </c>
@@ -6273,7 +6290,7 @@
         <v>-62.790219999999998</v>
       </c>
     </row>
-    <row r="246" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="246" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U246" s="1">
         <v>0.98921700000000001</v>
       </c>
@@ -6296,7 +6313,7 @@
         <v>-63.130020000000002</v>
       </c>
     </row>
-    <row r="247" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="247" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U247" s="1">
         <v>1.0023679999999999</v>
       </c>
@@ -6319,7 +6336,7 @@
         <v>-63.52214</v>
       </c>
     </row>
-    <row r="248" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="248" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U248" s="1">
         <v>1.015657</v>
       </c>
@@ -6342,7 +6359,7 @@
         <v>-63.972279999999998</v>
       </c>
     </row>
-    <row r="249" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="249" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U249" s="1">
         <v>1.029061</v>
       </c>
@@ -6365,7 +6382,7 @@
         <v>-64.477670000000003</v>
       </c>
     </row>
-    <row r="250" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="250" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U250" s="1">
         <v>1.042567</v>
       </c>
@@ -6388,7 +6405,7 @@
         <v>-65.055700000000002</v>
       </c>
     </row>
-    <row r="251" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="251" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U251" s="1">
         <v>1.0561780000000001</v>
       </c>
@@ -6411,7 +6428,7 @@
         <v>-65.721959999999996</v>
       </c>
     </row>
-    <row r="252" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="252" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U252" s="1">
         <v>1.069868</v>
       </c>
@@ -6434,7 +6451,7 @@
         <v>-66.481255000000004</v>
       </c>
     </row>
-    <row r="253" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="253" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U253" s="1">
         <v>1.0836250000000001</v>
       </c>
@@ -6457,7 +6474,7 @@
         <v>-67.356290000000001</v>
       </c>
     </row>
-    <row r="254" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="254" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U254" s="1">
         <v>1.0974139999999999</v>
       </c>
@@ -6480,7 +6497,7 @@
         <v>-68.376800000000003</v>
       </c>
     </row>
-    <row r="255" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="255" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U255" s="1">
         <v>1.1112280000000001</v>
       </c>
@@ -6503,7 +6520,7 @@
         <v>-69.567999999999998</v>
       </c>
     </row>
-    <row r="256" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="256" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U256" s="1">
         <v>1.1250260000000001</v>
       </c>
@@ -6526,7 +6543,7 @@
         <v>-70.955830000000006</v>
       </c>
     </row>
-    <row r="257" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="257" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U257" s="1">
         <v>1.1387970000000001</v>
       </c>
@@ -6549,7 +6566,7 @@
         <v>-72.561965999999998</v>
       </c>
     </row>
-    <row r="258" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="258" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U258" s="1">
         <v>1.1525110000000001</v>
       </c>
@@ -6572,7 +6589,7 @@
         <v>-74.397829999999999</v>
       </c>
     </row>
-    <row r="259" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="259" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U259" s="1">
         <v>1.16615</v>
       </c>
@@ -6595,7 +6612,7 @@
         <v>-76.470169999999996</v>
       </c>
     </row>
-    <row r="260" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="260" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U260" s="1">
         <v>1.179675</v>
       </c>
@@ -6618,7 +6635,7 @@
         <v>-78.787734999999998</v>
       </c>
     </row>
-    <row r="261" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="261" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U261" s="1">
         <v>1.1930719999999999</v>
       </c>
@@ -6641,7 +6658,7 @@
         <v>-81.35445</v>
       </c>
     </row>
-    <row r="262" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="262" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U262" s="1">
         <v>1.2063120000000001</v>
       </c>
@@ -6664,7 +6681,7 @@
         <v>-84.164640000000006</v>
       </c>
     </row>
-    <row r="263" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="263" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U263" s="1">
         <v>1.2193909999999999</v>
       </c>
@@ -6687,7 +6704,7 @@
         <v>-87.198325999999994</v>
       </c>
     </row>
-    <row r="264" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="264" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U264" s="1">
         <v>1.2322960000000001</v>
       </c>
@@ -6710,7 +6727,7 @@
         <v>-90.414344999999997</v>
       </c>
     </row>
-    <row r="265" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="265" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U265" s="1">
         <v>1.2450349999999999</v>
       </c>
@@ -6733,7 +6750,7 @@
         <v>-93.754906000000005</v>
       </c>
     </row>
-    <row r="266" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="266" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U266" s="1">
         <v>1.2576080000000001</v>
       </c>
@@ -6756,7 +6773,7 @@
         <v>-97.156750000000002</v>
       </c>
     </row>
-    <row r="267" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="267" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U267" s="1">
         <v>1.270044</v>
       </c>
@@ -6779,7 +6796,7 @@
         <v>-100.54484600000001</v>
       </c>
     </row>
-    <row r="268" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="268" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U268" s="1">
         <v>1.282359</v>
       </c>
@@ -6802,7 +6819,7 @@
         <v>-103.83505</v>
       </c>
     </row>
-    <row r="269" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="269" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U269" s="1">
         <v>1.2945709999999999</v>
       </c>
@@ -6825,7 +6842,7 @@
         <v>-106.95927</v>
       </c>
     </row>
-    <row r="270" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="270" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U270" s="1">
         <v>1.3067219999999999</v>
       </c>
@@ -6848,7 +6865,7 @@
         <v>-109.86393</v>
       </c>
     </row>
-    <row r="271" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="271" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U271" s="1">
         <v>1.3188519999999999</v>
       </c>
@@ -6871,7 +6888,7 @@
         <v>-112.48354</v>
       </c>
     </row>
-    <row r="272" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="272" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U272" s="1">
         <v>1.3309850000000001</v>
       </c>
@@ -6894,7 +6911,7 @@
         <v>-114.76264</v>
       </c>
     </row>
-    <row r="273" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="273" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U273" s="1">
         <v>1.343145</v>
       </c>
@@ -6917,7 +6934,7 @@
         <v>-116.67896</v>
       </c>
     </row>
-    <row r="274" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="274" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U274" s="1">
         <v>1.3553580000000001</v>
       </c>
@@ -6940,7 +6957,7 @@
         <v>-118.23151</v>
       </c>
     </row>
-    <row r="275" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="275" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U275" s="1">
         <v>1.367634</v>
       </c>
@@ -6963,7 +6980,7 @@
         <v>-119.43397</v>
       </c>
     </row>
-    <row r="276" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="276" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U276" s="1">
         <v>1.3799710000000001</v>
       </c>
@@ -6986,7 +7003,7 @@
         <v>-120.32277000000001</v>
       </c>
     </row>
-    <row r="277" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="277" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U277" s="1">
         <v>1.392366</v>
       </c>
@@ -7009,7 +7026,7 @@
         <v>-120.95222</v>
       </c>
     </row>
-    <row r="278" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="278" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U278" s="1">
         <v>1.404822</v>
       </c>
@@ -7032,7 +7049,7 @@
         <v>-121.36874</v>
       </c>
     </row>
-    <row r="279" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="279" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U279" s="1">
         <v>1.4173210000000001</v>
       </c>
@@ -7055,7 +7072,7 @@
         <v>-121.61515</v>
       </c>
     </row>
-    <row r="280" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="280" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U280" s="1">
         <v>1.429867</v>
       </c>
@@ -7078,7 +7095,7 @@
         <v>-121.74253</v>
       </c>
     </row>
-    <row r="281" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="281" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U281" s="1">
         <v>1.4424360000000001</v>
       </c>
@@ -7101,7 +7118,7 @@
         <v>-121.782776</v>
       </c>
     </row>
-    <row r="282" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="282" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U282" s="1">
         <v>1.4550099999999999</v>
       </c>
@@ -7124,7 +7141,7 @@
         <v>-121.77585000000001</v>
       </c>
     </row>
-    <row r="283" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="283" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U283" s="1">
         <v>1.467563</v>
       </c>
@@ -7147,7 +7164,7 @@
         <v>-121.776855</v>
       </c>
     </row>
-    <row r="284" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="284" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U284" s="1">
         <v>1.4800800000000001</v>
       </c>
@@ -7170,7 +7187,7 @@
         <v>-121.82532999999999</v>
       </c>
     </row>
-    <row r="285" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="285" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U285" s="1">
         <v>1.4925280000000001</v>
       </c>
@@ -7193,7 +7210,7 @@
         <v>-121.95308</v>
       </c>
     </row>
-    <row r="286" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="286" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U286" s="1">
         <v>1.504896</v>
       </c>
@@ -7216,7 +7233,7 @@
         <v>-122.19007000000001</v>
       </c>
     </row>
-    <row r="287" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="287" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U287" s="1">
         <v>1.5171600000000001</v>
       </c>
@@ -7239,7 +7256,7 @@
         <v>-122.54978</v>
       </c>
     </row>
-    <row r="288" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="288" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U288" s="1">
         <v>1.5293099999999999</v>
       </c>
@@ -7262,7 +7279,7 @@
         <v>-123.0278</v>
       </c>
     </row>
-    <row r="289" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="289" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U289" s="1">
         <v>1.5413250000000001</v>
       </c>
@@ -7285,7 +7302,7 @@
         <v>-123.621925</v>
       </c>
     </row>
-    <row r="290" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="290" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U290" s="1">
         <v>1.5532189999999999</v>
       </c>
@@ -7308,7 +7325,7 @@
         <v>-124.31753999999999</v>
       </c>
     </row>
-    <row r="291" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="291" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U291" s="1">
         <v>1.564988</v>
       </c>
@@ -7331,7 +7348,7 @@
         <v>-125.078705</v>
       </c>
     </row>
-    <row r="292" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="292" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U292" s="1">
         <v>1.576662</v>
       </c>
@@ -7354,7 +7371,7 @@
         <v>-125.85575</v>
       </c>
     </row>
-    <row r="293" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="293" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U293" s="1">
         <v>1.588273</v>
       </c>
@@ -7377,7 +7394,7 @@
         <v>-126.5843</v>
       </c>
     </row>
-    <row r="294" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="294" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U294" s="1">
         <v>1.5998650000000001</v>
       </c>
@@ -7400,7 +7417,7 @@
         <v>-127.19208500000001</v>
       </c>
     </row>
-    <row r="295" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="295" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U295" s="1">
         <v>1.611496</v>
       </c>
@@ -7423,7 +7440,7 @@
         <v>-127.60164</v>
       </c>
     </row>
-    <row r="296" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="296" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U296" s="1">
         <v>1.6232009999999999</v>
       </c>
@@ -7446,7 +7463,7 @@
         <v>-127.74751999999999</v>
       </c>
     </row>
-    <row r="297" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="297" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U297" s="1">
         <v>1.6350260000000001</v>
       </c>
@@ -7469,7 +7486,7 @@
         <v>-127.59350000000001</v>
       </c>
     </row>
-    <row r="298" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="298" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U298" s="1">
         <v>1.6469929999999999</v>
       </c>
@@ -7492,7 +7509,7 @@
         <v>-127.12273999999999</v>
       </c>
     </row>
-    <row r="299" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="299" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U299" s="1">
         <v>1.659122</v>
       </c>
@@ -7515,7 +7532,7 @@
         <v>-126.34961</v>
       </c>
     </row>
-    <row r="300" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="300" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U300" s="1">
         <v>1.6714230000000001</v>
       </c>
@@ -7538,7 +7555,7 @@
         <v>-125.30871</v>
       </c>
     </row>
-    <row r="301" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="301" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U301" s="1">
         <v>1.68391</v>
       </c>
@@ -7561,7 +7578,7 @@
         <v>-124.039154</v>
       </c>
     </row>
-    <row r="302" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="302" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U302" s="1">
         <v>1.6965760000000001</v>
       </c>
@@ -7584,7 +7601,7 @@
         <v>-122.58333</v>
       </c>
     </row>
-    <row r="303" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="303" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U303" s="1">
         <v>1.7094529999999999</v>
       </c>
@@ -7607,7 +7624,7 @@
         <v>-120.97055</v>
       </c>
     </row>
-    <row r="304" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="304" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U304" s="1">
         <v>1.7225299999999999</v>
       </c>
@@ -7630,7 +7647,7 @@
         <v>-119.215996</v>
       </c>
     </row>
-    <row r="305" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="305" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U305" s="1">
         <v>1.7358260000000001</v>
       </c>
@@ -7653,7 +7670,7 @@
         <v>-117.34018</v>
       </c>
     </row>
-    <row r="306" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="306" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U306" s="1">
         <v>1.749328</v>
       </c>
@@ -7676,7 +7693,7 @@
         <v>-115.36299</v>
       </c>
     </row>
-    <row r="307" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="307" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U307" s="1">
         <v>1.763037</v>
       </c>
@@ -7699,7 +7716,7 @@
         <v>-113.30888</v>
       </c>
     </row>
-    <row r="308" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="308" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U308" s="1">
         <v>1.776939</v>
       </c>
@@ -7722,7 +7739,7 @@
         <v>-111.215164</v>
       </c>
     </row>
-    <row r="309" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="309" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U309" s="1">
         <v>1.7910250000000001</v>
       </c>
@@ -7745,7 +7762,7 @@
         <v>-109.12452999999999</v>
       </c>
     </row>
-    <row r="310" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="310" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U310" s="1">
         <v>1.8052699999999999</v>
       </c>
@@ -7768,7 +7785,7 @@
         <v>-107.07518</v>
       </c>
     </row>
-    <row r="311" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="311" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U311" s="1">
         <v>1.8196730000000001</v>
       </c>
@@ -7791,7 +7808,7 @@
         <v>-105.10456000000001</v>
       </c>
     </row>
-    <row r="312" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="312" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U312" s="1">
         <v>1.834203</v>
       </c>
@@ -7814,7 +7831,7 @@
         <v>-103.248695</v>
       </c>
     </row>
-    <row r="313" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="313" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U313" s="1">
         <v>1.8488420000000001</v>
       </c>
@@ -7837,7 +7854,7 @@
         <v>-101.543594</v>
       </c>
     </row>
-    <row r="314" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="314" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U314" s="1">
         <v>1.863561</v>
       </c>
@@ -7860,7 +7877,7 @@
         <v>-100.033485</v>
       </c>
     </row>
-    <row r="315" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="315" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U315" s="1">
         <v>1.87832</v>
       </c>
@@ -7883,7 +7900,7 @@
         <v>-98.768196000000003</v>
       </c>
     </row>
-    <row r="316" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="316" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U316" s="1">
         <v>1.8930929999999999</v>
       </c>
@@ -7906,7 +7923,7 @@
         <v>-97.803250000000006</v>
       </c>
     </row>
-    <row r="317" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="317" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U317" s="1">
         <v>1.9078459999999999</v>
       </c>
@@ -7929,7 +7946,7 @@
         <v>-97.178830000000005</v>
       </c>
     </row>
-    <row r="318" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="318" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U318" s="1">
         <v>1.9225559999999999</v>
       </c>
@@ -7952,7 +7969,7 @@
         <v>-96.921524000000005</v>
       </c>
     </row>
-    <row r="319" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="319" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U319" s="1">
         <v>1.937192</v>
       </c>
@@ -7975,7 +7992,7 @@
         <v>-97.047659999999993</v>
       </c>
     </row>
-    <row r="320" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="320" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U320" s="1">
         <v>1.9517180000000001</v>
       </c>
@@ -7998,7 +8015,7 @@
         <v>-97.569275000000005</v>
       </c>
     </row>
-    <row r="321" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="321" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U321" s="1">
         <v>1.966107</v>
       </c>
@@ -8021,7 +8038,7 @@
         <v>-98.497116000000005</v>
       </c>
     </row>
-    <row r="322" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="322" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U322" s="1">
         <v>1.9803280000000001</v>
       </c>
@@ -8044,7 +8061,7 @@
         <v>-99.834175000000002</v>
       </c>
     </row>
-    <row r="323" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="323" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U323" s="1">
         <v>1.9943470000000001</v>
       </c>
@@ -8067,7 +8084,7 @@
         <v>-101.57755</v>
       </c>
     </row>
-    <row r="324" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="324" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U324" s="1">
         <v>2.008168</v>
       </c>
@@ -8090,7 +8107,7 @@
         <v>-103.69694</v>
       </c>
     </row>
-    <row r="325" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="325" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U325" s="1">
         <v>2.0217610000000001</v>
       </c>
@@ -8113,7 +8130,7 @@
         <v>-106.13637</v>
       </c>
     </row>
-    <row r="326" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="326" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U326" s="1">
         <v>2.0351210000000002</v>
       </c>
@@ -8136,7 +8153,7 @@
         <v>-108.84399999999999</v>
       </c>
     </row>
-    <row r="327" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="327" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U327" s="1">
         <v>2.0482399999999998</v>
       </c>
@@ -8159,7 +8176,7 @@
         <v>-111.757355</v>
       </c>
     </row>
-    <row r="328" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="328" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U328" s="1">
         <v>2.0611350000000002</v>
       </c>
@@ -8182,7 +8199,7 @@
         <v>-114.79787</v>
       </c>
     </row>
-    <row r="329" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="329" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U329" s="1">
         <v>2.0738089999999998</v>
       </c>
@@ -8205,7 +8222,7 @@
         <v>-117.88111000000001</v>
       </c>
     </row>
-    <row r="330" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="330" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U330" s="1">
         <v>2.0862959999999999</v>
       </c>
@@ -8228,7 +8245,7 @@
         <v>-120.918724</v>
       </c>
     </row>
-    <row r="331" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="331" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U331" s="1">
         <v>2.0986199999999999</v>
       </c>
@@ -8251,7 +8268,7 @@
         <v>-123.81318</v>
       </c>
     </row>
-    <row r="332" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="332" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U332" s="1">
         <v>2.1108259999999999</v>
       </c>
@@ -8274,7 +8291,7 @@
         <v>-126.47112</v>
       </c>
     </row>
-    <row r="333" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="333" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U333" s="1">
         <v>2.1229360000000002</v>
       </c>
@@ -8297,7 +8314,7 @@
         <v>-128.82341</v>
       </c>
     </row>
-    <row r="334" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="334" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U334" s="1">
         <v>2.1349879999999999</v>
       </c>
@@ -8320,7 +8337,7 @@
         <v>-130.82695000000001</v>
       </c>
     </row>
-    <row r="335" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="335" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U335" s="1">
         <v>2.1470039999999999</v>
       </c>
@@ -8343,7 +8360,7 @@
         <v>-132.45529999999999</v>
       </c>
     </row>
-    <row r="336" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="336" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U336" s="1">
         <v>2.159014</v>
       </c>
@@ -8366,7 +8383,7 @@
         <v>-133.70132000000001</v>
       </c>
     </row>
-    <row r="337" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="337" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U337" s="1">
         <v>2.1710319999999999</v>
       </c>
@@ -8389,7 +8406,7 @@
         <v>-134.69589999999999</v>
       </c>
     </row>
-    <row r="338" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="338" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U338" s="1">
         <v>2.1830820000000002</v>
       </c>
@@ -8412,7 +8429,7 @@
         <v>-135.56432000000001</v>
       </c>
     </row>
-    <row r="339" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="339" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U339" s="1">
         <v>2.1951999999999998</v>
       </c>
@@ -8435,7 +8452,7 @@
         <v>-136.25264000000001</v>
       </c>
     </row>
-    <row r="340" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="340" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U340" s="1">
         <v>2.2073960000000001</v>
       </c>
@@ -8458,7 +8475,7 @@
         <v>-136.66745</v>
       </c>
     </row>
-    <row r="341" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="341" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U341" s="1">
         <v>2.2196910000000001</v>
       </c>
@@ -8481,7 +8498,7 @@
         <v>-136.75174000000001</v>
       </c>
     </row>
-    <row r="342" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="342" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U342" s="1">
         <v>2.2320869999999999</v>
       </c>
@@ -8504,7 +8521,7 @@
         <v>-136.47539</v>
       </c>
     </row>
-    <row r="343" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="343" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U343" s="1">
         <v>2.2445919999999999</v>
       </c>
@@ -8527,7 +8544,7 @@
         <v>-135.81630000000001</v>
       </c>
     </row>
-    <row r="344" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="344" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U344" s="1">
         <v>2.25719</v>
       </c>
@@ -8550,7 +8567,7 @@
         <v>-134.75960000000001</v>
       </c>
     </row>
-    <row r="345" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="345" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U345" s="1">
         <v>2.2698839999999998</v>
       </c>
@@ -8573,7 +8590,7 @@
         <v>-133.37172000000001</v>
       </c>
     </row>
-    <row r="346" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="346" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U346" s="1">
         <v>2.2826490000000002</v>
       </c>
@@ -8596,7 +8613,7 @@
         <v>-131.8365</v>
       </c>
     </row>
-    <row r="347" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="347" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U347" s="1">
         <v>2.295506</v>
       </c>
@@ -8619,7 +8636,7 @@
         <v>-130.28447</v>
       </c>
     </row>
-    <row r="348" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="348" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U348" s="1">
         <v>2.3084199999999999</v>
       </c>
@@ -8642,7 +8659,7 @@
         <v>-128.73346000000001</v>
       </c>
     </row>
-    <row r="349" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="349" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U349" s="1">
         <v>2.3214009999999998</v>
       </c>
@@ -8665,7 +8682,7 @@
         <v>-127.21359</v>
       </c>
     </row>
-    <row r="350" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="350" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U350" s="1">
         <v>2.3344279999999999</v>
       </c>
@@ -8688,7 +8705,7 @@
         <v>-125.74947</v>
       </c>
     </row>
-    <row r="351" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="351" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U351" s="1">
         <v>2.3475060000000001</v>
       </c>
@@ -8711,7 +8728,7 @@
         <v>-124.35093999999999</v>
       </c>
     </row>
-    <row r="352" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="352" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U352" s="1">
         <v>2.3606199999999999</v>
       </c>
@@ -8734,7 +8751,7 @@
         <v>-123.03342000000001</v>
       </c>
     </row>
-    <row r="353" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="353" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U353" s="1">
         <v>2.373767</v>
       </c>
@@ -8757,7 +8774,7 @@
         <v>-121.8052</v>
       </c>
     </row>
-    <row r="354" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="354" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U354" s="1">
         <v>2.386946</v>
       </c>
@@ -8780,7 +8797,7 @@
         <v>-120.66926599999999</v>
       </c>
     </row>
-    <row r="355" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="355" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U355" s="1">
         <v>2.4001510000000001</v>
       </c>
@@ -8803,7 +8820,7 @@
         <v>-119.623116</v>
       </c>
     </row>
-    <row r="356" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="356" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U356" s="1">
         <v>2.4133599999999999</v>
       </c>
@@ -8826,7 +8843,7 @@
         <v>-118.67804</v>
       </c>
     </row>
-    <row r="357" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="357" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U357" s="1">
         <v>2.4265810000000001</v>
       </c>
@@ -8849,7 +8866,7 @@
         <v>-117.846504</v>
       </c>
     </row>
-    <row r="358" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="358" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U358" s="1">
         <v>2.4397859999999998</v>
       </c>
@@ -8872,7 +8889,7 @@
         <v>-117.13347</v>
       </c>
     </row>
-    <row r="359" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="359" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U359" s="1">
         <v>2.4529589999999999</v>
       </c>
@@ -8895,7 +8912,7 @@
         <v>-116.56111</v>
       </c>
     </row>
-    <row r="360" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="360" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U360" s="1">
         <v>2.4661</v>
       </c>
@@ -8918,7 +8935,7 @@
         <v>-116.14485000000001</v>
       </c>
     </row>
-    <row r="361" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="361" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U361" s="1">
         <v>2.4791919999999998</v>
       </c>
@@ -8941,7 +8958,7 @@
         <v>-115.87651</v>
       </c>
     </row>
-    <row r="362" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="362" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U362" s="1">
         <v>2.492235</v>
       </c>
@@ -8964,7 +8981,7 @@
         <v>-115.7508</v>
       </c>
     </row>
-    <row r="363" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="363" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U363" s="1">
         <v>2.5052340000000002</v>
       </c>
@@ -8987,7 +9004,7 @@
         <v>-115.75147</v>
       </c>
     </row>
-    <row r="364" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="364" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U364" s="1">
         <v>2.5181979999999999</v>
       </c>
@@ -9010,7 +9027,7 @@
         <v>-115.84093</v>
       </c>
     </row>
-    <row r="365" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="365" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U365" s="1">
         <v>2.5311349999999999</v>
       </c>
@@ -9033,7 +9050,7 @@
         <v>-115.982635</v>
       </c>
     </row>
-    <row r="366" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="366" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U366" s="1">
         <v>2.5440520000000002</v>
       </c>
@@ -9056,7 +9073,7 @@
         <v>-116.14348</v>
       </c>
     </row>
-    <row r="367" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="367" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U367" s="1">
         <v>2.5569670000000002</v>
       </c>
@@ -9079,7 +9096,7 @@
         <v>-116.29516</v>
       </c>
     </row>
-    <row r="368" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="368" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U368" s="1">
         <v>2.5698859999999999</v>
       </c>
@@ -9102,7 +9119,7 @@
         <v>-116.41314</v>
       </c>
     </row>
-    <row r="369" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="369" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U369" s="1">
         <v>2.5828280000000001</v>
       </c>
@@ -9125,7 +9142,7 @@
         <v>-116.47299</v>
       </c>
     </row>
-    <row r="370" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="370" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U370" s="1">
         <v>2.5958169999999998</v>
       </c>
@@ -9148,7 +9165,7 @@
         <v>-116.45189000000001</v>
       </c>
     </row>
-    <row r="371" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="371" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U371" s="1">
         <v>2.6088580000000001</v>
       </c>
@@ -9171,7 +9188,7 @@
         <v>-116.32295000000001</v>
       </c>
     </row>
-    <row r="372" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="372" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U372" s="1">
         <v>2.6219709999999998</v>
       </c>
@@ -9194,7 +9211,7 @@
         <v>-116.07689999999999</v>
       </c>
     </row>
-    <row r="373" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="373" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U373" s="1">
         <v>2.6351589999999998</v>
       </c>
@@ -9217,7 +9234,7 @@
         <v>-115.71241999999999</v>
       </c>
     </row>
-    <row r="374" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="374" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U374" s="1">
         <v>2.6484700000000001</v>
       </c>
@@ -9240,7 +9257,7 @@
         <v>-115.2182</v>
       </c>
     </row>
-    <row r="375" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="375" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U375" s="1">
         <v>2.6618889999999999</v>
       </c>
@@ -9263,7 +9280,7 @@
         <v>-114.5762</v>
       </c>
     </row>
-    <row r="376" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="376" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U376" s="1">
         <v>2.6754540000000002</v>
       </c>
@@ -9286,7 +9303,7 @@
         <v>-113.78268</v>
       </c>
     </row>
-    <row r="377" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="377" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U377" s="1">
         <v>2.6891620000000001</v>
       </c>
@@ -9309,7 +9326,7 @@
         <v>-112.83994</v>
       </c>
     </row>
-    <row r="378" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="378" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U378" s="1">
         <v>2.7030319999999999</v>
       </c>
@@ -9332,7 +9349,7 @@
         <v>-111.75372</v>
       </c>
     </row>
-    <row r="379" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="379" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U379" s="1">
         <v>2.717066</v>
       </c>
@@ -9355,7 +9372,7 @@
         <v>-110.537384</v>
       </c>
     </row>
-    <row r="380" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="380" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U380" s="1">
         <v>2.7312609999999999</v>
       </c>
@@ -9378,7 +9395,7 @@
         <v>-109.20972999999999</v>
       </c>
     </row>
-    <row r="381" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="381" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U381" s="1">
         <v>2.7456100000000001</v>
       </c>
@@ -9401,7 +9418,7 @@
         <v>-107.80506</v>
       </c>
     </row>
-    <row r="382" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="382" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U382" s="1">
         <v>2.760113</v>
       </c>
@@ -9424,7 +9441,7 @@
         <v>-106.3574</v>
       </c>
     </row>
-    <row r="383" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="383" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U383" s="1">
         <v>2.774753</v>
       </c>
@@ -9447,7 +9464,7 @@
         <v>-104.8999</v>
       </c>
     </row>
-    <row r="384" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="384" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U384" s="1">
         <v>2.7895189999999999</v>
       </c>
@@ -9470,7 +9487,7 @@
         <v>-103.47078</v>
       </c>
     </row>
-    <row r="385" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="385" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U385" s="1">
         <v>2.8043819999999999</v>
       </c>
@@ -9493,7 +9510,7 @@
         <v>-102.11926</v>
       </c>
     </row>
-    <row r="386" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="386" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U386" s="1">
         <v>2.8193320000000002</v>
       </c>
@@ -9516,7 +9533,7 @@
         <v>-100.89288999999999</v>
       </c>
     </row>
-    <row r="387" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="387" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U387" s="1">
         <v>2.8343280000000002</v>
       </c>
@@ -9539,7 +9556,7 @@
         <v>-99.838393999999994</v>
       </c>
     </row>
-    <row r="388" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="388" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U388" s="1">
         <v>2.8493469999999999</v>
       </c>
@@ -9562,7 +9579,7 @@
         <v>-99.01464</v>
       </c>
     </row>
-    <row r="389" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="389" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U389" s="1">
         <v>2.8643619999999999</v>
       </c>
@@ -9585,7 +9602,7 @@
         <v>-98.463239999999999</v>
       </c>
     </row>
-    <row r="390" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="390" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U390" s="1">
         <v>2.879359</v>
       </c>
@@ -9608,7 +9625,7 @@
         <v>-98.202834999999993</v>
       </c>
     </row>
-    <row r="391" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="391" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U391" s="1">
         <v>2.8943059999999998</v>
       </c>
@@ -9631,7 +9648,7 @@
         <v>-98.250916000000004</v>
       </c>
     </row>
-    <row r="392" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="392" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U392" s="1">
         <v>2.909176</v>
       </c>
@@ -9654,7 +9671,7 @@
         <v>-98.620540000000005</v>
       </c>
     </row>
-    <row r="393" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="393" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U393" s="1">
         <v>2.923943</v>
       </c>
@@ -9677,7 +9694,7 @@
         <v>-99.324460000000002</v>
       </c>
     </row>
-    <row r="394" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="394" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U394" s="1">
         <v>2.9385949999999998</v>
       </c>
@@ -9700,7 +9717,7 @@
         <v>-100.37153000000001</v>
       </c>
     </row>
-    <row r="395" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="395" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U395" s="1">
         <v>2.9531130000000001</v>
       </c>
@@ -9723,7 +9740,7 @@
         <v>-101.73959000000001</v>
       </c>
     </row>
-    <row r="396" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="396" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U396" s="1">
         <v>2.9674809999999998</v>
       </c>
@@ -9746,7 +9763,7 @@
         <v>-103.39604</v>
       </c>
     </row>
-    <row r="397" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="397" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U397" s="1">
         <v>2.9816940000000001</v>
       </c>
@@ -9769,7 +9786,7 @@
         <v>-105.31308</v>
       </c>
     </row>
-    <row r="398" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="398" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U398" s="1">
         <v>2.9957289999999999</v>
       </c>
@@ -9792,7 +9809,7 @@
         <v>-107.45528</v>
       </c>
     </row>
-    <row r="399" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="399" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U399" s="1">
         <v>3.0095740000000002</v>
       </c>
@@ -9815,7 +9832,7 @@
         <v>-109.79645499999999</v>
       </c>
     </row>
-    <row r="400" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="400" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U400" s="1">
         <v>3.023196</v>
       </c>
@@ -9838,7 +9855,7 @@
         <v>-112.32223</v>
       </c>
     </row>
-    <row r="401" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="401" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U401" s="1">
         <v>3.0365829999999998</v>
       </c>
@@ -9861,7 +9878,7 @@
         <v>-115.02067599999999</v>
       </c>
     </row>
-    <row r="402" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="402" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U402" s="1">
         <v>3.049709</v>
       </c>
@@ -9884,7 +9901,7 @@
         <v>-117.87527</v>
       </c>
     </row>
-    <row r="403" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="403" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U403" s="1">
         <v>3.062567</v>
       </c>
@@ -9907,7 +9924,7 @@
         <v>-120.86384</v>
       </c>
     </row>
-    <row r="404" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="404" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U404" s="1">
         <v>3.075151</v>
       </c>
@@ -9930,7 +9947,7 @@
         <v>-123.93850999999999</v>
       </c>
     </row>
-    <row r="405" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="405" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U405" s="1">
         <v>3.0874760000000001</v>
       </c>
@@ -9953,7 +9970,7 @@
         <v>-127.0265</v>
       </c>
     </row>
-    <row r="406" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="406" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U406" s="1">
         <v>3.099564</v>
       </c>
@@ -9976,7 +9993,7 @@
         <v>-130.17635000000001</v>
       </c>
     </row>
-    <row r="407" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="407" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U407" s="1">
         <v>3.111469</v>
       </c>
@@ -9999,7 +10016,7 @@
         <v>-133.68893</v>
       </c>
     </row>
-    <row r="408" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="408" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U408" s="1">
         <v>3.123243</v>
       </c>
@@ -10022,7 +10039,7 @@
         <v>-137.67537999999999</v>
       </c>
     </row>
-    <row r="409" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="409" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U409" s="1">
         <v>3.1349490000000002</v>
       </c>
@@ -10045,7 +10062,7 @@
         <v>-141.93477999999999</v>
       </c>
     </row>
-    <row r="410" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="410" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U410" s="1">
         <v>3.1466440000000002</v>
       </c>
@@ -10068,7 +10085,7 @@
         <v>-146.26102</v>
       </c>
     </row>
-    <row r="411" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="411" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U411" s="1">
         <v>3.1583909999999999</v>
       </c>
@@ -10091,7 +10108,7 @@
         <v>-150.44399999999999</v>
       </c>
     </row>
-    <row r="412" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="412" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U412" s="1">
         <v>3.17021</v>
       </c>
@@ -10114,7 +10131,7 @@
         <v>-154.28963999999999</v>
       </c>
     </row>
-    <row r="413" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="413" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U413" s="1">
         <v>3.1821389999999998</v>
       </c>
@@ -10137,7 +10154,7 @@
         <v>-157.63968</v>
       </c>
     </row>
-    <row r="414" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="414" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U414" s="1">
         <v>3.1941839999999999</v>
       </c>
@@ -10160,7 +10177,7 @@
         <v>-160.37121999999999</v>
       </c>
     </row>
-    <row r="415" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="415" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U415" s="1">
         <v>3.2063619999999999</v>
       </c>
@@ -10183,7 +10200,7 @@
         <v>-162.39411999999999</v>
       </c>
     </row>
-    <row r="416" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="416" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U416" s="1">
         <v>3.2186699999999999</v>
       </c>
@@ -10206,7 +10223,7 @@
         <v>-163.66679999999999</v>
       </c>
     </row>
-    <row r="417" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="417" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U417" s="1">
         <v>3.231109</v>
       </c>
@@ -10229,7 +10246,7 @@
         <v>-164.19159999999999</v>
       </c>
     </row>
-    <row r="418" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="418" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U418" s="1">
         <v>3.2436699999999998</v>
       </c>
@@ -10252,7 +10269,7 @@
         <v>-164.00984</v>
       </c>
     </row>
-    <row r="419" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="419" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U419" s="1">
         <v>3.2563460000000002</v>
       </c>
@@ -10275,7 +10292,7 @@
         <v>-163.18567999999999</v>
       </c>
     </row>
-    <row r="420" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="420" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U420" s="1">
         <v>3.269139</v>
       </c>
@@ -10298,7 +10315,7 @@
         <v>-161.78423000000001</v>
       </c>
     </row>
-    <row r="421" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="421" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U421" s="1">
         <v>3.282035</v>
       </c>
@@ -10321,7 +10338,7 @@
         <v>-159.87582</v>
       </c>
     </row>
-    <row r="422" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="422" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U422" s="1">
         <v>3.2950309999999998</v>
       </c>
@@ -10344,7 +10361,7 @@
         <v>-157.53996000000001</v>
       </c>
     </row>
-    <row r="423" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="423" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U423" s="1">
         <v>3.3081079999999998</v>
       </c>
@@ -10367,7 +10384,7 @@
         <v>-154.86287999999999</v>
       </c>
     </row>
-    <row r="424" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="424" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U424" s="1">
         <v>3.3212670000000002</v>
       </c>
@@ -10390,7 +10407,7 @@
         <v>-151.9239</v>
       </c>
     </row>
-    <row r="425" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="425" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U425" s="1">
         <v>3.334473</v>
       </c>
@@ -10413,7 +10430,7 @@
         <v>-148.78899999999999</v>
       </c>
     </row>
-    <row r="426" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="426" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U426" s="1">
         <v>3.3477199999999998</v>
       </c>
@@ -10436,7 +10453,7 @@
         <v>-145.53816</v>
       </c>
     </row>
-    <row r="427" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="427" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U427" s="1">
         <v>3.360976</v>
       </c>
@@ -10459,7 +10476,7 @@
         <v>-142.32355999999999</v>
       </c>
     </row>
-    <row r="428" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="428" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U428" s="1">
         <v>3.3742329999999998</v>
       </c>
@@ -10482,7 +10499,7 @@
         <v>-139.33641</v>
       </c>
     </row>
-    <row r="429" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="429" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U429" s="1">
         <v>3.3874559999999998</v>
       </c>
@@ -10505,7 +10522,7 @@
         <v>-136.66633999999999</v>
       </c>
     </row>
-    <row r="430" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="430" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U430" s="1">
         <v>3.4006439999999998</v>
       </c>
@@ -10528,7 +10545,7 @@
         <v>-134.32138</v>
       </c>
     </row>
-    <row r="431" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="431" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U431" s="1">
         <v>3.4137650000000002</v>
       </c>
@@ -10551,7 +10568,7 @@
         <v>-132.29881</v>
       </c>
     </row>
-    <row r="432" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="432" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U432" s="1">
         <v>3.4268049999999999</v>
       </c>
@@ -10574,7 +10591,7 @@
         <v>-130.59900999999999</v>
       </c>
     </row>
-    <row r="433" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="433" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U433" s="1">
         <v>3.439737</v>
       </c>
@@ -10597,7 +10614,7 @@
         <v>-129.22394</v>
       </c>
     </row>
-    <row r="434" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="434" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U434" s="1">
         <v>3.4525640000000002</v>
       </c>
@@ -10620,7 +10637,7 @@
         <v>-128.16401999999999</v>
       </c>
     </row>
-    <row r="435" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="435" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U435" s="1">
         <v>3.465265</v>
       </c>
@@ -10643,7 +10660,7 @@
         <v>-127.39433</v>
       </c>
     </row>
-    <row r="436" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="436" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U436" s="1">
         <v>3.47783</v>
       </c>
@@ -10666,7 +10683,7 @@
         <v>-126.88549999999999</v>
       </c>
     </row>
-    <row r="437" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="437" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U437" s="1">
         <v>3.4902500000000001</v>
       </c>
@@ -10689,7 +10706,7 @@
         <v>-126.67122000000001</v>
       </c>
     </row>
-    <row r="438" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="438" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U438" s="1">
         <v>3.5025200000000001</v>
       </c>
@@ -10712,7 +10729,7 @@
         <v>-126.88303000000001</v>
       </c>
     </row>
-    <row r="439" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="439" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U439" s="1">
         <v>3.5146449999999998</v>
       </c>
@@ -10735,7 +10752,7 @@
         <v>-127.57979</v>
       </c>
     </row>
-    <row r="440" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="440" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U440" s="1">
         <v>3.526627</v>
       </c>
@@ -10758,7 +10775,7 @@
         <v>-128.71728999999999</v>
       </c>
     </row>
-    <row r="441" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="441" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U441" s="1">
         <v>3.5384899999999999</v>
       </c>
@@ -10781,7 +10798,7 @@
         <v>-130.24744000000001</v>
       </c>
     </row>
-    <row r="442" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="442" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U442" s="1">
         <v>3.5502419999999999</v>
       </c>
@@ -10804,7 +10821,7 @@
         <v>-132.09829999999999</v>
       </c>
     </row>
-    <row r="443" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="443" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U443" s="1">
         <v>3.5619170000000002</v>
       </c>
@@ -10827,7 +10844,7 @@
         <v>-134.19322</v>
       </c>
     </row>
-    <row r="444" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="444" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U444" s="1">
         <v>3.5735169999999998</v>
       </c>
@@ -10850,7 +10867,7 @@
         <v>-136.44717</v>
       </c>
     </row>
-    <row r="445" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="445" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U445" s="1">
         <v>3.5850360000000001</v>
       </c>
@@ -10873,7 +10890,7 @@
         <v>-138.78645</v>
       </c>
     </row>
-    <row r="446" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="446" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U446" s="1">
         <v>3.5964520000000002</v>
       </c>
@@ -10896,7 +10913,7 @@
         <v>-141.17184</v>
       </c>
     </row>
-    <row r="447" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="447" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U447" s="1">
         <v>3.6077430000000001</v>
       </c>
@@ -10919,7 +10936,7 @@
         <v>-143.57198</v>
       </c>
     </row>
-    <row r="448" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="448" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U448" s="1">
         <v>3.6188790000000002</v>
       </c>
@@ -10942,7 +10959,7 @@
         <v>-145.96396999999999</v>
       </c>
     </row>
-    <row r="449" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="449" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U449" s="1">
         <v>3.6298530000000002</v>
       </c>
@@ -10965,7 +10982,7 @@
         <v>-148.35045</v>
       </c>
     </row>
-    <row r="450" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="450" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U450" s="1">
         <v>3.6406480000000001</v>
       </c>
@@ -10988,7 +11005,7 @@
         <v>-150.75631999999999</v>
       </c>
     </row>
-    <row r="451" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="451" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U451" s="1">
         <v>3.651278</v>
       </c>
@@ -11011,7 +11028,7 @@
         <v>-153.21003999999999</v>
       </c>
     </row>
-    <row r="452" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="452" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U452" s="1">
         <v>3.6617320000000002</v>
       </c>
@@ -11034,7 +11051,7 @@
         <v>-155.73222000000001</v>
       </c>
     </row>
-    <row r="453" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="453" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U453" s="1">
         <v>3.6720229999999998</v>
       </c>
@@ -11057,7 +11074,7 @@
         <v>-158.33564999999999</v>
       </c>
     </row>
-    <row r="454" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="454" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U454" s="1">
         <v>3.6821510000000002</v>
       </c>
@@ -11080,7 +11097,7 @@
         <v>-161.01133999999999</v>
       </c>
     </row>
-    <row r="455" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="455" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U455" s="1">
         <v>3.692126</v>
       </c>
@@ -11103,7 +11120,7 @@
         <v>-163.73007000000001</v>
       </c>
     </row>
-    <row r="456" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="456" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U456" s="1">
         <v>3.7019669999999998</v>
       </c>
@@ -11126,7 +11143,7 @@
         <v>-166.45155</v>
       </c>
     </row>
-    <row r="457" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="457" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U457" s="1">
         <v>3.7116899999999999</v>
       </c>
@@ -11149,7 +11166,7 @@
         <v>-169.12424999999999</v>
       </c>
     </row>
-    <row r="458" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="458" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U458" s="1">
         <v>3.7213080000000001</v>
       </c>
@@ -11172,7 +11189,7 @@
         <v>-171.70231999999999</v>
       </c>
     </row>
-    <row r="459" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="459" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U459" s="1">
         <v>3.7308340000000002</v>
       </c>
@@ -11195,7 +11212,7 @@
         <v>-174.15039999999999</v>
       </c>
     </row>
-    <row r="460" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="460" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U460" s="1">
         <v>3.7402839999999999</v>
       </c>
@@ -11218,7 +11235,7 @@
         <v>-176.42957000000001</v>
       </c>
     </row>
-    <row r="461" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="461" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U461" s="1">
         <v>3.749673</v>
       </c>
@@ -11241,7 +11258,7 @@
         <v>-178.50042999999999</v>
       </c>
     </row>
-    <row r="462" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="462" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U462" s="1">
         <v>3.7590330000000001</v>
       </c>
@@ -11264,7 +11281,7 @@
         <v>-180.33147</v>
       </c>
     </row>
-    <row r="463" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="463" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U463" s="1">
         <v>3.768383</v>
       </c>
@@ -11287,7 +11304,7 @@
         <v>-181.89139</v>
       </c>
     </row>
-    <row r="464" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="464" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U464" s="1">
         <v>3.7777630000000002</v>
       </c>
@@ -11310,7 +11327,7 @@
         <v>-183.16362000000001</v>
       </c>
     </row>
-    <row r="465" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="465" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U465" s="1">
         <v>3.7872110000000001</v>
       </c>
@@ -11333,7 +11350,7 @@
         <v>-184.13463999999999</v>
       </c>
     </row>
-    <row r="466" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="466" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U466" s="1">
         <v>3.7967680000000001</v>
       </c>
@@ -11356,7 +11373,7 @@
         <v>-184.77338</v>
       </c>
     </row>
-    <row r="467" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="467" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U467" s="1">
         <v>3.8064589999999998</v>
       </c>
@@ -11379,7 +11396,7 @@
         <v>-185.05089000000001</v>
       </c>
     </row>
-    <row r="468" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="468" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U468" s="1">
         <v>3.8163170000000002</v>
       </c>
@@ -11402,7 +11419,7 @@
         <v>-184.94502</v>
       </c>
     </row>
-    <row r="469" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="469" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U469" s="1">
         <v>3.826343</v>
       </c>
@@ -11425,7 +11442,7 @@
         <v>-184.42326</v>
       </c>
     </row>
-    <row r="470" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="470" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U470" s="1">
         <v>3.8365589999999998</v>
       </c>
@@ -11448,7 +11465,7 @@
         <v>-183.45869999999999</v>
       </c>
     </row>
-    <row r="471" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="471" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U471" s="1">
         <v>3.8469570000000002</v>
       </c>
@@ -11471,7 +11488,7 @@
         <v>-182.03448</v>
       </c>
     </row>
-    <row r="472" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="472" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U472" s="1">
         <v>3.8575409999999999</v>
       </c>
@@ -11494,7 +11511,7 @@
         <v>-180.14348000000001</v>
       </c>
     </row>
-    <row r="473" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="473" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U473" s="1">
         <v>3.8682940000000001</v>
       </c>
@@ -11517,7 +11534,7 @@
         <v>-177.79413</v>
       </c>
     </row>
-    <row r="474" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="474" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U474" s="1">
         <v>3.8792119999999999</v>
       </c>
@@ -11540,7 +11557,7 @@
         <v>-175.01796999999999</v>
       </c>
     </row>
-    <row r="475" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="475" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U475" s="1">
         <v>3.890266</v>
       </c>
@@ -11563,7 +11580,7 @@
         <v>-171.85432</v>
       </c>
     </row>
-    <row r="476" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="476" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U476" s="1">
         <v>3.901443</v>
       </c>
@@ -11586,7 +11603,7 @@
         <v>-168.35705999999999</v>
       </c>
     </row>
-    <row r="477" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="477" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U477" s="1">
         <v>3.9127169999999998</v>
       </c>
@@ -11609,7 +11626,7 @@
         <v>-164.59093999999999</v>
       </c>
     </row>
-    <row r="478" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="478" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U478" s="1">
         <v>3.924064</v>
       </c>
@@ -11632,7 +11649,7 @@
         <v>-160.62447</v>
       </c>
     </row>
-    <row r="479" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="479" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U479" s="1">
         <v>3.9354490000000002</v>
       </c>
@@ -11655,7 +11672,7 @@
         <v>-156.54329000000001</v>
       </c>
     </row>
-    <row r="480" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="480" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U480" s="1">
         <v>3.9468540000000001</v>
       </c>
@@ -11678,7 +11695,7 @@
         <v>-152.43704</v>
       </c>
     </row>
-    <row r="481" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="481" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U481" s="1">
         <v>3.9582280000000001</v>
       </c>
@@ -11701,7 +11718,7 @@
         <v>-148.39519000000001</v>
       </c>
     </row>
-    <row r="482" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="482" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U482" s="1">
         <v>3.969554</v>
       </c>
@@ -11724,7 +11741,7 @@
         <v>-144.51275999999999</v>
       </c>
     </row>
-    <row r="483" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="483" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U483" s="1">
         <v>3.9807959999999998</v>
       </c>
@@ -11747,7 +11764,7 @@
         <v>-140.88449</v>
       </c>
     </row>
-    <row r="484" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="484" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U484" s="1">
         <v>3.9919199999999999</v>
       </c>
@@ -11770,7 +11787,7 @@
         <v>-137.59705</v>
       </c>
     </row>
-    <row r="485" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="485" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U485" s="1">
         <v>4.0029300000000001</v>
       </c>
@@ -11793,7 +11810,7 @@
         <v>-134.72878</v>
       </c>
     </row>
-    <row r="486" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="486" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U486" s="1">
         <v>4.0138150000000001</v>
       </c>
@@ -11816,7 +11833,7 @@
         <v>-132.32598999999999</v>
       </c>
     </row>
-    <row r="487" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="487" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U487" s="1">
         <v>4.0245980000000001</v>
       </c>
@@ -11839,7 +11856,7 @@
         <v>-130.40880999999999</v>
       </c>
     </row>
-    <row r="488" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="488" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U488" s="1">
         <v>4.0352769999999998</v>
       </c>
@@ -11862,7 +11879,7 @@
         <v>-128.98186000000001</v>
       </c>
     </row>
-    <row r="489" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="489" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U489" s="1">
         <v>4.0458600000000002</v>
       </c>
@@ -11885,7 +11902,7 @@
         <v>-128.02988999999999</v>
       </c>
     </row>
-    <row r="490" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="490" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U490" s="1">
         <v>4.0563570000000002</v>
       </c>
@@ -11908,7 +11925,7 @@
         <v>-127.51119</v>
       </c>
     </row>
-    <row r="491" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="491" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U491" s="1">
         <v>4.0667819999999999</v>
       </c>
@@ -11931,7 +11948,7 @@
         <v>-127.35418</v>
       </c>
     </row>
-    <row r="492" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="492" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U492" s="1">
         <v>4.07714</v>
       </c>
@@ -11954,7 +11971,7 @@
         <v>-127.47811</v>
       </c>
     </row>
-    <row r="493" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="493" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U493" s="1">
         <v>4.0874459999999999</v>
       </c>
@@ -11977,7 +11994,7 @@
         <v>-127.82024</v>
       </c>
     </row>
-    <row r="494" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="494" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U494" s="1">
         <v>4.097696</v>
       </c>
@@ -12000,7 +12017,7 @@
         <v>-128.32649000000001</v>
       </c>
     </row>
-    <row r="495" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="495" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U495" s="1">
         <v>4.1078979999999996</v>
       </c>
@@ -12023,7 +12040,7 @@
         <v>-128.94498999999999</v>
       </c>
     </row>
-    <row r="496" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="496" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U496" s="1">
         <v>4.1180459999999997</v>
       </c>
@@ -12046,7 +12063,7 @@
         <v>-129.63285999999999</v>
       </c>
     </row>
-    <row r="497" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="497" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U497" s="1">
         <v>4.128145</v>
       </c>
@@ -12069,7 +12086,7 @@
         <v>-130.35956999999999</v>
       </c>
     </row>
-    <row r="498" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="498" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U498" s="1">
         <v>4.1381730000000001</v>
       </c>
@@ -12092,7 +12109,7 @@
         <v>-131.10230000000001</v>
       </c>
     </row>
-    <row r="499" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="499" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U499" s="1">
         <v>4.1481349999999999</v>
       </c>
@@ -12115,7 +12132,7 @@
         <v>-131.85715999999999</v>
       </c>
     </row>
-    <row r="500" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="500" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U500" s="1">
         <v>4.1580120000000003</v>
       </c>
@@ -12138,7 +12155,7 @@
         <v>-132.62251000000001</v>
       </c>
     </row>
-    <row r="501" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="501" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U501" s="1">
         <v>4.167789</v>
       </c>
@@ -12161,7 +12178,7 @@
         <v>-133.40358000000001</v>
       </c>
     </row>
-    <row r="502" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="502" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U502" s="1">
         <v>4.1774469999999999</v>
       </c>
@@ -12184,7 +12201,7 @@
         <v>-134.22210000000001</v>
       </c>
     </row>
-    <row r="503" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="503" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U503" s="1">
         <v>4.1869839999999998</v>
       </c>
@@ -12207,7 +12224,7 @@
         <v>-135.09610000000001</v>
       </c>
     </row>
-    <row r="504" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="504" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U504" s="1">
         <v>4.1963879999999998</v>
       </c>
@@ -12230,7 +12247,7 @@
         <v>-136.03530000000001</v>
       </c>
     </row>
-    <row r="505" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="505" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U505" s="1">
         <v>4.2056760000000004</v>
       </c>
@@ -12253,7 +12270,7 @@
         <v>-137.04947000000001</v>
       </c>
     </row>
-    <row r="506" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="506" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U506" s="1">
         <v>4.2148630000000002</v>
       </c>
@@ -12276,7 +12293,7 @@
         <v>-138.14131</v>
       </c>
     </row>
-    <row r="507" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="507" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U507" s="1">
         <v>4.2239779999999998</v>
       </c>
@@ -12299,7 +12316,7 @@
         <v>-139.29291000000001</v>
       </c>
     </row>
-    <row r="508" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="508" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U508" s="1">
         <v>4.2330420000000002</v>
       </c>
@@ -12322,7 +12339,7 @@
         <v>-140.47818000000001</v>
       </c>
     </row>
-    <row r="509" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="509" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U509" s="1">
         <v>4.2420869999999997</v>
       </c>
@@ -12345,7 +12362,7 @@
         <v>-141.66101</v>
       </c>
     </row>
-    <row r="510" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="510" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U510" s="1">
         <v>4.2511479999999997</v>
       </c>
@@ -12368,7 +12385,7 @@
         <v>-142.79208</v>
       </c>
     </row>
-    <row r="511" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="511" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U511" s="1">
         <v>4.2602500000000001</v>
       </c>
@@ -12391,7 +12408,7 @@
         <v>-143.80824000000001</v>
       </c>
     </row>
-    <row r="512" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="512" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U512" s="1">
         <v>4.2694140000000003</v>
       </c>
@@ -12414,7 +12431,7 @@
         <v>-144.65324000000001</v>
       </c>
     </row>
-    <row r="513" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="513" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U513" s="1">
         <v>4.2786609999999996</v>
       </c>
@@ -12437,7 +12454,7 @@
         <v>-145.28344999999999</v>
       </c>
     </row>
-    <row r="514" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="514" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U514" s="1">
         <v>4.2880120000000002</v>
       </c>
@@ -12460,7 +12477,7 @@
         <v>-145.65423999999999</v>
       </c>
     </row>
-    <row r="515" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="515" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U515" s="1">
         <v>4.2974740000000002</v>
       </c>
@@ -12483,7 +12500,7 @@
         <v>-145.72651999999999</v>
       </c>
     </row>
-    <row r="516" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="516" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U516" s="1">
         <v>4.3070570000000004</v>
       </c>
@@ -12506,7 +12523,7 @@
         <v>-145.47998000000001</v>
       </c>
     </row>
-    <row r="517" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="517" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U517" s="1">
         <v>4.3167619999999998</v>
       </c>
@@ -12529,7 +12546,7 @@
         <v>-144.90942000000001</v>
       </c>
     </row>
-    <row r="518" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="518" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U518" s="1">
         <v>4.3265880000000001</v>
       </c>
@@ -12552,7 +12569,7 @@
         <v>-144.01479</v>
       </c>
     </row>
-    <row r="519" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="519" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U519" s="1">
         <v>4.3365169999999997</v>
       </c>
@@ -12575,7 +12592,7 @@
         <v>-142.80437000000001</v>
       </c>
     </row>
-    <row r="520" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="520" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U520" s="1">
         <v>4.3465410000000002</v>
       </c>
@@ -12598,7 +12615,7 @@
         <v>-141.30797000000001</v>
       </c>
     </row>
-    <row r="521" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="521" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U521" s="1">
         <v>4.3566339999999997</v>
       </c>
@@ -12621,7 +12638,7 @@
         <v>-139.56120000000001</v>
       </c>
     </row>
-    <row r="522" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="522" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U522" s="1">
         <v>4.3667829999999999</v>
       </c>
@@ -12644,7 +12661,7 @@
         <v>-137.60257999999999</v>
       </c>
     </row>
-    <row r="523" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="523" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U523" s="1">
         <v>4.3769720000000003</v>
       </c>
@@ -12667,7 +12684,7 @@
         <v>-135.48661999999999</v>
       </c>
     </row>
-    <row r="524" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="524" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U524" s="1">
         <v>4.3871890000000002</v>
       </c>
@@ -12690,7 +12707,7 @@
         <v>-133.27385000000001</v>
       </c>
     </row>
-    <row r="525" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="525" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U525" s="1">
         <v>4.3974060000000001</v>
       </c>
@@ -12713,7 +12730,7 @@
         <v>-131.02332000000001</v>
       </c>
     </row>
-    <row r="526" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="526" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U526" s="1">
         <v>4.4076269999999997</v>
       </c>
@@ -12736,7 +12753,7 @@
         <v>-128.79912999999999</v>
       </c>
     </row>
-    <row r="527" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="527" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U527" s="1">
         <v>4.4178259999999998</v>
       </c>
@@ -12759,7 +12776,7 @@
         <v>-126.65149</v>
       </c>
     </row>
-    <row r="528" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="528" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U528" s="1">
         <v>4.4280109999999997</v>
       </c>
@@ -12782,7 +12799,7 @@
         <v>-124.61668400000001</v>
       </c>
     </row>
-    <row r="529" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="529" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U529" s="1">
         <v>4.4381570000000004</v>
       </c>
@@ -12805,7 +12822,7 @@
         <v>-122.72942</v>
       </c>
     </row>
-    <row r="530" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="530" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U530" s="1">
         <v>4.4482590000000002</v>
       </c>
@@ -12828,7 +12845,7 @@
         <v>-121.018585</v>
       </c>
     </row>
-    <row r="531" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="531" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U531" s="1">
         <v>4.4582800000000002</v>
       </c>
@@ -12851,7 +12868,7 @@
         <v>-119.51334</v>
       </c>
     </row>
-    <row r="532" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="532" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U532" s="1">
         <v>4.4682040000000001</v>
       </c>
@@ -12874,7 +12891,7 @@
         <v>-118.244</v>
       </c>
     </row>
-    <row r="533" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="533" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U533" s="1">
         <v>4.4779929999999997</v>
       </c>
@@ -12897,7 +12914,7 @@
         <v>-117.234314</v>
       </c>
     </row>
-    <row r="534" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="534" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U534" s="1">
         <v>4.487616</v>
       </c>
@@ -12920,7 +12937,7 @@
         <v>-116.51553</v>
       </c>
     </row>
-    <row r="535" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="535" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U535" s="1">
         <v>4.4970330000000001</v>
       </c>
@@ -12943,7 +12960,7 @@
         <v>-116.12812</v>
       </c>
     </row>
-    <row r="536" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="536" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U536" s="1">
         <v>4.5061980000000004</v>
       </c>
@@ -12966,7 +12983,7 @@
         <v>-116.11750000000001</v>
       </c>
     </row>
-    <row r="537" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="537" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U537" s="1">
         <v>4.5150639999999997</v>
       </c>
@@ -12989,7 +13006,7 @@
         <v>-116.53057</v>
       </c>
     </row>
-    <row r="538" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="538" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U538" s="1">
         <v>4.5235890000000003</v>
       </c>
@@ -13012,7 +13029,7 @@
         <v>-117.40170999999999</v>
       </c>
     </row>
-    <row r="539" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="539" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U539" s="1">
         <v>4.5317239999999996</v>
       </c>
@@ -13035,7 +13052,7 @@
         <v>-118.75373</v>
       </c>
     </row>
-    <row r="540" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="540" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U540" s="1">
         <v>4.5394490000000003</v>
       </c>
@@ -13058,7 +13075,7 @@
         <v>-120.59169</v>
       </c>
     </row>
-    <row r="541" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="541" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U541" s="1">
         <v>4.5467560000000002</v>
       </c>
@@ -13081,7 +13098,7 @@
         <v>-122.89704</v>
       </c>
     </row>
-    <row r="542" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="542" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U542" s="1">
         <v>4.5536390000000004</v>
       </c>
@@ -13104,7 +13121,7 @@
         <v>-125.617355</v>
       </c>
     </row>
-    <row r="543" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="543" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U543" s="1">
         <v>4.5601430000000001</v>
       </c>
@@ -13127,7 +13144,7 @@
         <v>-128.67696000000001</v>
       </c>
     </row>
-    <row r="544" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="544" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U544" s="1">
         <v>4.5663090000000004</v>
       </c>
@@ -13150,7 +13167,7 @@
         <v>-131.97351</v>
       </c>
     </row>
-    <row r="545" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="545" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U545" s="1">
         <v>4.5722120000000004</v>
       </c>
@@ -13173,7 +13190,7 @@
         <v>-135.37710000000001</v>
       </c>
     </row>
-    <row r="546" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="546" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U546" s="1">
         <v>4.5779129999999997</v>
       </c>
@@ -13196,7 +13213,7 @@
         <v>-138.7602</v>
       </c>
     </row>
-    <row r="547" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="547" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U547" s="1">
         <v>4.5834929999999998</v>
       </c>
@@ -13219,7 +13236,7 @@
         <v>-142.00765999999999</v>
       </c>
     </row>
-    <row r="548" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="548" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U548" s="1">
         <v>4.5890139999999997</v>
       </c>
@@ -13242,7 +13259,7 @@
         <v>-145.00897000000001</v>
       </c>
     </row>
-    <row r="549" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="549" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U549" s="1">
         <v>4.5945359999999997</v>
       </c>
@@ -13265,7 +13282,7 @@
         <v>-147.66866999999999</v>
       </c>
     </row>
-    <row r="550" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="550" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U550" s="1">
         <v>4.6000959999999997</v>
       </c>
@@ -13288,7 +13305,7 @@
         <v>-149.9222</v>
       </c>
     </row>
-    <row r="551" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="551" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U551" s="1">
         <v>4.605721</v>
       </c>
@@ -13311,7 +13328,7 @@
         <v>-151.72441000000001</v>
       </c>
     </row>
-    <row r="552" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="552" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U552" s="1">
         <v>4.6114050000000004</v>
       </c>
@@ -13334,7 +13351,7 @@
         <v>-153.04602</v>
       </c>
     </row>
-    <row r="553" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="553" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U553" s="1">
         <v>4.6171369999999996</v>
       </c>
@@ -13357,7 +13374,7 @@
         <v>-153.87899999999999</v>
       </c>
     </row>
-    <row r="554" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="554" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U554" s="1">
         <v>4.622884</v>
       </c>
@@ -13380,7 +13397,7 @@
         <v>-154.23195000000001</v>
       </c>
     </row>
-    <row r="555" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="555" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U555" s="1">
         <v>4.6286100000000001</v>
       </c>
@@ -13403,7 +13420,7 @@
         <v>-154.12445</v>
       </c>
     </row>
-    <row r="556" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="556" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U556" s="1">
         <v>4.6342600000000003</v>
       </c>
@@ -13426,7 +13443,7 @@
         <v>-153.59181000000001</v>
       </c>
     </row>
-    <row r="557" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="557" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U557" s="1">
         <v>4.6397890000000004</v>
       </c>
@@ -13449,7 +13466,7 @@
         <v>-152.68451999999999</v>
       </c>
     </row>
-    <row r="558" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="558" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U558" s="1">
         <v>4.6451570000000002</v>
       </c>
@@ -13472,7 +13489,7 @@
         <v>-151.46652</v>
       </c>
     </row>
-    <row r="559" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="559" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U559" s="1">
         <v>4.6503100000000002</v>
       </c>
@@ -13495,7 +13512,7 @@
         <v>-149.99449000000001</v>
       </c>
     </row>
-    <row r="560" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="560" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U560" s="1">
         <v>4.6552179999999996</v>
       </c>
@@ -13518,7 +13535,7 @@
         <v>-148.32988</v>
       </c>
     </row>
-    <row r="561" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="561" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U561" s="1">
         <v>4.6598540000000002</v>
       </c>
@@ -13541,7 +13558,7 @@
         <v>-146.53479999999999</v>
       </c>
     </row>
-    <row r="562" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="562" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U562" s="1">
         <v>4.6642080000000004</v>
       </c>
@@ -13564,7 +13581,7 @@
         <v>-144.65010000000001</v>
       </c>
     </row>
-    <row r="563" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="563" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U563" s="1">
         <v>4.6682800000000002</v>
       </c>
@@ -13587,7 +13604,7 @@
         <v>-142.70499000000001</v>
       </c>
     </row>
-    <row r="564" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="564" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U564" s="1">
         <v>4.6720810000000004</v>
       </c>
@@ -13610,7 +13627,7 @@
         <v>-140.72284999999999</v>
       </c>
     </row>
-    <row r="565" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="565" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U565" s="1">
         <v>4.6756450000000003</v>
       </c>
@@ -13633,7 +13650,7 @@
         <v>-138.71999</v>
       </c>
     </row>
-    <row r="566" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="566" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U566" s="1">
         <v>4.6789889999999996</v>
       </c>
@@ -13656,7 +13673,7 @@
         <v>-136.6926</v>
       </c>
     </row>
-    <row r="567" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="567" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U567" s="1">
         <v>4.6821650000000004</v>
       </c>
@@ -13679,7 +13696,7 @@
         <v>-134.64134000000001</v>
       </c>
     </row>
-    <row r="568" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="568" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U568" s="1">
         <v>4.6852070000000001</v>
       </c>
@@ -13702,7 +13719,7 @@
         <v>-132.56844000000001</v>
       </c>
     </row>
-    <row r="569" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="569" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U569" s="1">
         <v>4.6881579999999996</v>
       </c>
@@ -13725,7 +13742,7 @@
         <v>-130.46587</v>
       </c>
     </row>
-    <row r="570" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="570" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U570" s="1">
         <v>4.6910740000000004</v>
       </c>
@@ -13748,7 +13765,7 @@
         <v>-128.34956</v>
       </c>
     </row>
-    <row r="571" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="571" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U571" s="1">
         <v>4.6939989999999998</v>
       </c>
@@ -13771,7 +13788,7 @@
         <v>-126.24272999999999</v>
       </c>
     </row>
-    <row r="572" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="572" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U572" s="1">
         <v>4.6969510000000003</v>
       </c>
@@ -13794,7 +13811,7 @@
         <v>-124.14644</v>
       </c>
     </row>
-    <row r="573" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="573" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U573" s="1">
         <v>4.6999639999999996</v>
       </c>
@@ -13817,7 +13834,7 @@
         <v>-122.074585</v>
       </c>
     </row>
-    <row r="574" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="574" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U574" s="1">
         <v>4.7030479999999999</v>
       </c>
@@ -13840,7 +13857,7 @@
         <v>-120.03999</v>
       </c>
     </row>
-    <row r="575" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="575" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U575" s="1">
         <v>4.7061960000000003</v>
       </c>
@@ -13863,7 +13880,7 @@
         <v>-118.02254000000001</v>
       </c>
     </row>
-    <row r="576" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="576" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U576" s="1">
         <v>4.7093939999999996</v>
       </c>
@@ -13886,7 +13903,7 @@
         <v>-116.00388</v>
       </c>
     </row>
-    <row r="577" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="577" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U577" s="1">
         <v>4.7126250000000001</v>
       </c>
@@ -13909,7 +13926,7 @@
         <v>-113.97093</v>
       </c>
     </row>
-    <row r="578" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="578" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U578" s="1">
         <v>4.7158410000000002</v>
       </c>
@@ -13932,7 +13949,7 @@
         <v>-111.88602</v>
       </c>
     </row>
-    <row r="579" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="579" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U579" s="1">
         <v>4.7189930000000002</v>
       </c>
@@ -13955,7 +13972,7 @@
         <v>-109.70484999999999</v>
       </c>
     </row>
-    <row r="580" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="580" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U580" s="1">
         <v>4.7220409999999999</v>
       </c>
@@ -13978,7 +13995,7 @@
         <v>-107.40770999999999</v>
       </c>
     </row>
-    <row r="581" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="581" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U581" s="1">
         <v>4.7249270000000001</v>
       </c>
@@ -14001,7 +14018,7 @@
         <v>-104.96731</v>
       </c>
     </row>
-    <row r="582" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="582" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U582" s="1">
         <v>4.7276189999999998</v>
       </c>
@@ -14024,7 +14041,7 @@
         <v>-102.3686</v>
       </c>
     </row>
-    <row r="583" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="583" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U583" s="1">
         <v>4.7300979999999999</v>
       </c>
@@ -14047,7 +14064,7 @@
         <v>-99.633200000000002</v>
       </c>
     </row>
-    <row r="584" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="584" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U584" s="1">
         <v>4.7323599999999999</v>
       </c>
@@ -14070,7 +14087,7 @@
         <v>-96.789153999999996</v>
       </c>
     </row>
-    <row r="585" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="585" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U585" s="1">
         <v>4.734394</v>
       </c>
@@ -14093,7 +14110,7 @@
         <v>-93.858329999999995</v>
       </c>
     </row>
-    <row r="586" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="586" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U586" s="1">
         <v>4.7362270000000004</v>
       </c>
@@ -14116,7 +14133,7 @@
         <v>-90.876720000000006</v>
       </c>
     </row>
-    <row r="587" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="587" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U587" s="1">
         <v>4.7379040000000003</v>
       </c>
@@ -14139,7 +14156,7 @@
         <v>-87.900734</v>
       </c>
     </row>
-    <row r="588" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="588" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U588" s="1">
         <v>4.7394670000000003</v>
       </c>
@@ -14162,7 +14179,7 @@
         <v>-84.978645</v>
       </c>
     </row>
-    <row r="589" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="589" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U589" s="1">
         <v>4.7409749999999997</v>
       </c>
@@ -14185,7 +14202,7 @@
         <v>-82.160933999999997</v>
       </c>
     </row>
-    <row r="590" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="590" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U590" s="1">
         <v>4.7424580000000001</v>
       </c>
@@ -14208,7 +14225,7 @@
         <v>-79.486649999999997</v>
       </c>
     </row>
-    <row r="591" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="591" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U591" s="1">
         <v>4.7439539999999996</v>
       </c>
@@ -14231,7 +14248,7 @@
         <v>-76.976616000000007</v>
       </c>
     </row>
-    <row r="592" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="592" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U592" s="1">
         <v>4.7455040000000004</v>
       </c>
@@ -14254,7 +14271,7 @@
         <v>-74.656549999999996</v>
       </c>
     </row>
-    <row r="593" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="593" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U593" s="1">
         <v>4.7471230000000002</v>
       </c>
@@ -14277,7 +14294,7 @@
         <v>-72.532775999999998</v>
       </c>
     </row>
-    <row r="594" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="594" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U594" s="1">
         <v>4.7488239999999999</v>
       </c>
@@ -14300,7 +14317,7 @@
         <v>-70.599140000000006</v>
       </c>
     </row>
-    <row r="595" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="595" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U595" s="1">
         <v>4.7506000000000004</v>
       </c>
@@ -14323,7 +14340,7 @@
         <v>-68.838009999999997</v>
       </c>
     </row>
-    <row r="596" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="596" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U596" s="1">
         <v>4.7524150000000001</v>
       </c>
@@ -14346,7 +14363,7 @@
         <v>-67.195800000000006</v>
       </c>
     </row>
-    <row r="597" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="597" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U597" s="1">
         <v>4.7542419999999996</v>
       </c>
@@ -14369,7 +14386,7 @@
         <v>-65.612170000000006</v>
       </c>
     </row>
-    <row r="598" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="598" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U598" s="1">
         <v>4.7560339999999997</v>
       </c>
@@ -14392,7 +14409,7 @@
         <v>-64.028580000000005</v>
       </c>
     </row>
-    <row r="599" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="599" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U599" s="1">
         <v>4.7577540000000003</v>
       </c>
@@ -14415,7 +14432,7 @@
         <v>-62.389519999999997</v>
       </c>
     </row>
-    <row r="600" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="600" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U600" s="1">
         <v>4.7593670000000001</v>
       </c>
@@ -14438,7 +14455,7 @@
         <v>-60.658484999999999</v>
       </c>
     </row>
-    <row r="601" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="601" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U601" s="1">
         <v>4.7608329999999999</v>
       </c>
@@ -14461,7 +14478,7 @@
         <v>-58.806365999999997</v>
       </c>
     </row>
-    <row r="602" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="602" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U602" s="1">
         <v>4.7621440000000002</v>
       </c>
@@ -14484,7 +14501,7 @@
         <v>-56.830005999999997</v>
       </c>
     </row>
-    <row r="603" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="603" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U603" s="1">
         <v>4.7632979999999998</v>
       </c>
@@ -14507,7 +14524,7 @@
         <v>-54.750121999999998</v>
       </c>
     </row>
-    <row r="604" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="604" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U604" s="1">
         <v>4.764303</v>
       </c>
@@ -14530,7 +14547,7 @@
         <v>-52.593685000000001</v>
       </c>
     </row>
-    <row r="605" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="605" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U605" s="1">
         <v>4.7651960000000004</v>
       </c>
@@ -14553,7 +14570,7 @@
         <v>-50.411006999999998</v>
       </c>
     </row>
-    <row r="606" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="606" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U606" s="1">
         <v>4.7660080000000002</v>
       </c>
@@ -14576,7 +14593,7 @@
         <v>-48.259132000000001</v>
       </c>
     </row>
-    <row r="607" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="607" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U607" s="1">
         <v>4.766775</v>
       </c>
@@ -14599,7 +14616,7 @@
         <v>-46.183815000000003</v>
       </c>
     </row>
-    <row r="608" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="608" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U608" s="1">
         <v>4.7675210000000003</v>
       </c>
@@ -14622,7 +14639,7 @@
         <v>-44.218741999999999</v>
       </c>
     </row>
-    <row r="609" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="609" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U609" s="1">
         <v>4.7682789999999997</v>
       </c>
@@ -14645,7 +14662,7 @@
         <v>-42.390495000000001</v>
       </c>
     </row>
-    <row r="610" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="610" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U610" s="1">
         <v>4.7690619999999999</v>
       </c>
@@ -14668,7 +14685,7 @@
         <v>-40.715564999999998</v>
       </c>
     </row>
-    <row r="611" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="611" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U611" s="1">
         <v>4.7698679999999998</v>
       </c>
@@ -14691,7 +14708,7 @@
         <v>-39.181310000000003</v>
       </c>
     </row>
-    <row r="612" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="612" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U612" s="1">
         <v>4.7706900000000001</v>
       </c>
@@ -14714,7 +14731,7 @@
         <v>-37.762</v>
       </c>
     </row>
-    <row r="613" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="613" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U613" s="1">
         <v>4.7714939999999997</v>
       </c>
@@ -14737,7 +14754,7 @@
         <v>-36.413204</v>
       </c>
     </row>
-    <row r="614" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="614" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U614" s="1">
         <v>4.7722569999999997</v>
       </c>
@@ -14760,7 +14777,7 @@
         <v>-35.082076999999998</v>
       </c>
     </row>
-    <row r="615" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="615" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U615" s="1">
         <v>4.7729549999999996</v>
       </c>
@@ -14783,7 +14800,7 @@
         <v>-33.732117000000002</v>
       </c>
     </row>
-    <row r="616" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="616" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U616" s="1">
         <v>4.7735469999999998</v>
       </c>
@@ -14806,7 +14823,7 @@
         <v>-32.317207000000003</v>
       </c>
     </row>
-    <row r="617" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="617" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U617" s="1">
         <v>4.7740130000000001</v>
       </c>
@@ -14829,7 +14846,7 @@
         <v>-30.799617999999999</v>
       </c>
     </row>
-    <row r="618" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="618" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U618" s="1">
         <v>4.7743349999999998</v>
       </c>
@@ -14852,7 +14869,7 @@
         <v>-29.167010000000001</v>
       </c>
     </row>
-    <row r="619" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="619" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U619" s="1">
         <v>4.7746449999999996</v>
       </c>
@@ -14875,7 +14892,7 @@
         <v>-19.729189999999999</v>
       </c>
     </row>
-    <row r="620" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="620" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U620" s="1">
         <v>4.7751250000000001</v>
       </c>
@@ -14898,7 +14915,7 @@
         <v>-16.202856000000001</v>
       </c>
     </row>
-    <row r="621" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="621" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U621" s="1">
         <v>4.7755869999999998</v>
       </c>
@@ -14921,7 +14938,7 @@
         <v>-13.134824</v>
       </c>
     </row>
-    <row r="622" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="622" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U622" s="1">
         <v>4.7760030000000002</v>
       </c>
@@ -14944,7 +14961,7 @@
         <v>-10.540304000000001</v>
       </c>
     </row>
-    <row r="623" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="623" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U623" s="1">
         <v>4.7764709999999999</v>
       </c>
@@ -14967,7 +14984,7 @@
         <v>-8.2479340000000008</v>
       </c>
     </row>
-    <row r="624" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="624" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U624" s="1">
         <v>4.7771189999999999</v>
       </c>
@@ -14990,7 +15007,7 @@
         <v>-6.0262260000000003</v>
       </c>
     </row>
-    <row r="625" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U625" s="1">
         <v>4.7775540000000003</v>
       </c>
@@ -15013,7 +15030,7 @@
         <v>-4.8709100000000003</v>
       </c>
     </row>
-    <row r="626" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U626" s="1">
         <v>4.7780639999999996</v>
       </c>
@@ -15036,7 +15053,7 @@
         <v>-3.6733707999999998</v>
       </c>
     </row>
-    <row r="627" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U627" s="1">
         <v>4.7786619999999997</v>
       </c>
@@ -15059,7 +15076,7 @@
         <v>-2.4297040000000001</v>
       </c>
     </row>
-    <row r="628" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U628" s="1">
         <v>4.7793409999999996</v>
       </c>
@@ -15082,7 +15099,7 @@
         <v>-1.1388514999999999</v>
       </c>
     </row>
-    <row r="629" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>27</v>
       </c>
@@ -15165,7 +15182,7 @@
         <v>0.2346897</v>
       </c>
     </row>
-    <row r="630" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U630" s="1">
         <v>8.5899999999999995E-4</v>
       </c>
@@ -15188,7 +15205,7 @@
         <v>1.882641</v>
       </c>
     </row>
-    <row r="631" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U631" s="1">
         <v>1.8E-3</v>
       </c>
@@ -15211,7 +15228,7 @@
         <v>3.5816623999999999</v>
       </c>
     </row>
-    <row r="632" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U632" s="1">
         <v>2.836E-3</v>
       </c>
@@ -15234,7 +15251,7 @@
         <v>5.334892</v>
       </c>
     </row>
-    <row r="633" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U633" s="1">
         <v>3.9569999999999996E-3</v>
       </c>
@@ -15257,7 +15274,7 @@
         <v>7.1454360000000001</v>
       </c>
     </row>
-    <row r="634" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U634" s="1">
         <v>5.1650000000000003E-3</v>
       </c>
@@ -15280,7 +15297,7 @@
         <v>9.0021439999999995</v>
       </c>
     </row>
-    <row r="635" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U635" s="1">
         <v>6.4790000000000004E-3</v>
       </c>
@@ -15303,7 +15320,7 @@
         <v>10.925337000000001</v>
       </c>
     </row>
-    <row r="636" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U636" s="1">
         <v>7.8899999999999994E-3</v>
       </c>
@@ -15326,7 +15343,7 @@
         <v>12.92366</v>
       </c>
     </row>
-    <row r="637" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U637" s="1">
         <v>9.3939999999999996E-3</v>
       </c>
@@ -15349,7 +15366,7 @@
         <v>14.980784999999999</v>
       </c>
     </row>
-    <row r="638" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U638" s="1">
         <v>1.0988E-2</v>
       </c>
@@ -15372,7 +15389,7 @@
         <v>17.087837</v>
       </c>
     </row>
-    <row r="639" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U639" s="1">
         <v>1.2673E-2</v>
       </c>
@@ -15395,7 +15412,7 @@
         <v>19.240316</v>
       </c>
     </row>
-    <row r="640" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:27" x14ac:dyDescent="0.3">
       <c r="U640" s="1">
         <v>1.4460000000000001E-2</v>
       </c>
@@ -15418,7 +15435,7 @@
         <v>21.450699</v>
       </c>
     </row>
-    <row r="641" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="641" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U641" s="1">
         <v>1.636E-2</v>
       </c>
@@ -15441,7 +15458,7 @@
         <v>23.742547999999999</v>
       </c>
     </row>
-    <row r="642" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="642" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U642" s="1">
         <v>1.8384000000000001E-2</v>
       </c>
@@ -15464,7 +15481,7 @@
         <v>26.136486000000001</v>
       </c>
     </row>
-    <row r="643" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="643" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U643" s="1">
         <v>2.0528000000000001E-2</v>
       </c>
@@ -15487,7 +15504,7 @@
         <v>28.637753</v>
       </c>
     </row>
-    <row r="644" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="644" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U644" s="1">
         <v>2.2818000000000001E-2</v>
       </c>
@@ -15510,7 +15527,7 @@
         <v>31.266172000000001</v>
       </c>
     </row>
-    <row r="645" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="645" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U645" s="1">
         <v>2.5260000000000001E-2</v>
       </c>
@@ -15533,7 +15550,7 @@
         <v>34.056980000000003</v>
       </c>
     </row>
-    <row r="646" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="646" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U646" s="1">
         <v>2.7872999999999998E-2</v>
       </c>
@@ -15556,7 +15573,7 @@
         <v>37.037280000000003</v>
       </c>
     </row>
-    <row r="647" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="647" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U647" s="1">
         <v>3.0651000000000001E-2</v>
       </c>
@@ -15579,7 +15596,7 @@
         <v>40.218387999999997</v>
       </c>
     </row>
-    <row r="648" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="648" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U648" s="1">
         <v>3.3582000000000001E-2</v>
       </c>
@@ -15602,7 +15619,7 @@
         <v>43.578426</v>
       </c>
     </row>
-    <row r="649" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="649" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U649" s="1">
         <v>3.6660999999999999E-2</v>
       </c>
@@ -15625,7 +15642,7 @@
         <v>47.094624000000003</v>
       </c>
     </row>
-    <row r="650" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="650" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U650" s="1">
         <v>3.9870000000000003E-2</v>
       </c>
@@ -15648,7 +15665,7 @@
         <v>50.739654999999999</v>
       </c>
     </row>
-    <row r="651" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="651" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U651" s="1">
         <v>4.3174999999999998E-2</v>
       </c>
@@ -15671,7 +15688,7 @@
         <v>54.450879999999998</v>
       </c>
     </row>
-    <row r="652" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="652" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U652" s="1">
         <v>4.657E-2</v>
       </c>
@@ -15694,7 +15711,7 @@
         <v>58.173896999999997</v>
       </c>
     </row>
-    <row r="653" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="653" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U653" s="1">
         <v>5.0039E-2</v>
       </c>
@@ -15717,7 +15734,7 @@
         <v>61.875216999999999</v>
       </c>
     </row>
-    <row r="654" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="654" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U654" s="1">
         <v>5.3553999999999997E-2</v>
       </c>
@@ -15740,7 +15757,7 @@
         <v>65.495109999999997</v>
       </c>
     </row>
-    <row r="655" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="655" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U655" s="1">
         <v>5.7118000000000002E-2</v>
       </c>
@@ -15763,7 +15780,7 @@
         <v>68.992810000000006</v>
       </c>
     </row>
-    <row r="656" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="656" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U656" s="1">
         <v>6.0699000000000003E-2</v>
       </c>
@@ -15786,7 +15803,7 @@
         <v>72.322999999999993</v>
       </c>
     </row>
-    <row r="657" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="657" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U657" s="1">
         <v>6.4302999999999999E-2</v>
       </c>
@@ -15809,7 +15826,7 @@
         <v>75.44659</v>
       </c>
     </row>
-    <row r="658" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="658" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U658" s="1">
         <v>6.7918000000000006E-2</v>
       </c>
@@ -15832,7 +15849,7 @@
         <v>78.35275</v>
       </c>
     </row>
-    <row r="659" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="659" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U659" s="1">
         <v>7.1537000000000003E-2</v>
       </c>
@@ -15855,7 +15872,7 @@
         <v>81.019649999999999</v>
       </c>
     </row>
-    <row r="660" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="660" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U660" s="1">
         <v>7.5157000000000002E-2</v>
       </c>
@@ -15878,7 +15895,7 @@
         <v>83.436806000000004</v>
       </c>
     </row>
-    <row r="661" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="661" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U661" s="1">
         <v>7.8783000000000006E-2</v>
       </c>
@@ -15901,7 +15918,7 @@
         <v>85.610299999999995</v>
       </c>
     </row>
-    <row r="662" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="662" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U662" s="1">
         <v>8.2408999999999996E-2</v>
       </c>
@@ -15924,7 +15941,7 @@
         <v>87.551990000000004</v>
       </c>
     </row>
-    <row r="663" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="663" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U663" s="1">
         <v>8.6039000000000004E-2</v>
       </c>
@@ -15947,7 +15964,7 @@
         <v>89.269424000000001</v>
       </c>
     </row>
-    <row r="664" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="664" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U664" s="1">
         <v>8.9659000000000003E-2</v>
       </c>
@@ -15970,7 +15987,7 @@
         <v>90.760329999999996</v>
       </c>
     </row>
-    <row r="665" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="665" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U665" s="1">
         <v>9.3258999999999995E-2</v>
       </c>
@@ -15993,7 +16010,7 @@
         <v>92.006910000000005</v>
       </c>
     </row>
-    <row r="666" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="666" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U666" s="1">
         <v>9.6840999999999997E-2</v>
       </c>
@@ -16016,7 +16033,7 @@
         <v>93.011340000000004</v>
       </c>
     </row>
-    <row r="667" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="667" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U667" s="1">
         <v>0.100406</v>
       </c>
@@ -16039,7 +16056,7 @@
         <v>93.797889999999995</v>
       </c>
     </row>
-    <row r="668" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="668" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U668" s="1">
         <v>0.10394299999999999</v>
       </c>
@@ -16062,7 +16079,7 @@
         <v>94.371380000000002</v>
       </c>
     </row>
-    <row r="669" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="669" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U669" s="1">
         <v>0.107474</v>
       </c>
@@ -16085,7 +16102,7 @@
         <v>94.75591</v>
       </c>
     </row>
-    <row r="670" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="670" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U670" s="1">
         <v>0.11097600000000001</v>
       </c>
@@ -16108,7 +16125,7 @@
         <v>94.962220000000002</v>
       </c>
     </row>
-    <row r="671" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="671" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U671" s="1">
         <v>0.11447400000000001</v>
       </c>
@@ -16131,7 +16148,7 @@
         <v>95.010779999999997</v>
       </c>
     </row>
-    <row r="672" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="672" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U672" s="1">
         <v>0.117967</v>
       </c>
@@ -16154,7 +16171,7 @@
         <v>94.947190000000006</v>
       </c>
     </row>
-    <row r="673" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="673" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U673" s="1">
         <v>0.12145499999999999</v>
       </c>
@@ -16177,7 +16194,7 @@
         <v>94.783919999999995</v>
       </c>
     </row>
-    <row r="674" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="674" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U674" s="1">
         <v>0.124968</v>
       </c>
@@ -16200,7 +16217,7 @@
         <v>94.571910000000003</v>
       </c>
     </row>
-    <row r="675" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="675" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U675" s="1">
         <v>0.128493</v>
       </c>
@@ -16223,7 +16240,7 @@
         <v>94.343469999999996</v>
       </c>
     </row>
-    <row r="676" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="676" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U676" s="1">
         <v>0.13204099999999999</v>
       </c>
@@ -16246,7 +16263,7 @@
         <v>94.106089999999995</v>
       </c>
     </row>
-    <row r="677" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="677" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U677" s="1">
         <v>0.13561100000000001</v>
       </c>
@@ -16269,7 +16286,7 @@
         <v>93.875910000000005</v>
       </c>
     </row>
-    <row r="678" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="678" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U678" s="1">
         <v>0.139212</v>
       </c>
@@ -16292,7 +16309,7 @@
         <v>93.671584999999993</v>
       </c>
     </row>
-    <row r="679" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="679" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U679" s="1">
         <v>0.142846</v>
       </c>
@@ -16315,7 +16332,7 @@
         <v>93.51661</v>
       </c>
     </row>
-    <row r="680" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="680" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U680" s="1">
         <v>0.14651700000000001</v>
       </c>
@@ -16338,7 +16355,7 @@
         <v>93.416749999999993</v>
       </c>
     </row>
-    <row r="681" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="681" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U681" s="1">
         <v>0.15021999999999999</v>
       </c>
@@ -16361,7 +16378,7 @@
         <v>93.369470000000007</v>
       </c>
     </row>
-    <row r="682" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="682" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U682" s="1">
         <v>0.15395300000000001</v>
       </c>
@@ -16384,7 +16401,7 @@
         <v>93.365250000000003</v>
       </c>
     </row>
-    <row r="683" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="683" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U683" s="1">
         <v>0.15768399999999999</v>
       </c>
@@ -16407,7 +16424,7 @@
         <v>93.360500000000002</v>
       </c>
     </row>
-    <row r="684" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="684" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U684" s="1">
         <v>0.161411</v>
       </c>
@@ -16430,7 +16447,7 @@
         <v>93.311779999999999</v>
       </c>
     </row>
-    <row r="685" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="685" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U685" s="1">
         <v>0.16514400000000001</v>
       </c>
@@ -16453,7 +16470,7 @@
         <v>93.229560000000006</v>
       </c>
     </row>
-    <row r="686" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="686" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U686" s="1">
         <v>0.16889100000000001</v>
       </c>
@@ -16476,7 +16493,7 @@
         <v>93.141105999999994</v>
       </c>
     </row>
-    <row r="687" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="687" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U687" s="1">
         <v>0.17267399999999999</v>
       </c>
@@ -16499,7 +16516,7 @@
         <v>93.078025999999994</v>
       </c>
     </row>
-    <row r="688" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="688" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U688" s="1">
         <v>0.17651600000000001</v>
       </c>
@@ -16522,7 +16539,7 @@
         <v>93.082589999999996</v>
       </c>
     </row>
-    <row r="689" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="689" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U689" s="1">
         <v>0.18041699999999999</v>
       </c>
@@ -16545,7 +16562,7 @@
         <v>93.181799999999996</v>
       </c>
     </row>
-    <row r="690" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="690" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U690" s="1">
         <v>0.18441199999999999</v>
       </c>
@@ -16568,7 +16585,7 @@
         <v>93.417500000000004</v>
       </c>
     </row>
-    <row r="691" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="691" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U691" s="1">
         <v>0.18849299999999999</v>
       </c>
@@ -16591,7 +16608,7 @@
         <v>93.826130000000006</v>
       </c>
     </row>
-    <row r="692" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="692" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U692" s="1">
         <v>0.192691</v>
       </c>
@@ -16614,7 +16631,7 @@
         <v>94.437775000000002</v>
       </c>
     </row>
-    <row r="693" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="693" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U693" s="1">
         <v>0.19699</v>
       </c>
@@ -16637,7 +16654,7 @@
         <v>95.271280000000004</v>
       </c>
     </row>
-    <row r="694" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="694" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U694" s="1">
         <v>0.20141600000000001</v>
       </c>
@@ -16660,7 +16677,7 @@
         <v>96.336259999999996</v>
       </c>
     </row>
-    <row r="695" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="695" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U695" s="1">
         <v>0.20594999999999999</v>
       </c>
@@ -16683,7 +16700,7 @@
         <v>97.636284000000003</v>
       </c>
     </row>
-    <row r="696" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="696" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U696" s="1">
         <v>0.210588</v>
       </c>
@@ -16706,7 +16723,7 @@
         <v>99.13879</v>
       </c>
     </row>
-    <row r="697" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="697" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U697" s="1">
         <v>0.21532699999999999</v>
       </c>
@@ -16729,7 +16746,7 @@
         <v>100.82342</v>
       </c>
     </row>
-    <row r="698" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="698" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U698" s="1">
         <v>0.22015100000000001</v>
       </c>
@@ -16752,7 +16769,7 @@
         <v>102.65946</v>
       </c>
     </row>
-    <row r="699" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="699" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U699" s="1">
         <v>0.22506399999999999</v>
       </c>
@@ -16775,7 +16792,7 @@
         <v>104.62097</v>
       </c>
     </row>
-    <row r="700" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="700" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U700" s="1">
         <v>0.230047</v>
       </c>
@@ -16798,7 +16815,7 @@
         <v>106.67685</v>
       </c>
     </row>
-    <row r="701" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="701" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U701" s="1">
         <v>0.2351</v>
       </c>
@@ -16821,7 +16838,7 @@
         <v>108.786674</v>
       </c>
     </row>
-    <row r="702" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="702" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U702" s="1">
         <v>0.24021200000000001</v>
       </c>
@@ -16844,7 +16861,7 @@
         <v>110.92229500000001</v>
       </c>
     </row>
-    <row r="703" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="703" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U703" s="1">
         <v>0.24538299999999999</v>
       </c>
@@ -16867,7 +16884,7 @@
         <v>113.060455</v>
       </c>
     </row>
-    <row r="704" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="704" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U704" s="1">
         <v>0.25062499999999999</v>
       </c>
@@ -16890,7 +16907,7 @@
         <v>115.20726999999999</v>
       </c>
     </row>
-    <row r="705" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="705" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U705" s="1">
         <v>0.25592900000000002</v>
       </c>
@@ -16913,7 +16930,7 @@
         <v>117.35993000000001</v>
       </c>
     </row>
-    <row r="706" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="706" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U706" s="1">
         <v>0.26131900000000002</v>
       </c>
@@ -16936,7 +16953,7 @@
         <v>119.53071</v>
       </c>
     </row>
-    <row r="707" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="707" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U707" s="1">
         <v>0.26680100000000001</v>
       </c>
@@ -16959,7 +16976,7 @@
         <v>121.753624</v>
       </c>
     </row>
-    <row r="708" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="708" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U708" s="1">
         <v>0.27238299999999999</v>
       </c>
@@ -16982,7 +16999,7 @@
         <v>124.0506</v>
       </c>
     </row>
-    <row r="709" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="709" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U709" s="1">
         <v>0.27808100000000002</v>
       </c>
@@ -17005,7 +17022,7 @@
         <v>126.45519</v>
       </c>
     </row>
-    <row r="710" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="710" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U710" s="1">
         <v>0.28389999999999999</v>
       </c>
@@ -17028,7 +17045,7 @@
         <v>128.99866</v>
       </c>
     </row>
-    <row r="711" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="711" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U711" s="1">
         <v>0.28986400000000001</v>
       </c>
@@ -17051,7 +17068,7 @@
         <v>131.72452000000001</v>
       </c>
     </row>
-    <row r="712" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="712" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U712" s="1">
         <v>0.29597400000000001</v>
       </c>
@@ -17074,7 +17091,7 @@
         <v>134.67276000000001</v>
       </c>
     </row>
-    <row r="713" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="713" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U713" s="1">
         <v>0.30224800000000002</v>
       </c>
@@ -17097,7 +17114,7 @@
         <v>137.87463</v>
       </c>
     </row>
-    <row r="714" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="714" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U714" s="1">
         <v>0.308697</v>
       </c>
@@ -17120,7 +17137,7 @@
         <v>141.36967000000001</v>
       </c>
     </row>
-    <row r="715" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="715" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U715" s="1">
         <v>0.31532700000000002</v>
       </c>
@@ -17143,7 +17160,7 @@
         <v>145.18527</v>
       </c>
     </row>
-    <row r="716" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="716" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U716" s="1">
         <v>0.32215700000000003</v>
       </c>
@@ -17166,7 +17183,7 @@
         <v>149.35590999999999</v>
       </c>
     </row>
-    <row r="717" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="717" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U717" s="1">
         <v>0.32917999999999997</v>
       </c>
@@ -17189,7 +17206,7 @@
         <v>153.90047000000001</v>
       </c>
     </row>
-    <row r="718" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="718" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U718" s="1">
         <v>0.33640599999999998</v>
       </c>
@@ -17212,7 +17229,7 @@
         <v>158.82198</v>
       </c>
     </row>
-    <row r="719" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="719" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U719" s="1">
         <v>0.34382800000000002</v>
       </c>
@@ -17235,7 +17252,7 @@
         <v>164.12209999999999</v>
       </c>
     </row>
-    <row r="720" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="720" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U720" s="1">
         <v>0.35145199999999999</v>
       </c>
@@ -17258,7 +17275,7 @@
         <v>169.79417000000001</v>
       </c>
     </row>
-    <row r="721" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="721" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U721" s="1">
         <v>0.35926599999999997</v>
       </c>
@@ -17281,7 +17298,7 @@
         <v>175.82220000000001</v>
       </c>
     </row>
-    <row r="722" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="722" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U722" s="1">
         <v>0.36724000000000001</v>
       </c>
@@ -17304,7 +17321,7 @@
         <v>182.13453999999999</v>
       </c>
     </row>
-    <row r="723" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="723" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U723" s="1">
         <v>0.37537700000000002</v>
       </c>
@@ -17327,7 +17344,7 @@
         <v>188.66225</v>
       </c>
     </row>
-    <row r="724" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="724" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U724" s="1">
         <v>0.38365500000000002</v>
       </c>
@@ -17350,7 +17367,7 @@
         <v>195.35811000000001</v>
       </c>
     </row>
-    <row r="725" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="725" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U725" s="1">
         <v>0.39206299999999999</v>
       </c>
@@ -17373,7 +17390,7 @@
         <v>202.15718000000001</v>
       </c>
     </row>
-    <row r="726" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="726" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U726" s="1">
         <v>0.40058899999999997</v>
       </c>
@@ -17396,7 +17413,7 @@
         <v>208.98799</v>
       </c>
     </row>
-    <row r="727" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="727" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U727" s="1">
         <v>0.409223</v>
       </c>
@@ -17419,7 +17436,7 @@
         <v>215.78008</v>
       </c>
     </row>
-    <row r="728" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="728" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U728" s="1">
         <v>0.41795199999999999</v>
       </c>
@@ -17442,7 +17459,7 @@
         <v>222.47345999999999</v>
       </c>
     </row>
-    <row r="729" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="729" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U729" s="1">
         <v>0.426757</v>
       </c>
@@ -17465,7 +17482,7 @@
         <v>228.99327</v>
       </c>
     </row>
-    <row r="730" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="730" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U730" s="1">
         <v>0.43563000000000002</v>
       </c>
@@ -17488,7 +17505,7 @@
         <v>235.27005</v>
       </c>
     </row>
-    <row r="731" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="731" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U731" s="1">
         <v>0.44453599999999999</v>
       </c>
@@ -17511,7 +17528,7 @@
         <v>241.21681000000001</v>
       </c>
     </row>
-    <row r="732" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="732" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U732" s="1">
         <v>0.45347199999999999</v>
       </c>
@@ -17534,7 +17551,7 @@
         <v>246.75491</v>
       </c>
     </row>
-    <row r="733" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="733" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U733" s="1">
         <v>0.46239999999999998</v>
       </c>
@@ -17557,7 +17574,7 @@
         <v>251.80431999999999</v>
       </c>
     </row>
-    <row r="734" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="734" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U734" s="1">
         <v>0.47131400000000001</v>
       </c>
@@ -17580,7 +17597,7 @@
         <v>256.279</v>
       </c>
     </row>
-    <row r="735" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="735" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U735" s="1">
         <v>0.48018</v>
       </c>
@@ -17603,7 +17620,7 @@
         <v>260.10117000000002</v>
       </c>
     </row>
-    <row r="736" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="736" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U736" s="1">
         <v>0.488983</v>
       </c>
@@ -17626,7 +17643,7 @@
         <v>263.18923999999998</v>
       </c>
     </row>
-    <row r="737" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="737" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U737" s="1">
         <v>0.49770599999999998</v>
       </c>
@@ -17649,7 +17666,7 @@
         <v>265.48853000000003</v>
       </c>
     </row>
-    <row r="738" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="738" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U738" s="1">
         <v>0.50635699999999995</v>
       </c>
@@ -17672,7 +17689,7 @@
         <v>266.99774000000002</v>
       </c>
     </row>
-    <row r="739" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="739" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U739" s="1">
         <v>0.51492400000000005</v>
       </c>
@@ -17695,7 +17712,7 @@
         <v>267.74185</v>
       </c>
     </row>
-    <row r="740" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="740" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U740" s="1">
         <v>0.52343099999999998</v>
       </c>
@@ -17718,7 +17735,7 @@
         <v>267.77285999999998</v>
       </c>
     </row>
-    <row r="741" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="741" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U741" s="1">
         <v>0.53188299999999999</v>
       </c>
@@ -17741,7 +17758,7 @@
         <v>267.18268</v>
       </c>
     </row>
-    <row r="742" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="742" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U742" s="1">
         <v>0.54029499999999997</v>
       </c>
@@ -17764,7 +17781,7 @@
         <v>266.06295999999998</v>
       </c>
     </row>
-    <row r="743" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="743" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U743" s="1">
         <v>0.54866999999999999</v>
       </c>
@@ -17787,7 +17804,7 @@
         <v>264.50371999999999</v>
       </c>
     </row>
-    <row r="744" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="744" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U744" s="1">
         <v>0.557033</v>
       </c>
@@ -17810,7 +17827,7 @@
         <v>262.6112</v>
       </c>
     </row>
-    <row r="745" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="745" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U745" s="1">
         <v>0.56538100000000002</v>
       </c>
@@ -17833,7 +17850,7 @@
         <v>260.49196999999998</v>
       </c>
     </row>
-    <row r="746" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="746" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U746" s="1">
         <v>0.57372800000000002</v>
       </c>
@@ -17856,7 +17873,7 @@
         <v>258.22732999999999</v>
       </c>
     </row>
-    <row r="747" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="747" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U747" s="1">
         <v>0.58207699999999996</v>
       </c>
@@ -17879,7 +17896,7 @@
         <v>255.88552999999999</v>
       </c>
     </row>
-    <row r="748" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="748" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U748" s="1">
         <v>0.59042899999999998</v>
       </c>
@@ -17902,7 +17919,7 @@
         <v>253.51163</v>
       </c>
     </row>
-    <row r="749" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="749" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U749" s="1">
         <v>0.59877599999999997</v>
       </c>
@@ -17925,7 +17942,7 @@
         <v>251.12924000000001</v>
       </c>
     </row>
-    <row r="750" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="750" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U750" s="1">
         <v>0.60711800000000005</v>
       </c>
@@ -17948,7 +17965,7 @@
         <v>248.74445</v>
       </c>
     </row>
-    <row r="751" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="751" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U751" s="1">
         <v>0.61545399999999995</v>
       </c>
@@ -17971,7 +17988,7 @@
         <v>246.36750000000001</v>
       </c>
     </row>
-    <row r="752" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="752" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U752" s="1">
         <v>0.62377400000000005</v>
       </c>
@@ -17994,7 +18011,7 @@
         <v>243.99531999999999</v>
       </c>
     </row>
-    <row r="753" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="753" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U753" s="1">
         <v>0.63208200000000003</v>
       </c>
@@ -18017,7 +18034,7 @@
         <v>241.61703</v>
       </c>
     </row>
-    <row r="754" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="754" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U754" s="1">
         <v>0.64038499999999998</v>
       </c>
@@ -18040,7 +18057,7 @@
         <v>239.24583000000001</v>
       </c>
     </row>
-    <row r="755" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="755" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U755" s="1">
         <v>0.64866999999999997</v>
       </c>
@@ -18063,7 +18080,7 @@
         <v>236.88042999999999</v>
       </c>
     </row>
-    <row r="756" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="756" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U756" s="1">
         <v>0.65692700000000004</v>
       </c>
@@ -18086,7 +18103,7 @@
         <v>234.48077000000001</v>
       </c>
     </row>
-    <row r="757" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="757" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U757" s="1">
         <v>0.66516500000000001</v>
       </c>
@@ -18109,7 +18126,7 @@
         <v>232.03460000000001</v>
       </c>
     </row>
-    <row r="758" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="758" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U758" s="1">
         <v>0.67337400000000003</v>
       </c>
@@ -18132,7 +18149,7 @@
         <v>229.553</v>
       </c>
     </row>
-    <row r="759" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="759" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U759" s="1">
         <v>0.68156099999999997</v>
       </c>
@@ -18155,7 +18172,7 @@
         <v>227.04498000000001</v>
       </c>
     </row>
-    <row r="760" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="760" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U760" s="1">
         <v>0.68971800000000005</v>
       </c>
@@ -18178,7 +18195,7 @@
         <v>224.50103999999999</v>
       </c>
     </row>
-    <row r="761" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="761" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U761" s="1">
         <v>0.69784999999999997</v>
       </c>
@@ -18201,7 +18218,7 @@
         <v>221.91175999999999</v>
       </c>
     </row>
-    <row r="762" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="762" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U762" s="1">
         <v>0.70593700000000004</v>
       </c>
@@ -18224,7 +18241,7 @@
         <v>219.26826</v>
       </c>
     </row>
-    <row r="763" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="763" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U763" s="1">
         <v>0.71399900000000005</v>
       </c>
@@ -18247,7 +18264,7 @@
         <v>216.57181</v>
       </c>
     </row>
-    <row r="764" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="764" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U764" s="1">
         <v>0.72201199999999999</v>
       </c>
@@ -18270,7 +18287,7 @@
         <v>213.82276999999999</v>
       </c>
     </row>
-    <row r="765" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="765" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U765" s="1">
         <v>0.72999700000000001</v>
       </c>
@@ -18293,7 +18310,7 @@
         <v>211.02945</v>
       </c>
     </row>
-    <row r="766" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="766" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U766" s="1">
         <v>0.73793600000000004</v>
       </c>
@@ -18316,7 +18333,7 @@
         <v>208.20094</v>
       </c>
     </row>
-    <row r="767" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="767" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U767" s="1">
         <v>0.74583200000000005</v>
       </c>
@@ -18339,7 +18356,7 @@
         <v>205.31844000000001</v>
       </c>
     </row>
-    <row r="768" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="768" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U768" s="1">
         <v>0.75368599999999997</v>
       </c>
@@ -18362,7 +18379,7 @@
         <v>202.38633999999999</v>
       </c>
     </row>
-    <row r="769" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="769" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U769" s="1">
         <v>0.76150399999999996</v>
       </c>
@@ -18385,7 +18402,7 @@
         <v>199.42944</v>
       </c>
     </row>
-    <row r="770" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="770" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U770" s="1">
         <v>0.76926799999999995</v>
       </c>
@@ -18408,7 +18425,7 @@
         <v>196.44434000000001</v>
       </c>
     </row>
-    <row r="771" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="771" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U771" s="1">
         <v>0.77699399999999996</v>
       </c>
@@ -18431,7 +18448,7 @@
         <v>193.42497</v>
       </c>
     </row>
-    <row r="772" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="772" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U772" s="1">
         <v>0.78468300000000002</v>
       </c>
@@ -18454,7 +18471,7 @@
         <v>190.40128999999999</v>
       </c>
     </row>
-    <row r="773" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="773" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U773" s="1">
         <v>0.79231799999999997</v>
       </c>
@@ -18477,7 +18494,7 @@
         <v>187.37152</v>
       </c>
     </row>
-    <row r="774" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="774" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U774" s="1">
         <v>0.79991199999999996</v>
       </c>
@@ -18500,7 +18517,7 @@
         <v>184.32648</v>
       </c>
     </row>
-    <row r="775" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="775" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U775" s="1">
         <v>0.80745999999999996</v>
       </c>
@@ -18523,7 +18540,7 @@
         <v>181.27806000000001</v>
       </c>
     </row>
-    <row r="776" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="776" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U776" s="1">
         <v>0.81498499999999996</v>
       </c>
@@ -18546,7 +18563,7 @@
         <v>178.26833999999999</v>
       </c>
     </row>
-    <row r="777" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="777" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U777" s="1">
         <v>0.82246699999999995</v>
       </c>
@@ -18569,7 +18586,7 @@
         <v>175.31306000000001</v>
       </c>
     </row>
-    <row r="778" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="778" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U778" s="1">
         <v>0.82994699999999999</v>
       </c>
@@ -18592,7 +18609,7 @@
         <v>172.43114</v>
       </c>
     </row>
-    <row r="779" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="779" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U779" s="1">
         <v>0.83741100000000002</v>
       </c>
@@ -18615,7 +18632,7 @@
         <v>169.66285999999999</v>
       </c>
     </row>
-    <row r="780" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="780" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U780" s="1">
         <v>0.84490799999999999</v>
       </c>
@@ -18638,7 +18655,7 @@
         <v>167.07219000000001</v>
       </c>
     </row>
-    <row r="781" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="781" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U781" s="1">
         <v>0.852437</v>
       </c>
@@ -18661,7 +18678,7 @@
         <v>164.72734</v>
       </c>
     </row>
-    <row r="782" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="782" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U782" s="1">
         <v>0.86003799999999997</v>
       </c>
@@ -18684,7 +18701,7 @@
         <v>162.68546000000001</v>
       </c>
     </row>
-    <row r="783" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="783" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U783" s="1">
         <v>0.86772199999999999</v>
       </c>
@@ -18707,7 +18724,7 @@
         <v>161.01622</v>
       </c>
     </row>
-    <row r="784" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="784" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U784" s="1">
         <v>0.87552700000000006</v>
       </c>
@@ -18730,7 +18747,7 @@
         <v>159.7867</v>
       </c>
     </row>
-    <row r="785" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="785" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U785" s="1">
         <v>0.88345799999999997</v>
       </c>
@@ -18753,7 +18770,7 @@
         <v>159.06358</v>
       </c>
     </row>
-    <row r="786" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="786" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U786" s="1">
         <v>0.89154999999999995</v>
       </c>
@@ -18776,7 +18793,7 @@
         <v>158.89989</v>
       </c>
     </row>
-    <row r="787" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="787" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U787" s="1">
         <v>0.89982300000000004</v>
       </c>
@@ -18799,7 +18816,7 @@
         <v>159.36062999999999</v>
       </c>
     </row>
-    <row r="788" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="788" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U788" s="1">
         <v>0.90828799999999998</v>
       </c>
@@ -18822,7 +18839,7 @@
         <v>160.49119999999999</v>
       </c>
     </row>
-    <row r="789" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="789" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U789" s="1">
         <v>0.91695499999999996</v>
       </c>
@@ -18845,7 +18862,7 @@
         <v>162.31241</v>
       </c>
     </row>
-    <row r="790" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="790" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U790" s="1">
         <v>0.92584500000000003</v>
       </c>
@@ -18868,7 +18885,7 @@
         <v>164.84845999999999</v>
       </c>
     </row>
-    <row r="791" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="791" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U791" s="1">
         <v>0.93494999999999995</v>
       </c>
@@ -18891,7 +18908,7 @@
         <v>168.10928000000001</v>
       </c>
     </row>
-    <row r="792" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="792" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U792" s="1">
         <v>0.944272</v>
       </c>
@@ -18914,7 +18931,7 @@
         <v>172.07497000000001</v>
       </c>
     </row>
-    <row r="793" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="793" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U793" s="1">
         <v>0.95380900000000002</v>
       </c>
@@ -18937,7 +18954,7 @@
         <v>176.71663000000001</v>
       </c>
     </row>
-    <row r="794" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="794" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U794" s="1">
         <v>0.96354499999999998</v>
       </c>
@@ -18960,7 +18977,7 @@
         <v>181.98661999999999</v>
       </c>
     </row>
-    <row r="795" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="795" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U795" s="1">
         <v>0.97347600000000001</v>
       </c>
@@ -18983,7 +19000,7 @@
         <v>187.82889</v>
       </c>
     </row>
-    <row r="796" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="796" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U796" s="1">
         <v>0.98358199999999996</v>
       </c>
@@ -19006,7 +19023,7 @@
         <v>194.16492</v>
       </c>
     </row>
-    <row r="797" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="797" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U797" s="1">
         <v>0.99383999999999995</v>
       </c>
@@ -19029,7 +19046,7 @@
         <v>200.88863000000001</v>
       </c>
     </row>
-    <row r="798" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="798" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U798" s="1">
         <v>1.0042260000000001</v>
       </c>
@@ -19052,7 +19069,7 @@
         <v>207.87917999999999</v>
       </c>
     </row>
-    <row r="799" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="799" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U799" s="1">
         <v>1.014723</v>
       </c>
@@ -19075,7 +19092,7 @@
         <v>215.0189</v>
       </c>
     </row>
-    <row r="800" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="800" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U800" s="1">
         <v>1.0253030000000001</v>
       </c>
@@ -19098,7 +19115,7 @@
         <v>222.18922000000001</v>
       </c>
     </row>
-    <row r="801" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="801" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U801" s="1">
         <v>1.035965</v>
       </c>
@@ -19121,7 +19138,7 @@
         <v>229.28323</v>
       </c>
     </row>
-    <row r="802" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="802" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U802" s="1">
         <v>1.046681</v>
       </c>
@@ -19144,7 +19161,7 @@
         <v>236.20393000000001</v>
       </c>
     </row>
-    <row r="803" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="803" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U803" s="1">
         <v>1.057477</v>
       </c>
@@ -19167,7 +19184,7 @@
         <v>242.89774</v>
       </c>
     </row>
-    <row r="804" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="804" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U804" s="1">
         <v>1.068357</v>
       </c>
@@ -19190,7 +19207,7 @@
         <v>249.37694999999999</v>
       </c>
     </row>
-    <row r="805" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="805" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U805" s="1">
         <v>1.079345</v>
       </c>
@@ -19213,7 +19230,7 @@
         <v>255.68158</v>
       </c>
     </row>
-    <row r="806" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="806" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U806" s="1">
         <v>1.090449</v>
       </c>
@@ -19236,7 +19253,7 @@
         <v>261.85912999999999</v>
       </c>
     </row>
-    <row r="807" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="807" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U807" s="1">
         <v>1.1016889999999999</v>
       </c>
@@ -19259,7 +19276,7 @@
         <v>267.96337999999997</v>
       </c>
     </row>
-    <row r="808" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="808" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U808" s="1">
         <v>1.1130819999999999</v>
       </c>
@@ -19282,7 +19299,7 @@
         <v>274.09473000000003</v>
       </c>
     </row>
-    <row r="809" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="809" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U809" s="1">
         <v>1.1246290000000001</v>
       </c>
@@ -19305,7 +19322,7 @@
         <v>280.33429999999998</v>
       </c>
     </row>
-    <row r="810" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="810" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U810" s="1">
         <v>1.1363350000000001</v>
       </c>
@@ -19328,7 +19345,7 @@
         <v>286.72055</v>
       </c>
     </row>
-    <row r="811" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="811" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U811" s="1">
         <v>1.1482019999999999</v>
       </c>
@@ -19351,7 +19368,7 @@
         <v>293.29147</v>
       </c>
     </row>
-    <row r="812" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="812" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U812" s="1">
         <v>1.1602030000000001</v>
       </c>
@@ -19374,7 +19391,7 @@
         <v>300.03250000000003</v>
       </c>
     </row>
-    <row r="813" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="813" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U813" s="1">
         <v>1.172326</v>
       </c>
@@ -19397,7 +19414,7 @@
         <v>306.87943000000001</v>
       </c>
     </row>
-    <row r="814" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="814" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U814" s="1">
         <v>1.1845300000000001</v>
       </c>
@@ -19420,7 +19437,7 @@
         <v>313.72710000000001</v>
       </c>
     </row>
-    <row r="815" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="815" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U815" s="1">
         <v>1.196796</v>
       </c>
@@ -19443,7 +19460,7 @@
         <v>320.43792999999999</v>
       </c>
     </row>
-    <row r="816" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="816" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U816" s="1">
         <v>1.2090749999999999</v>
       </c>
@@ -19466,7 +19483,7 @@
         <v>326.85205000000002</v>
       </c>
     </row>
-    <row r="817" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="817" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U817" s="1">
         <v>1.221344</v>
       </c>
@@ -19489,7 +19506,7 @@
         <v>332.78287</v>
       </c>
     </row>
-    <row r="818" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="818" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U818" s="1">
         <v>1.2335799999999999</v>
       </c>
@@ -19512,7 +19529,7 @@
         <v>338.08148</v>
       </c>
     </row>
-    <row r="819" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="819" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U819" s="1">
         <v>1.2457510000000001</v>
       </c>
@@ -19535,7 +19552,7 @@
         <v>342.60205000000002</v>
       </c>
     </row>
-    <row r="820" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="820" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U820" s="1">
         <v>1.257844</v>
       </c>
@@ -19558,7 +19575,7 @@
         <v>346.21005000000002</v>
       </c>
     </row>
-    <row r="821" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="821" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U821" s="1">
         <v>1.269855</v>
       </c>
@@ -19581,7 +19598,7 @@
         <v>348.83742999999998</v>
       </c>
     </row>
-    <row r="822" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="822" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U822" s="1">
         <v>1.2817890000000001</v>
       </c>
@@ -19604,7 +19621,7 @@
         <v>350.49581999999998</v>
       </c>
     </row>
-    <row r="823" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="823" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U823" s="1">
         <v>1.2936399999999999</v>
       </c>
@@ -19627,7 +19644,7 @@
         <v>351.21426000000002</v>
       </c>
     </row>
-    <row r="824" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="824" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U824" s="1">
         <v>1.3054220000000001</v>
       </c>
@@ -19650,7 +19667,7 @@
         <v>351.03278</v>
       </c>
     </row>
-    <row r="825" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="825" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U825" s="1">
         <v>1.317142</v>
       </c>
@@ -19673,7 +19690,7 @@
         <v>350.04915999999997</v>
       </c>
     </row>
-    <row r="826" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="826" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U826" s="1">
         <v>1.3288219999999999</v>
       </c>
@@ -19696,7 +19713,7 @@
         <v>348.40823</v>
       </c>
     </row>
-    <row r="827" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="827" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U827" s="1">
         <v>1.340482</v>
       </c>
@@ -19719,7 +19736,7 @@
         <v>346.27963</v>
       </c>
     </row>
-    <row r="828" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="828" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U828" s="1">
         <v>1.3521369999999999</v>
       </c>
@@ -19742,7 +19759,7 @@
         <v>343.80745999999999</v>
       </c>
     </row>
-    <row r="829" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="829" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U829" s="1">
         <v>1.363777</v>
       </c>
@@ -19765,7 +19782,7 @@
         <v>341.08199999999999</v>
       </c>
     </row>
-    <row r="830" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="830" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U830" s="1">
         <v>1.3754280000000001</v>
       </c>
@@ -19788,7 +19805,7 @@
         <v>338.20571999999999</v>
       </c>
     </row>
-    <row r="831" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="831" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U831" s="1">
         <v>1.387089</v>
       </c>
@@ -19811,7 +19828,7 @@
         <v>335.298</v>
       </c>
     </row>
-    <row r="832" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="832" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U832" s="1">
         <v>1.3988</v>
       </c>
@@ -19834,7 +19851,7 @@
         <v>332.50006000000002</v>
       </c>
     </row>
-    <row r="833" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="833" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U833" s="1">
         <v>1.4105319999999999</v>
       </c>
@@ -19857,7 +19874,7 @@
         <v>329.87689999999998</v>
       </c>
     </row>
-    <row r="834" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="834" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U834" s="1">
         <v>1.4223330000000001</v>
       </c>
@@ -19880,7 +19897,7 @@
         <v>327.46600000000001</v>
       </c>
     </row>
-    <row r="835" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="835" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U835" s="1">
         <v>1.4341919999999999</v>
       </c>
@@ -19903,7 +19920,7 @@
         <v>325.35683999999998</v>
       </c>
     </row>
-    <row r="836" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="836" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U836" s="1">
         <v>1.4461200000000001</v>
       </c>
@@ -19926,7 +19943,7 @@
         <v>323.5883</v>
       </c>
     </row>
-    <row r="837" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="837" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U837" s="1">
         <v>1.4581249999999999</v>
       </c>
@@ -19949,7 +19966,7 @@
         <v>322.18941999999998</v>
       </c>
     </row>
-    <row r="838" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="838" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U838" s="1">
         <v>1.4702059999999999</v>
       </c>
@@ -19972,7 +19989,7 @@
         <v>321.16910000000001</v>
       </c>
     </row>
-    <row r="839" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="839" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U839" s="1">
         <v>1.482369</v>
       </c>
@@ -19995,7 +20012,7 @@
         <v>320.53949999999998</v>
       </c>
     </row>
-    <row r="840" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="840" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U840" s="1">
         <v>1.4946159999999999</v>
       </c>
@@ -20018,7 +20035,7 @@
         <v>320.31121999999999</v>
       </c>
     </row>
-    <row r="841" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="841" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U841" s="1">
         <v>1.506942</v>
       </c>
@@ -20041,7 +20058,7 @@
         <v>320.45477</v>
       </c>
     </row>
-    <row r="842" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="842" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U842" s="1">
         <v>1.5193559999999999</v>
       </c>
@@ -20064,7 +20081,7 @@
         <v>320.95247999999998</v>
       </c>
     </row>
-    <row r="843" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="843" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U843" s="1">
         <v>1.5318419999999999</v>
       </c>
@@ -20087,7 +20104,7 @@
         <v>321.77390000000003</v>
       </c>
     </row>
-    <row r="844" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="844" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U844" s="1">
         <v>1.544397</v>
       </c>
@@ -20110,7 +20127,7 @@
         <v>322.85645</v>
       </c>
     </row>
-    <row r="845" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="845" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U845" s="1">
         <v>1.5570090000000001</v>
       </c>
@@ -20133,7 +20150,7 @@
         <v>324.13882000000001</v>
       </c>
     </row>
-    <row r="846" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="846" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U846" s="1">
         <v>1.569663</v>
       </c>
@@ -20156,7 +20173,7 @@
         <v>325.55020000000002</v>
       </c>
     </row>
-    <row r="847" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="847" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U847" s="1">
         <v>1.582341</v>
       </c>
@@ -20179,7 +20196,7 @@
         <v>326.9982</v>
       </c>
     </row>
-    <row r="848" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="848" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U848" s="1">
         <v>1.595019</v>
       </c>
@@ -20202,7 +20219,7 @@
         <v>328.36266999999998</v>
       </c>
     </row>
-    <row r="849" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="849" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U849" s="1">
         <v>1.6077030000000001</v>
       </c>
@@ -20225,7 +20242,7 @@
         <v>329.57094999999998</v>
       </c>
     </row>
-    <row r="850" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="850" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U850" s="1">
         <v>1.6203730000000001</v>
       </c>
@@ -20248,7 +20265,7 @@
         <v>330.57477</v>
       </c>
     </row>
-    <row r="851" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="851" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U851" s="1">
         <v>1.6330229999999999</v>
       </c>
@@ -20271,7 +20288,7 @@
         <v>331.30176</v>
       </c>
     </row>
-    <row r="852" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="852" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U852" s="1">
         <v>1.645634</v>
       </c>
@@ -20294,7 +20311,7 @@
         <v>331.66552999999999</v>
       </c>
     </row>
-    <row r="853" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="853" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U853" s="1">
         <v>1.6582220000000001</v>
       </c>
@@ -20317,7 +20334,7 @@
         <v>331.64150000000001</v>
       </c>
     </row>
-    <row r="854" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="854" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U854" s="1">
         <v>1.6707380000000001</v>
       </c>
@@ -20340,7 +20357,7 @@
         <v>331.18830000000003</v>
       </c>
     </row>
-    <row r="855" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="855" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U855" s="1">
         <v>1.6831970000000001</v>
       </c>
@@ -20363,7 +20380,7 @@
         <v>330.23964999999998</v>
       </c>
     </row>
-    <row r="856" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="856" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U856" s="1">
         <v>1.6955800000000001</v>
       </c>
@@ -20386,7 +20403,7 @@
         <v>328.78888000000001</v>
       </c>
     </row>
-    <row r="857" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="857" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U857" s="1">
         <v>1.707892</v>
       </c>
@@ -20409,7 +20426,7 @@
         <v>326.85003999999998</v>
       </c>
     </row>
-    <row r="858" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="858" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U858" s="1">
         <v>1.7201299999999999</v>
       </c>
@@ -20432,7 +20449,7 @@
         <v>324.44574</v>
       </c>
     </row>
-    <row r="859" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="859" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U859" s="1">
         <v>1.732307</v>
       </c>
@@ -20455,7 +20472,7 @@
         <v>321.60577000000001</v>
       </c>
     </row>
-    <row r="860" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="860" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U860" s="1">
         <v>1.7444040000000001</v>
       </c>
@@ -20478,7 +20495,7 @@
         <v>318.35811999999999</v>
       </c>
     </row>
-    <row r="861" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="861" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U861" s="1">
         <v>1.7564379999999999</v>
       </c>
@@ -20501,7 +20518,7 @@
         <v>314.73453000000001</v>
       </c>
     </row>
-    <row r="862" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="862" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U862" s="1">
         <v>1.768416</v>
       </c>
@@ -20524,7 +20541,7 @@
         <v>310.81366000000003</v>
       </c>
     </row>
-    <row r="863" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="863" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U863" s="1">
         <v>1.7803640000000001</v>
       </c>
@@ -20547,7 +20564,7 @@
         <v>306.72134</v>
       </c>
     </row>
-    <row r="864" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="864" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U864" s="1">
         <v>1.7922880000000001</v>
       </c>
@@ -20570,7 +20587,7 @@
         <v>302.56702000000001</v>
       </c>
     </row>
-    <row r="865" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="865" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U865" s="1">
         <v>1.8041959999999999</v>
       </c>
@@ -20593,7 +20610,7 @@
         <v>298.4042</v>
       </c>
     </row>
-    <row r="866" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="866" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U866" s="1">
         <v>1.8161080000000001</v>
       </c>
@@ -20616,7 +20633,7 @@
         <v>294.31326000000001</v>
       </c>
     </row>
-    <row r="867" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="867" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U867" s="1">
         <v>1.8280350000000001</v>
       </c>
@@ -20639,7 +20656,7 @@
         <v>290.40190000000001</v>
       </c>
     </row>
-    <row r="868" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="868" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U868" s="1">
         <v>1.839987</v>
       </c>
@@ -20662,7 +20679,7 @@
         <v>286.75121999999999</v>
       </c>
     </row>
-    <row r="869" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="869" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U869" s="1">
         <v>1.8519749999999999</v>
       </c>
@@ -20685,7 +20702,7 @@
         <v>283.42077999999998</v>
       </c>
     </row>
-    <row r="870" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="870" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U870" s="1">
         <v>1.8639889999999999</v>
       </c>
@@ -20708,7 +20725,7 @@
         <v>280.42734000000002</v>
       </c>
     </row>
-    <row r="871" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="871" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U871" s="1">
         <v>1.8760490000000001</v>
       </c>
@@ -20731,7 +20748,7 @@
         <v>277.78854000000001</v>
       </c>
     </row>
-    <row r="872" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="872" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U872" s="1">
         <v>1.888147</v>
       </c>
@@ -20754,7 +20771,7 @@
         <v>275.5274</v>
       </c>
     </row>
-    <row r="873" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="873" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U873" s="1">
         <v>1.900285</v>
       </c>
@@ -20777,7 +20794,7 @@
         <v>273.63319999999999</v>
       </c>
     </row>
-    <row r="874" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="874" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U874" s="1">
         <v>1.9124779999999999</v>
       </c>
@@ -20800,7 +20817,7 @@
         <v>272.11385999999999</v>
       </c>
     </row>
-    <row r="875" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="875" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U875" s="1">
         <v>1.924717</v>
       </c>
@@ -20823,7 +20840,7 @@
         <v>270.95890000000003</v>
       </c>
     </row>
-    <row r="876" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="876" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U876" s="1">
         <v>1.937022</v>
       </c>
@@ -20846,7 +20863,7 @@
         <v>270.16609999999997</v>
       </c>
     </row>
-    <row r="877" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="877" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U877" s="1">
         <v>1.9493860000000001</v>
       </c>
@@ -20869,7 +20886,7 @@
         <v>269.73025999999999</v>
       </c>
     </row>
-    <row r="878" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="878" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U878" s="1">
         <v>1.961819</v>
       </c>
@@ -20892,7 +20909,7 @@
         <v>269.63479999999998</v>
       </c>
     </row>
-    <row r="879" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="879" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U879" s="1">
         <v>1.97431</v>
       </c>
@@ -20915,7 +20932,7 @@
         <v>269.86385999999999</v>
       </c>
     </row>
-    <row r="880" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="880" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U880" s="1">
         <v>1.986882</v>
       </c>
@@ -20938,7 +20955,7 @@
         <v>270.41592000000003</v>
       </c>
     </row>
-    <row r="881" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="881" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U881" s="1">
         <v>1.9995080000000001</v>
       </c>
@@ -20961,7 +20978,7 @@
         <v>271.27237000000002</v>
       </c>
     </row>
-    <row r="882" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="882" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U882" s="1">
         <v>2.012232</v>
       </c>
@@ -20984,7 +21001,7 @@
         <v>272.43756000000002</v>
       </c>
     </row>
-    <row r="883" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="883" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U883" s="1">
         <v>2.0250539999999999</v>
       </c>
@@ -21007,7 +21024,7 @@
         <v>273.96737999999999</v>
       </c>
     </row>
-    <row r="884" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="884" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U884" s="1">
         <v>2.0379719999999999</v>
       </c>
@@ -21030,7 +21047,7 @@
         <v>275.85852</v>
       </c>
     </row>
-    <row r="885" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="885" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U885" s="1">
         <v>2.0510060000000001</v>
       </c>
@@ -21053,7 +21070,7 @@
         <v>278.10406</v>
       </c>
     </row>
-    <row r="886" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="886" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U886" s="1">
         <v>2.0641620000000001</v>
       </c>
@@ -21076,7 +21093,7 @@
         <v>280.73212000000001</v>
       </c>
     </row>
-    <row r="887" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="887" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U887" s="1">
         <v>2.077445</v>
       </c>
@@ -21099,7 +21116,7 @@
         <v>283.78814999999997</v>
       </c>
     </row>
-    <row r="888" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="888" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U888" s="1">
         <v>2.0908410000000002</v>
       </c>
@@ -21122,7 +21139,7 @@
         <v>287.24907999999999</v>
       </c>
     </row>
-    <row r="889" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="889" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U889" s="1">
         <v>2.1043699999999999</v>
       </c>
@@ -21145,7 +21162,7 @@
         <v>291.08728000000002</v>
       </c>
     </row>
-    <row r="890" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="890" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U890" s="1">
         <v>2.1179999999999999</v>
       </c>
@@ -21168,7 +21185,7 @@
         <v>295.28460000000001</v>
       </c>
     </row>
-    <row r="891" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="891" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U891" s="1">
         <v>2.1317360000000001</v>
       </c>
@@ -21191,7 +21208,7 @@
         <v>299.77713</v>
       </c>
     </row>
-    <row r="892" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="892" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U892" s="1">
         <v>2.1455380000000002</v>
       </c>
@@ -21214,7 +21231,7 @@
         <v>304.45940000000002</v>
       </c>
     </row>
-    <row r="893" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="893" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U893" s="1">
         <v>2.1594069999999999</v>
       </c>
@@ -21237,7 +21254,7 @@
         <v>309.21746999999999</v>
       </c>
     </row>
-    <row r="894" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="894" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U894" s="1">
         <v>2.1732999999999998</v>
       </c>
@@ -21260,7 +21277,7 @@
         <v>313.93414000000001</v>
       </c>
     </row>
-    <row r="895" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="895" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U895" s="1">
         <v>2.1871909999999999</v>
       </c>
@@ -21283,7 +21300,7 @@
         <v>318.43488000000002</v>
       </c>
     </row>
-    <row r="896" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="896" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U896" s="1">
         <v>2.2010529999999999</v>
       </c>
@@ -21306,7 +21323,7 @@
         <v>322.55038000000002</v>
       </c>
     </row>
-    <row r="897" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="897" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U897" s="1">
         <v>2.2148880000000002</v>
       </c>
@@ -21329,7 +21346,7 @@
         <v>326.17327999999998</v>
       </c>
     </row>
-    <row r="898" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="898" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U898" s="1">
         <v>2.2286540000000001</v>
       </c>
@@ -21352,7 +21369,7 @@
         <v>329.20134999999999</v>
       </c>
     </row>
-    <row r="899" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="899" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U899" s="1">
         <v>2.2423609999999998</v>
       </c>
@@ -21375,7 +21392,7 @@
         <v>331.52330000000001</v>
       </c>
     </row>
-    <row r="900" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="900" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U900" s="1">
         <v>2.2559589999999998</v>
       </c>
@@ -21398,7 +21415,7 @@
         <v>333.02159999999998</v>
       </c>
     </row>
-    <row r="901" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="901" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U901" s="1">
         <v>2.2694540000000001</v>
       </c>
@@ -21421,7 +21438,7 @@
         <v>333.61380000000003</v>
       </c>
     </row>
-    <row r="902" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="902" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U902" s="1">
         <v>2.282816</v>
       </c>
@@ -21444,7 +21461,7 @@
         <v>333.27213</v>
       </c>
     </row>
-    <row r="903" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="903" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U903" s="1">
         <v>2.296055</v>
       </c>
@@ -21467,7 +21484,7 @@
         <v>331.98773</v>
       </c>
     </row>
-    <row r="904" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="904" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U904" s="1">
         <v>2.3091599999999999</v>
       </c>
@@ -21490,7 +21507,7 @@
         <v>329.7944</v>
       </c>
     </row>
-    <row r="905" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="905" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U905" s="1">
         <v>2.3221530000000001</v>
       </c>
@@ -21513,7 +21530,7 @@
         <v>326.76420000000002</v>
       </c>
     </row>
-    <row r="906" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="906" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U906" s="1">
         <v>2.3350270000000002</v>
       </c>
@@ -21536,7 +21553,7 @@
         <v>322.98050000000001</v>
       </c>
     </row>
-    <row r="907" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="907" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U907" s="1">
         <v>2.347804</v>
       </c>
@@ -21559,7 +21576,7 @@
         <v>318.53708</v>
       </c>
     </row>
-    <row r="908" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="908" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U908" s="1">
         <v>2.3604910000000001</v>
       </c>
@@ -21582,7 +21599,7 @@
         <v>313.56732</v>
       </c>
     </row>
-    <row r="909" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="909" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U909" s="1">
         <v>2.3731170000000001</v>
       </c>
@@ -21605,7 +21622,7 @@
         <v>308.23525999999998</v>
       </c>
     </row>
-    <row r="910" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="910" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U910" s="1">
         <v>2.38571</v>
       </c>
@@ -21628,7 +21645,7 @@
         <v>302.74259999999998</v>
       </c>
     </row>
-    <row r="911" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="911" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U911" s="1">
         <v>2.398285</v>
       </c>
@@ -21651,7 +21668,7 @@
         <v>297.25252999999998</v>
       </c>
     </row>
-    <row r="912" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="912" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U912" s="1">
         <v>2.4108700000000001</v>
       </c>
@@ -21674,7 +21691,7 @@
         <v>291.90253000000001</v>
       </c>
     </row>
-    <row r="913" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="913" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U913" s="1">
         <v>2.4234779999999998</v>
       </c>
@@ -21697,7 +21714,7 @@
         <v>286.83526999999998</v>
       </c>
     </row>
-    <row r="914" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="914" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U914" s="1">
         <v>2.436131</v>
       </c>
@@ -21720,7 +21737,7 @@
         <v>282.18040000000002</v>
       </c>
     </row>
-    <row r="915" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="915" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U915" s="1">
         <v>2.4488249999999998</v>
       </c>
@@ -21743,7 +21760,7 @@
         <v>278.02071999999998</v>
       </c>
     </row>
-    <row r="916" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="916" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U916" s="1">
         <v>2.46157</v>
       </c>
@@ -21766,7 +21783,7 @@
         <v>274.38670000000002</v>
       </c>
     </row>
-    <row r="917" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="917" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U917" s="1">
         <v>2.4743629999999999</v>
       </c>
@@ -21789,7 +21806,7 @@
         <v>271.29903999999999</v>
       </c>
     </row>
-    <row r="918" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="918" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U918" s="1">
         <v>2.4872160000000001</v>
       </c>
@@ -21812,7 +21829,7 @@
         <v>268.77611999999999</v>
       </c>
     </row>
-    <row r="919" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="919" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U919" s="1">
         <v>2.5001180000000001</v>
       </c>
@@ -21835,7 +21852,7 @@
         <v>266.80822999999998</v>
       </c>
     </row>
-    <row r="920" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="920" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U920" s="1">
         <v>2.5130780000000001</v>
       </c>
@@ -21858,7 +21875,7 @@
         <v>265.35336000000001</v>
       </c>
     </row>
-    <row r="921" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="921" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U921" s="1">
         <v>2.526078</v>
       </c>
@@ -21881,7 +21898,7 @@
         <v>264.34528</v>
       </c>
     </row>
-    <row r="922" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="922" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U922" s="1">
         <v>2.53911</v>
       </c>
@@ -21904,7 +21921,7 @@
         <v>263.70337000000001</v>
       </c>
     </row>
-    <row r="923" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="923" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U923" s="1">
         <v>2.5521479999999999</v>
       </c>
@@ -21927,7 +21944,7 @@
         <v>263.32816000000003</v>
       </c>
     </row>
-    <row r="924" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="924" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U924" s="1">
         <v>2.5651820000000001</v>
       </c>
@@ -21950,7 +21967,7 @@
         <v>263.10989999999998</v>
       </c>
     </row>
-    <row r="925" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="925" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U925" s="1">
         <v>2.5781839999999998</v>
       </c>
@@ -21973,7 +21990,7 @@
         <v>262.93729999999999</v>
       </c>
     </row>
-    <row r="926" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="926" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U926" s="1">
         <v>2.5911499999999998</v>
       </c>
@@ -21996,7 +22013,7 @@
         <v>262.70190000000002</v>
       </c>
     </row>
-    <row r="927" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="927" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U927" s="1">
         <v>2.6040350000000001</v>
       </c>
@@ -22019,7 +22036,7 @@
         <v>262.27213</v>
       </c>
     </row>
-    <row r="928" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="928" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U928" s="1">
         <v>2.6168659999999999</v>
       </c>
@@ -22042,7 +22059,7 @@
         <v>261.55759999999998</v>
       </c>
     </row>
-    <row r="929" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="929" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U929" s="1">
         <v>2.6296089999999999</v>
       </c>
@@ -22065,7 +22082,7 @@
         <v>260.51758000000001</v>
       </c>
     </row>
-    <row r="930" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="930" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U930" s="1">
         <v>2.6422650000000001</v>
       </c>
@@ -22088,7 +22105,7 @@
         <v>259.0829</v>
       </c>
     </row>
-    <row r="931" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="931" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U931" s="1">
         <v>2.6548250000000002</v>
       </c>
@@ -22111,7 +22128,7 @@
         <v>257.20600000000002</v>
       </c>
     </row>
-    <row r="932" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="932" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U932" s="1">
         <v>2.6673170000000002</v>
       </c>
@@ -22134,7 +22151,7 @@
         <v>254.91739999999999</v>
       </c>
     </row>
-    <row r="933" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="933" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U933" s="1">
         <v>2.679738</v>
       </c>
@@ -22157,7 +22174,7 @@
         <v>252.30318</v>
       </c>
     </row>
-    <row r="934" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="934" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U934" s="1">
         <v>2.692094</v>
       </c>
@@ -22180,7 +22197,7 @@
         <v>249.40427</v>
       </c>
     </row>
-    <row r="935" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="935" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U935" s="1">
         <v>2.7043919999999999</v>
       </c>
@@ -22203,7 +22220,7 @@
         <v>246.25064</v>
       </c>
     </row>
-    <row r="936" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="936" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U936" s="1">
         <v>2.7166649999999999</v>
       </c>
@@ -22226,7 +22243,7 @@
         <v>242.95433</v>
       </c>
     </row>
-    <row r="937" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="937" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U937" s="1">
         <v>2.7289249999999998</v>
       </c>
@@ -22249,7 +22266,7 @@
         <v>239.66322</v>
       </c>
     </row>
-    <row r="938" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="938" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U938" s="1">
         <v>2.7411970000000001</v>
       </c>
@@ -22272,7 +22289,7 @@
         <v>236.49289999999999</v>
       </c>
     </row>
-    <row r="939" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="939" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U939" s="1">
         <v>2.7535259999999999</v>
       </c>
@@ -22295,7 +22312,7 @@
         <v>233.65720999999999</v>
       </c>
     </row>
-    <row r="940" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="940" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U940" s="1">
         <v>2.7659310000000001</v>
       </c>
@@ -22318,7 +22335,7 @@
         <v>231.36786000000001</v>
       </c>
     </row>
-    <row r="941" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="941" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U941" s="1">
         <v>2.7784450000000001</v>
       </c>
@@ -22341,7 +22358,7 @@
         <v>229.69862000000001</v>
       </c>
     </row>
-    <row r="942" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="942" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U942" s="1">
         <v>2.7911009999999998</v>
       </c>
@@ -22364,7 +22381,7 @@
         <v>228.70706000000001</v>
       </c>
     </row>
-    <row r="943" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="943" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U943" s="1">
         <v>2.803938</v>
       </c>
@@ -22387,7 +22404,7 @@
         <v>228.46046000000001</v>
       </c>
     </row>
-    <row r="944" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="944" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U944" s="1">
         <v>2.8169930000000001</v>
       </c>
@@ -22410,7 +22427,7 @@
         <v>229.02350000000001</v>
       </c>
     </row>
-    <row r="945" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="945" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U945" s="1">
         <v>2.8303069999999999</v>
       </c>
@@ -22433,7 +22450,7 @@
         <v>230.61024</v>
       </c>
     </row>
-    <row r="946" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="946" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U946" s="1">
         <v>2.843899</v>
       </c>
@@ -22456,7 +22473,7 @@
         <v>233.45115999999999</v>
       </c>
     </row>
-    <row r="947" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="947" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U947" s="1">
         <v>2.8578000000000001</v>
       </c>
@@ -22479,7 +22496,7 @@
         <v>237.64268000000001</v>
       </c>
     </row>
-    <row r="948" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="948" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U948" s="1">
         <v>2.872004</v>
       </c>
@@ -22502,7 +22519,7 @@
         <v>243.24109999999999</v>
       </c>
     </row>
-    <row r="949" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="949" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U949" s="1">
         <v>2.8865370000000001</v>
       </c>
@@ -22525,7 +22542,7 @@
         <v>250.28620000000001</v>
       </c>
     </row>
-    <row r="950" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="950" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U950" s="1">
         <v>2.9013939999999998</v>
       </c>
@@ -22548,7 +22565,7 @@
         <v>258.80169999999998</v>
       </c>
     </row>
-    <row r="951" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="951" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U951" s="1">
         <v>2.9165730000000001</v>
       </c>
@@ -22571,7 +22588,7 @@
         <v>268.76130000000001</v>
       </c>
     </row>
-    <row r="952" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="952" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U952" s="1">
         <v>2.932067</v>
       </c>
@@ -22594,7 +22611,7 @@
         <v>280.10311999999999</v>
       </c>
     </row>
-    <row r="953" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="953" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U953" s="1">
         <v>2.9478599999999999</v>
       </c>
@@ -22617,7 +22634,7 @@
         <v>292.72028</v>
       </c>
     </row>
-    <row r="954" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="954" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U954" s="1">
         <v>2.9639250000000001</v>
       </c>
@@ -22640,7 +22657,7 @@
         <v>306.46557999999999</v>
       </c>
     </row>
-    <row r="955" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="955" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U955" s="1">
         <v>2.9802379999999999</v>
       </c>
@@ -22663,7 +22680,7 @@
         <v>321.15753000000001</v>
       </c>
     </row>
-    <row r="956" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="956" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U956" s="1">
         <v>2.996775</v>
       </c>
@@ -22686,7 +22703,7 @@
         <v>336.60183999999998</v>
       </c>
     </row>
-    <row r="957" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="957" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U957" s="1">
         <v>3.0134850000000002</v>
       </c>
@@ -22709,7 +22726,7 @@
         <v>352.54867999999999</v>
       </c>
     </row>
-    <row r="958" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="958" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U958" s="1">
         <v>3.0303290000000001</v>
       </c>
@@ -22732,7 +22749,7 @@
         <v>368.67946999999998</v>
       </c>
     </row>
-    <row r="959" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="959" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U959" s="1">
         <v>3.0472640000000002</v>
       </c>
@@ -22755,7 +22772,7 @@
         <v>384.66922</v>
       </c>
     </row>
-    <row r="960" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="960" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U960" s="1">
         <v>3.0642450000000001</v>
       </c>
@@ -22778,7 +22795,7 @@
         <v>400.20925999999997</v>
       </c>
     </row>
-    <row r="961" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="961" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U961" s="1">
         <v>3.081242</v>
       </c>
@@ -22801,7 +22818,7 @@
         <v>415.00423999999998</v>
       </c>
     </row>
-    <row r="962" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="962" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U962" s="1">
         <v>3.0982099999999999</v>
       </c>
@@ -22824,7 +22841,7 @@
         <v>428.73752000000002</v>
       </c>
     </row>
-    <row r="963" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="963" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U963" s="1">
         <v>3.115132</v>
       </c>
@@ -22847,7 +22864,7 @@
         <v>441.14364999999998</v>
       </c>
     </row>
-    <row r="964" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="964" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U964" s="1">
         <v>3.1319910000000002</v>
       </c>
@@ -22870,7 +22887,7 @@
         <v>452.05790000000002</v>
       </c>
     </row>
-    <row r="965" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="965" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U965" s="1">
         <v>3.1487470000000002</v>
       </c>
@@ -22893,7 +22910,7 @@
         <v>461.31040000000002</v>
       </c>
     </row>
-    <row r="966" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="966" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U966" s="1">
         <v>3.165397</v>
       </c>
@@ -22916,7 +22933,7 @@
         <v>468.76825000000002</v>
       </c>
     </row>
-    <row r="967" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="967" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U967" s="1">
         <v>3.181918</v>
       </c>
@@ -22939,7 +22956,7 @@
         <v>474.36541999999997</v>
       </c>
     </row>
-    <row r="968" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="968" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U968" s="1">
         <v>3.1983220000000001</v>
       </c>
@@ -22962,7 +22979,7 @@
         <v>478.13884999999999</v>
       </c>
     </row>
-    <row r="969" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="969" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U969" s="1">
         <v>3.2145929999999998</v>
       </c>
@@ -22985,7 +23002,7 @@
         <v>480.16986000000003</v>
       </c>
     </row>
-    <row r="970" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="970" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U970" s="1">
         <v>3.230731</v>
       </c>
@@ -23008,7 +23025,7 @@
         <v>480.50243999999998</v>
       </c>
     </row>
-    <row r="971" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="971" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U971" s="1">
         <v>3.246731</v>
       </c>
@@ -23031,7 +23048,7 @@
         <v>479.22561999999999</v>
       </c>
     </row>
-    <row r="972" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="972" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U972" s="1">
         <v>3.262626</v>
       </c>
@@ -23054,7 +23071,7 @@
         <v>476.53429999999997</v>
       </c>
     </row>
-    <row r="973" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="973" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U973" s="1">
         <v>3.2783959999999999</v>
       </c>
@@ -23077,7 +23094,7 @@
         <v>472.62732</v>
       </c>
     </row>
-    <row r="974" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="974" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U974" s="1">
         <v>3.2940800000000001</v>
       </c>
@@ -23100,7 +23117,7 @@
         <v>467.68542000000002</v>
       </c>
     </row>
-    <row r="975" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="975" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U975" s="1">
         <v>3.3096589999999999</v>
       </c>
@@ -23123,7 +23140,7 @@
         <v>461.87040000000002</v>
       </c>
     </row>
-    <row r="976" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="976" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U976" s="1">
         <v>3.3251539999999999</v>
       </c>
@@ -23146,7 +23163,7 @@
         <v>455.33292</v>
       </c>
     </row>
-    <row r="977" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="977" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U977" s="1">
         <v>3.34056</v>
       </c>
@@ -23169,7 +23186,7 @@
         <v>448.24783000000002</v>
       </c>
     </row>
-    <row r="978" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="978" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U978" s="1">
         <v>3.355893</v>
       </c>
@@ -23192,7 +23209,7 @@
         <v>440.76114000000001</v>
       </c>
     </row>
-    <row r="979" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="979" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U979" s="1">
         <v>3.3711639999999998</v>
       </c>
@@ -23215,7 +23232,7 @@
         <v>433.02294999999998</v>
       </c>
     </row>
-    <row r="980" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="980" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U980" s="1">
         <v>3.3864019999999999</v>
       </c>
@@ -23238,7 +23255,7 @@
         <v>425.20123000000001</v>
       </c>
     </row>
-    <row r="981" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="981" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U981" s="1">
         <v>3.4016039999999998</v>
       </c>
@@ -23261,7 +23278,7 @@
         <v>417.44033999999999</v>
       </c>
     </row>
-    <row r="982" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="982" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U982" s="1">
         <v>3.4168099999999999</v>
       </c>
@@ -23284,7 +23301,7 @@
         <v>409.86565999999999</v>
       </c>
     </row>
-    <row r="983" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="983" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U983" s="1">
         <v>3.4320089999999999</v>
       </c>
@@ -23307,7 +23324,7 @@
         <v>402.5881</v>
       </c>
     </row>
-    <row r="984" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="984" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U984" s="1">
         <v>3.447222</v>
       </c>
@@ -23330,7 +23347,7 @@
         <v>395.69072999999997</v>
       </c>
     </row>
-    <row r="985" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="985" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U985" s="1">
         <v>3.4624700000000002</v>
       </c>
@@ -23353,7 +23370,7 @@
         <v>389.28714000000002</v>
       </c>
     </row>
-    <row r="986" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="986" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U986" s="1">
         <v>3.47777</v>
       </c>
@@ -23376,7 +23393,7 @@
         <v>383.49619999999999</v>
       </c>
     </row>
-    <row r="987" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="987" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U987" s="1">
         <v>3.4931369999999999</v>
       </c>
@@ -23399,7 +23416,7 @@
         <v>378.40985000000001</v>
       </c>
     </row>
-    <row r="988" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="988" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U988" s="1">
         <v>3.5085760000000001</v>
       </c>
@@ -23422,7 +23439,7 @@
         <v>374.05655000000002</v>
       </c>
     </row>
-    <row r="989" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="989" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U989" s="1">
         <v>3.5240939999999998</v>
       </c>
@@ -23445,7 +23462,7 @@
         <v>370.43783999999999</v>
       </c>
     </row>
-    <row r="990" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="990" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U990" s="1">
         <v>3.539682</v>
       </c>
@@ -23468,7 +23485,7 @@
         <v>367.55439999999999</v>
       </c>
     </row>
-    <row r="991" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="991" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U991" s="1">
         <v>3.5553490000000001</v>
       </c>
@@ -23491,7 +23508,7 @@
         <v>365.39269999999999</v>
       </c>
     </row>
-    <row r="992" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="992" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U992" s="1">
         <v>3.5710799999999998</v>
       </c>
@@ -23514,7 +23531,7 @@
         <v>363.91230000000002</v>
       </c>
     </row>
-    <row r="993" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="993" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U993" s="1">
         <v>3.5868790000000002</v>
       </c>
@@ -23537,7 +23554,7 @@
         <v>363.04138</v>
       </c>
     </row>
-    <row r="994" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="994" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U994" s="1">
         <v>3.6027110000000002</v>
       </c>
@@ -23560,7 +23577,7 @@
         <v>362.66208</v>
       </c>
     </row>
-    <row r="995" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="995" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U995" s="1">
         <v>3.618576</v>
       </c>
@@ -23583,7 +23600,7 @@
         <v>362.63184000000001</v>
       </c>
     </row>
-    <row r="996" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="996" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U996" s="1">
         <v>3.6344400000000001</v>
       </c>
@@ -23606,7 +23623,7 @@
         <v>362.80945000000003</v>
       </c>
     </row>
-    <row r="997" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="997" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U997" s="1">
         <v>3.6503009999999998</v>
       </c>
@@ -23629,7 +23646,7 @@
         <v>363.06738000000001</v>
       </c>
     </row>
-    <row r="998" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="998" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U998" s="1">
         <v>3.6661320000000002</v>
       </c>
@@ -23652,7 +23669,7 @@
         <v>363.28359999999998</v>
       </c>
     </row>
-    <row r="999" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="999" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U999" s="1">
         <v>3.6819510000000002</v>
       </c>
@@ -23675,7 +23692,7 @@
         <v>363.36630000000002</v>
       </c>
     </row>
-    <row r="1000" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1000" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1000" s="1">
         <v>3.6977370000000001</v>
       </c>
@@ -23698,7 +23715,7 @@
         <v>363.2534</v>
       </c>
     </row>
-    <row r="1001" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1001" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1001" s="1">
         <v>3.7134800000000001</v>
       </c>
@@ -23721,7 +23738,7 @@
         <v>362.84787</v>
       </c>
     </row>
-    <row r="1002" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1002" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1002" s="1">
         <v>3.7291780000000001</v>
       </c>
@@ -23744,7 +23761,7 @@
         <v>362.0788</v>
       </c>
     </row>
-    <row r="1003" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1003" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1003" s="1">
         <v>3.7448220000000001</v>
       </c>
@@ -23767,7 +23784,7 @@
         <v>360.92430000000002</v>
       </c>
     </row>
-    <row r="1004" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1004" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1004" s="1">
         <v>3.7604109999999999</v>
       </c>
@@ -23790,7 +23807,7 @@
         <v>359.39233000000002</v>
       </c>
     </row>
-    <row r="1005" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1005" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1005" s="1">
         <v>3.775957</v>
       </c>
@@ -23813,7 +23830,7 @@
         <v>357.50792999999999</v>
       </c>
     </row>
-    <row r="1006" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1006" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1006" s="1">
         <v>3.7914460000000001</v>
       </c>
@@ -23836,7 +23853,7 @@
         <v>355.28750000000002</v>
       </c>
     </row>
-    <row r="1007" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1007" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1007" s="1">
         <v>3.8068849999999999</v>
       </c>
@@ -23859,7 +23876,7 @@
         <v>352.73696999999999</v>
       </c>
     </row>
-    <row r="1008" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1008" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1008" s="1">
         <v>3.8222710000000002</v>
       </c>
@@ -23882,7 +23899,7 @@
         <v>349.87551999999999</v>
       </c>
     </row>
-    <row r="1009" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1009" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1009" s="1">
         <v>3.837615</v>
       </c>
@@ -23905,7 +23922,7 @@
         <v>346.76407</v>
       </c>
     </row>
-    <row r="1010" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1010" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1010" s="1">
         <v>3.852929</v>
       </c>
@@ -23928,7 +23945,7 @@
         <v>343.49610000000001</v>
       </c>
     </row>
-    <row r="1011" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1011" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1011" s="1">
         <v>3.8682159999999999</v>
       </c>
@@ -23951,7 +23968,7 @@
         <v>340.13538</v>
       </c>
     </row>
-    <row r="1012" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1012" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1012" s="1">
         <v>3.8834909999999998</v>
       </c>
@@ -23974,7 +23991,7 @@
         <v>336.7396</v>
       </c>
     </row>
-    <row r="1013" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1013" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1013" s="1">
         <v>3.8987449999999999</v>
       </c>
@@ -23997,7 +24014,7 @@
         <v>333.35712000000001</v>
       </c>
     </row>
-    <row r="1014" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1014" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1014" s="1">
         <v>3.9139949999999999</v>
       </c>
@@ -24020,7 +24037,7 @@
         <v>330.03616</v>
       </c>
     </row>
-    <row r="1015" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1015" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1015" s="1">
         <v>3.929249</v>
       </c>
@@ -24043,7 +24060,7 @@
         <v>326.86079999999998</v>
       </c>
     </row>
-    <row r="1016" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1016" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1016" s="1">
         <v>3.9445350000000001</v>
       </c>
@@ -24066,7 +24083,7 @@
         <v>323.93259999999998</v>
       </c>
     </row>
-    <row r="1017" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1017" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1017" s="1">
         <v>3.9598620000000002</v>
       </c>
@@ -24089,7 +24106,7 @@
         <v>321.33877999999999</v>
       </c>
     </row>
-    <row r="1018" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1018" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1018" s="1">
         <v>3.97526</v>
       </c>
@@ -24112,7 +24129,7 @@
         <v>319.16653000000002</v>
       </c>
     </row>
-    <row r="1019" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1019" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1019" s="1">
         <v>3.9907219999999999</v>
       </c>
@@ -24135,7 +24152,7 @@
         <v>317.47660000000002</v>
       </c>
     </row>
-    <row r="1020" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1020" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1020" s="1">
         <v>4.006278</v>
       </c>
@@ -24158,7 +24175,7 @@
         <v>316.31830000000002</v>
       </c>
     </row>
-    <row r="1021" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1021" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1021" s="1">
         <v>4.0219230000000001</v>
       </c>
@@ -24181,7 +24198,7 @@
         <v>315.76</v>
       </c>
     </row>
-    <row r="1022" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1022" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1022" s="1">
         <v>4.0376799999999999</v>
       </c>
@@ -24204,7 +24221,7 @@
         <v>315.85687000000001</v>
       </c>
     </row>
-    <row r="1023" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1023" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1023" s="1">
         <v>4.053553</v>
       </c>
@@ -24227,7 +24244,7 @@
         <v>316.65800000000002</v>
       </c>
     </row>
-    <row r="1024" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1024" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1024" s="1">
         <v>4.069553</v>
       </c>
@@ -24250,7 +24267,7 @@
         <v>318.18007999999998</v>
       </c>
     </row>
-    <row r="1025" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1025" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1025" s="1">
         <v>4.0856849999999998</v>
       </c>
@@ -24273,7 +24290,7 @@
         <v>320.42153999999999</v>
       </c>
     </row>
-    <row r="1026" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1026" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1026" s="1">
         <v>4.1019620000000003</v>
       </c>
@@ -24296,7 +24313,7 @@
         <v>323.38997999999998</v>
       </c>
     </row>
-    <row r="1027" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1027" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1027" s="1">
         <v>4.1183610000000002</v>
       </c>
@@ -24319,7 +24336,7 @@
         <v>327.05515000000003</v>
       </c>
     </row>
-    <row r="1028" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1028" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1028" s="1">
         <v>4.1348919999999998</v>
       </c>
@@ -24342,7 +24359,7 @@
         <v>331.34949999999998</v>
       </c>
     </row>
-    <row r="1029" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1029" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1029" s="1">
         <v>4.1515420000000001</v>
       </c>
@@ -24365,7 +24382,7 @@
         <v>336.21167000000003</v>
       </c>
     </row>
-    <row r="1030" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1030" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1030" s="1">
         <v>4.1682860000000002</v>
       </c>
@@ -24388,7 +24405,7 @@
         <v>341.54379999999998</v>
       </c>
     </row>
-    <row r="1031" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1031" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1031" s="1">
         <v>4.1851190000000003</v>
       </c>
@@ -24411,7 +24428,7 @@
         <v>347.21755999999999</v>
       </c>
     </row>
-    <row r="1032" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1032" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1032" s="1">
         <v>4.201981</v>
       </c>
@@ -24434,7 +24451,7 @@
         <v>353.03199999999998</v>
       </c>
     </row>
-    <row r="1033" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1033" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1033" s="1">
         <v>4.2188720000000002</v>
       </c>
@@ -24457,7 +24474,7 @@
         <v>358.78250000000003</v>
       </c>
     </row>
-    <row r="1034" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1034" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1034" s="1">
         <v>4.2357519999999997</v>
       </c>
@@ -24480,7 +24497,7 @@
         <v>364.30313000000001</v>
       </c>
     </row>
-    <row r="1035" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1035" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1035" s="1">
         <v>4.2525930000000001</v>
       </c>
@@ -24503,7 +24520,7 @@
         <v>369.39197000000001</v>
       </c>
     </row>
-    <row r="1036" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1036" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1036" s="1">
         <v>4.2694010000000002</v>
       </c>
@@ -24526,7 +24543,7 @@
         <v>373.89913999999999</v>
       </c>
     </row>
-    <row r="1037" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1037" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1037" s="1">
         <v>4.2861500000000001</v>
       </c>
@@ -24549,7 +24566,7 @@
         <v>377.70492999999999</v>
       </c>
     </row>
-    <row r="1038" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1038" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1038" s="1">
         <v>4.3028120000000003</v>
       </c>
@@ -24572,7 +24589,7 @@
         <v>380.66005999999999</v>
       </c>
     </row>
-    <row r="1039" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1039" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1039" s="1">
         <v>4.319388</v>
       </c>
@@ -24595,7 +24612,7 @@
         <v>382.65176000000002</v>
       </c>
     </row>
-    <row r="1040" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1040" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1040" s="1">
         <v>4.3358809999999997</v>
       </c>
@@ -24618,7 +24635,7 @@
         <v>383.68603999999999</v>
       </c>
     </row>
-    <row r="1041" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1041" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1041" s="1">
         <v>4.3522800000000004</v>
       </c>
@@ -24641,7 +24658,7 @@
         <v>383.81256000000002</v>
       </c>
     </row>
-    <row r="1042" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1042" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1042" s="1">
         <v>4.3685679999999998</v>
       </c>
@@ -24664,7 +24681,7 @@
         <v>382.99727999999999</v>
       </c>
     </row>
-    <row r="1043" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1043" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1043" s="1">
         <v>4.3847860000000001</v>
       </c>
@@ -24687,7 +24704,7 @@
         <v>381.29090000000002</v>
       </c>
     </row>
-    <row r="1044" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1044" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1044" s="1">
         <v>4.4009229999999997</v>
       </c>
@@ -24710,7 +24727,7 @@
         <v>378.85342000000003</v>
       </c>
     </row>
-    <row r="1045" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1045" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1045" s="1">
         <v>4.4169919999999996</v>
       </c>
@@ -24733,7 +24750,7 @@
         <v>375.80329999999998</v>
       </c>
     </row>
-    <row r="1046" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1046" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1046" s="1">
         <v>4.4329989999999997</v>
       </c>
@@ -24756,7 +24773,7 @@
         <v>372.21780000000001</v>
       </c>
     </row>
-    <row r="1047" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1047" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1047" s="1">
         <v>4.4489510000000001</v>
       </c>
@@ -24779,7 +24796,7 @@
         <v>368.19644</v>
       </c>
     </row>
-    <row r="1048" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1048" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1048" s="1">
         <v>4.4648519999999996</v>
       </c>
@@ -24802,7 +24819,7 @@
         <v>363.88263000000001</v>
       </c>
     </row>
-    <row r="1049" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1049" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1049" s="1">
         <v>4.4807009999999998</v>
       </c>
@@ -24825,7 +24842,7 @@
         <v>359.36635999999999</v>
       </c>
     </row>
-    <row r="1050" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1050" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1050" s="1">
         <v>4.4964880000000003</v>
       </c>
@@ -24848,7 +24865,7 @@
         <v>354.68002000000001</v>
       </c>
     </row>
-    <row r="1051" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1051" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1051" s="1">
         <v>4.5122229999999997</v>
       </c>
@@ -24871,7 +24888,7 @@
         <v>349.86563000000001</v>
       </c>
     </row>
-    <row r="1052" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1052" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1052" s="1">
         <v>4.5279020000000001</v>
       </c>
@@ -24894,7 +24911,7 @@
         <v>344.98110000000003</v>
       </c>
     </row>
-    <row r="1053" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1053" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1053" s="1">
         <v>4.5435439999999998</v>
       </c>
@@ -24917,7 +24934,7 @@
         <v>340.096</v>
       </c>
     </row>
-    <row r="1054" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1054" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1054" s="1">
         <v>4.5591340000000002</v>
       </c>
@@ -24940,7 +24957,7 @@
         <v>335.23218000000003</v>
       </c>
     </row>
-    <row r="1055" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1055" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1055" s="1">
         <v>4.5746960000000003</v>
       </c>
@@ -24963,7 +24980,7 @@
         <v>330.40550000000002</v>
       </c>
     </row>
-    <row r="1056" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1056" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1056" s="1">
         <v>4.5902099999999999</v>
       </c>
@@ -24986,7 +25003,7 @@
         <v>325.64413000000002</v>
       </c>
     </row>
-    <row r="1057" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1057" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1057" s="1">
         <v>4.6056790000000003</v>
       </c>
@@ -25009,7 +25026,7 @@
         <v>320.94630000000001</v>
       </c>
     </row>
-    <row r="1058" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1058" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1058" s="1">
         <v>4.6211149999999996</v>
       </c>
@@ -25032,7 +25049,7 @@
         <v>316.34044999999998</v>
       </c>
     </row>
-    <row r="1059" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1059" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1059" s="1">
         <v>4.636514</v>
       </c>
@@ -25055,7 +25072,7 @@
         <v>311.85903999999999</v>
       </c>
     </row>
-    <row r="1060" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1060" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1060" s="1">
         <v>4.6518839999999999</v>
       </c>
@@ -25078,7 +25095,7 @@
         <v>307.55916999999999</v>
       </c>
     </row>
-    <row r="1061" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1061" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1061" s="1">
         <v>4.6672099999999999</v>
       </c>
@@ -25101,7 +25118,7 @@
         <v>303.50599999999997</v>
       </c>
     </row>
-    <row r="1062" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1062" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1062" s="1">
         <v>4.6824979999999998</v>
       </c>
@@ -25124,7 +25141,7 @@
         <v>299.70693999999997</v>
       </c>
     </row>
-    <row r="1063" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1063" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1063" s="1">
         <v>4.6977460000000004</v>
       </c>
@@ -25147,7 +25164,7 @@
         <v>296.14425999999997</v>
       </c>
     </row>
-    <row r="1064" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1064" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1064" s="1">
         <v>4.7129490000000001</v>
       </c>
@@ -25170,7 +25187,7 @@
         <v>292.78426999999999</v>
       </c>
     </row>
-    <row r="1065" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1065" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1065" s="1">
         <v>4.7280889999999998</v>
       </c>
@@ -25193,7 +25210,7 @@
         <v>289.56655999999998</v>
       </c>
     </row>
-    <row r="1066" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1066" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1066" s="1">
         <v>4.7431809999999999</v>
       </c>
@@ -25216,7 +25233,7 @@
         <v>286.47129999999999</v>
       </c>
     </row>
-    <row r="1067" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1067" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1067" s="1">
         <v>4.7581990000000003</v>
       </c>
@@ -25239,7 +25256,7 @@
         <v>283.47199999999998</v>
       </c>
     </row>
-    <row r="1068" spans="21:27" x14ac:dyDescent="0.35">
+    <row r="1068" spans="21:27" x14ac:dyDescent="0.3">
       <c r="U1068" s="1">
         <v>4.768561</v>
       </c>
